--- a/research/traditional_assets/database/data/luxembourg/luxembourg_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_r_e_i_t.xlsx
@@ -650,10 +650,10 @@
         <v>0.1272471745622767</v>
       </c>
       <c r="X2">
-        <v>0.07250508641070338</v>
+        <v>0.07248791741450472</v>
       </c>
       <c r="Y2">
-        <v>0.05474208815157336</v>
+        <v>0.05475925714777202</v>
       </c>
       <c r="Z2">
         <v>0.09204192099504779</v>
@@ -662,10 +662,10 @@
         <v>0.04138997714057675</v>
       </c>
       <c r="AB2">
-        <v>0.06546325176723049</v>
+        <v>0.06545008993833873</v>
       </c>
       <c r="AC2">
-        <v>-0.02407327462665373</v>
+        <v>-0.02406011279776198</v>
       </c>
       <c r="AD2">
         <v>1112.9</v>
@@ -787,10 +787,10 @@
         <v>0.1272471745622767</v>
       </c>
       <c r="X3">
-        <v>0.07250508641070338</v>
+        <v>0.07248791741450472</v>
       </c>
       <c r="Y3">
-        <v>0.05474208815157336</v>
+        <v>0.05475925714777202</v>
       </c>
       <c r="Z3">
         <v>0.09204192099504779</v>
@@ -799,10 +799,10 @@
         <v>0.04138997714057675</v>
       </c>
       <c r="AB3">
-        <v>0.06546325176723049</v>
+        <v>0.06545008993833873</v>
       </c>
       <c r="AC3">
-        <v>-0.02407327462665373</v>
+        <v>-0.02406011279776198</v>
       </c>
       <c r="AD3">
         <v>1112.9</v>
@@ -1139,49 +1139,49 @@
         <v>8.832684824902721</v>
       </c>
       <c r="F2">
-        <v>4.56784350936784</v>
+        <v>4.53089036400796</v>
       </c>
       <c r="G2">
         <v>4.88757136583224</v>
       </c>
       <c r="H2">
-        <v>3.76940711462451</v>
+        <v>3.97881862099253</v>
       </c>
       <c r="I2">
         <v>0.23339554977665</v>
       </c>
       <c r="J2">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="K2">
         <v>3655.4</v>
       </c>
       <c r="L2">
-        <v>3831.42960793775</v>
+        <v>3835.48511783873</v>
       </c>
       <c r="M2">
         <v>4543.7</v>
       </c>
       <c r="N2">
-        <v>4465.12360793775</v>
+        <v>4516.86211783873</v>
       </c>
       <c r="O2">
         <v>1112.9</v>
       </c>
       <c r="P2">
-        <v>858.294</v>
+        <v>905.977</v>
       </c>
       <c r="Q2">
-        <v>0.0654632517672305</v>
+        <v>0.0654500899383387</v>
       </c>
       <c r="R2">
-        <v>0.0661404670643303</v>
+        <v>0.0656787415174285</v>
       </c>
       <c r="S2">
         <v>0.04233384</v>
       </c>
       <c r="T2">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0725050864107034</v>
+        <v>0.07248791741450469</v>
       </c>
       <c r="X2">
-        <v>0.0711191632491833</v>
+        <v>0.07134837940423271</v>
       </c>
       <c r="Y2">
         <v>0.616349131974705</v>
       </c>
       <c r="Z2">
-        <v>0.584362246613265</v>
+        <v>0.590031856910686</v>
       </c>
       <c r="AA2">
         <v>1112.9</v>
@@ -1236,7 +1236,7 @@
         <v>3655.4</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04330000000000001</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.06753755623901206</v>
+        <v>0.06752358092304805</v>
       </c>
       <c r="C2">
-        <v>4535.911951004956</v>
+        <v>4535.995704998334</v>
       </c>
       <c r="D2">
-        <v>4311.311951004956</v>
+        <v>4311.395704998334</v>
       </c>
       <c r="E2">
         <v>-1112.9</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.06753755623901206</v>
+        <v>0.06752358092304805</v>
       </c>
       <c r="T2">
         <v>0.5016993284768603</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.2494</v>
       </c>
       <c r="W2">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06741340297375195</v>
+        <v>0.06738895411222597</v>
       </c>
       <c r="C3">
-        <v>4501.467205523733</v>
+        <v>4502.672192318373</v>
       </c>
       <c r="D3">
-        <v>4324.550205523733</v>
+        <v>4325.755192318373</v>
       </c>
       <c r="E3">
         <v>-1065.217</v>
@@ -1539,37 +1539,37 @@
         <v>227</v>
       </c>
       <c r="M3">
-        <v>2.4652111</v>
+        <v>2.3984549</v>
       </c>
       <c r="N3">
-        <v>224.5347889</v>
+        <v>224.6015451</v>
       </c>
       <c r="O3">
-        <v>55.99897635166</v>
+        <v>56.01562534794</v>
       </c>
       <c r="P3">
-        <v>168.53581254834</v>
+        <v>168.58591975206</v>
       </c>
       <c r="Q3">
-        <v>169.23581254834</v>
+        <v>169.28591975206</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06770236643813329</v>
+        <v>0.06768828516386462</v>
       </c>
       <c r="T3">
         <v>0.505503121567312</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.2494</v>
       </c>
       <c r="W3">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>92.08136374203409</v>
+        <v>94.64426452213048</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.06728924970849187</v>
+        <v>0.06725432730140389</v>
       </c>
       <c r="C4">
-        <v>4467.104008845567</v>
+        <v>4469.44465037994</v>
       </c>
       <c r="D4">
-        <v>4337.870008845566</v>
+        <v>4340.21065037994</v>
       </c>
       <c r="E4">
         <v>-1017.534</v>
@@ -1621,37 +1621,37 @@
         <v>227</v>
       </c>
       <c r="M4">
-        <v>4.930422200000001</v>
+        <v>4.7969098</v>
       </c>
       <c r="N4">
-        <v>222.0695778</v>
+        <v>222.2030902</v>
       </c>
       <c r="O4">
-        <v>55.38415270332</v>
+        <v>55.41745069588</v>
       </c>
       <c r="P4">
-        <v>166.68542509668</v>
+        <v>166.78563950412</v>
       </c>
       <c r="Q4">
-        <v>167.38542509668</v>
+        <v>167.48563950412</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.06787054011070599</v>
+        <v>0.06785635071571826</v>
       </c>
       <c r="T4">
         <v>0.5093845430881814</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.2494</v>
       </c>
       <c r="W4">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>46.04068187101704</v>
+        <v>47.32213226106524</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06716509644323176</v>
+        <v>0.0671197004905818</v>
       </c>
       <c r="C5">
-        <v>4432.823116820126</v>
+        <v>4436.314044530693</v>
       </c>
       <c r="D5">
-        <v>4351.272116820126</v>
+        <v>4354.763044530692</v>
       </c>
       <c r="E5">
         <v>-969.8510000000001</v>
@@ -1703,37 +1703,37 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>7.395633300000001</v>
+        <v>7.1953647</v>
       </c>
       <c r="N5">
-        <v>219.6043667</v>
+        <v>219.8046353</v>
       </c>
       <c r="O5">
-        <v>54.76932905498</v>
+        <v>54.81927604382</v>
       </c>
       <c r="P5">
-        <v>164.83503764502</v>
+        <v>164.98535925618</v>
       </c>
       <c r="Q5">
-        <v>165.53503764502</v>
+        <v>165.68535925618</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.06804218128168224</v>
+        <v>0.06802788153668227</v>
       </c>
       <c r="T5">
         <v>0.5133459939187591</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.2494</v>
       </c>
       <c r="W5">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>30.69378791401136</v>
+        <v>31.54808817404349</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06704094317797167</v>
+        <v>0.06698507367975973</v>
       </c>
       <c r="C6">
-        <v>4398.625294666993</v>
+        <v>4403.281353108786</v>
       </c>
       <c r="D6">
-        <v>4364.757294666992</v>
+        <v>4369.413353108785</v>
       </c>
       <c r="E6">
         <v>-922.1680000000001</v>
@@ -1785,37 +1785,37 @@
         <v>227</v>
       </c>
       <c r="M6">
-        <v>9.860844400000001</v>
+        <v>9.5938196</v>
       </c>
       <c r="N6">
-        <v>217.1391556</v>
+        <v>217.4061804</v>
       </c>
       <c r="O6">
-        <v>54.15450540664001</v>
+        <v>54.22110139176001</v>
       </c>
       <c r="P6">
-        <v>162.98465019336</v>
+        <v>163.18507900824</v>
       </c>
       <c r="Q6">
-        <v>163.68465019336</v>
+        <v>163.88507900824</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.06821739831038717</v>
+        <v>0.06820298591641638</v>
       </c>
       <c r="T6">
         <v>0.5173899749749741</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.2494</v>
       </c>
       <c r="W6">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.02034093550852</v>
+        <v>23.66106613053262</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.06691678991271159</v>
+        <v>0.06685044686893764</v>
       </c>
       <c r="C7">
-        <v>4364.511317121313</v>
+        <v>4370.347567662136</v>
       </c>
       <c r="D7">
-        <v>4378.326317121313</v>
+        <v>4384.162567662136</v>
       </c>
       <c r="E7">
         <v>-874.4850000000001</v>
@@ -1867,37 +1867,37 @@
         <v>227</v>
       </c>
       <c r="M7">
-        <v>12.3260555</v>
+        <v>11.9922745</v>
       </c>
       <c r="N7">
-        <v>214.6739445</v>
+        <v>215.0077255</v>
       </c>
       <c r="O7">
-        <v>53.53968175830001</v>
+        <v>53.6229267397</v>
       </c>
       <c r="P7">
-        <v>161.1342627417</v>
+        <v>161.3847987603</v>
       </c>
       <c r="Q7">
-        <v>161.8342627417</v>
+        <v>162.0847987603</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.06839630411864378</v>
+        <v>0.06838177670414489</v>
       </c>
       <c r="T7">
         <v>0.5215190924744777</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.2494</v>
       </c>
       <c r="W7">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.41627274840682</v>
+        <v>18.92885290442609</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06679263664745148</v>
+        <v>0.06671582005811556</v>
       </c>
       <c r="C8">
-        <v>4330.481968582172</v>
+        <v>4337.513693172114</v>
       </c>
       <c r="D8">
-        <v>4391.979968582172</v>
+        <v>4399.011693172114</v>
       </c>
       <c r="E8">
         <v>-826.8020000000001</v>
@@ -1949,37 +1949,37 @@
         <v>227</v>
       </c>
       <c r="M8">
-        <v>14.7912666</v>
+        <v>14.3907294</v>
       </c>
       <c r="N8">
-        <v>212.2087334</v>
+        <v>212.6092706</v>
       </c>
       <c r="O8">
-        <v>52.92485810996</v>
+        <v>53.02475208764</v>
       </c>
       <c r="P8">
-        <v>159.28387529004</v>
+        <v>159.58451851236</v>
       </c>
       <c r="Q8">
-        <v>159.98387529004</v>
+        <v>160.28451851236</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.06857901643345903</v>
+        <v>0.06856437155118678</v>
       </c>
       <c r="T8">
         <v>0.5257360635378006</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.2494</v>
       </c>
       <c r="W8">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.34689395700568</v>
+        <v>15.77404408702175</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06666848338219139</v>
+        <v>0.06658119324729347</v>
       </c>
       <c r="C9">
-        <v>4296.538043263737</v>
+        <v>4304.780748281826</v>
       </c>
       <c r="D9">
-        <v>4405.719043263736</v>
+        <v>4413.961748281826</v>
       </c>
       <c r="E9">
         <v>-779.119</v>
@@ -2031,37 +2031,37 @@
         <v>227</v>
       </c>
       <c r="M9">
-        <v>17.2564777</v>
+        <v>16.7891843</v>
       </c>
       <c r="N9">
-        <v>209.7435223</v>
+        <v>210.2108157</v>
       </c>
       <c r="O9">
-        <v>52.31003446162</v>
+        <v>52.42657743558001</v>
       </c>
       <c r="P9">
-        <v>157.43348783838</v>
+        <v>157.78423826442</v>
       </c>
       <c r="Q9">
-        <v>158.13348783838</v>
+        <v>158.48423826442</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.06876565804536709</v>
+        <v>0.06875089316913277</v>
       </c>
       <c r="T9">
         <v>0.5300437221508724</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.2494</v>
       </c>
       <c r="W9">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>13.1544805345763</v>
+        <v>13.52060921744721</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06661038291693129</v>
+        <v>0.06653663843647141</v>
       </c>
       <c r="C10">
-        <v>4255.314137726135</v>
+        <v>4262.067881506794</v>
       </c>
       <c r="D10">
-        <v>4412.178137726135</v>
+        <v>4418.931881506794</v>
       </c>
       <c r="E10">
         <v>-731.4360000000001</v>
@@ -2113,37 +2113,37 @@
         <v>227</v>
       </c>
       <c r="M10">
-        <v>20.1412992</v>
+        <v>19.7598352</v>
       </c>
       <c r="N10">
-        <v>206.8587008</v>
+        <v>207.2401648</v>
       </c>
       <c r="O10">
-        <v>51.59055997952</v>
+        <v>51.68569710112001</v>
       </c>
       <c r="P10">
-        <v>155.26814082048</v>
+        <v>155.55446769888</v>
       </c>
       <c r="Q10">
-        <v>155.96814082048</v>
+        <v>156.25446769888</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.06895635708362097</v>
+        <v>0.06894146960486022</v>
       </c>
       <c r="T10">
         <v>0.5344450255164022</v>
       </c>
       <c r="U10">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.2494</v>
       </c>
       <c r="W10">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.27037524967605</v>
+        <v>11.48795006144586</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.0664944862516712</v>
+        <v>0.06641327062564932</v>
       </c>
       <c r="C11">
-        <v>4220.572236289155</v>
+        <v>4228.205267725571</v>
       </c>
       <c r="D11">
-        <v>4425.119236289154</v>
+        <v>4432.75226772557</v>
       </c>
       <c r="E11">
         <v>-683.7530000000002</v>
@@ -2195,37 +2195,37 @@
         <v>227</v>
       </c>
       <c r="M11">
-        <v>22.6589616</v>
+        <v>22.2298146</v>
       </c>
       <c r="N11">
-        <v>204.3410384</v>
+        <v>204.7701854</v>
       </c>
       <c r="O11">
-        <v>50.96265497696</v>
+        <v>51.06968423876</v>
       </c>
       <c r="P11">
-        <v>153.37838342304</v>
+        <v>153.70050116124</v>
       </c>
       <c r="Q11">
-        <v>154.07838342304</v>
+        <v>154.40050116124</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.06915124730952879</v>
+        <v>0.06913623453368056</v>
       </c>
       <c r="T11">
         <v>0.5389430608240315</v>
       </c>
       <c r="U11">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.2494</v>
       </c>
       <c r="W11">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>10.01811133304538</v>
+        <v>10.21151116572965</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.0665437215864111</v>
+        <v>0.06641750481482724</v>
       </c>
       <c r="C12">
-        <v>4167.382323011587</v>
+        <v>4180.046496560328</v>
       </c>
       <c r="D12">
-        <v>4419.612323011586</v>
+        <v>4432.276496560327</v>
       </c>
       <c r="E12">
         <v>-636.0700000000001</v>
@@ -2277,37 +2277,37 @@
         <v>227</v>
       </c>
       <c r="M12">
-        <v>26.22565</v>
+        <v>25.510405</v>
       </c>
       <c r="N12">
-        <v>200.77435</v>
+        <v>201.489595</v>
       </c>
       <c r="O12">
-        <v>50.07312289</v>
+        <v>50.251504993</v>
       </c>
       <c r="P12">
-        <v>150.70122711</v>
+        <v>151.238090007</v>
       </c>
       <c r="Q12">
-        <v>151.40122711</v>
+        <v>151.938090007</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.06935046842934567</v>
+        <v>0.06933532757203026</v>
       </c>
       <c r="T12">
         <v>0.5435410524718304</v>
       </c>
       <c r="U12">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.2494</v>
       </c>
       <c r="W12">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.655648191751204</v>
+        <v>8.898329916753575</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.066444338121151</v>
+        <v>0.06630689720400515</v>
       </c>
       <c r="C13">
-        <v>4130.829370022618</v>
+        <v>4144.825435503832</v>
       </c>
       <c r="D13">
-        <v>4430.742370022617</v>
+        <v>4444.738435503831</v>
       </c>
       <c r="E13">
         <v>-588.3870000000001</v>
@@ -2359,37 +2359,37 @@
         <v>227</v>
       </c>
       <c r="M13">
-        <v>28.848215</v>
+        <v>28.0614455</v>
       </c>
       <c r="N13">
-        <v>198.151785</v>
+        <v>198.9385545</v>
       </c>
       <c r="O13">
-        <v>49.419055179</v>
+        <v>49.61527549230001</v>
       </c>
       <c r="P13">
-        <v>148.732729821</v>
+        <v>149.3232790077</v>
       </c>
       <c r="Q13">
-        <v>149.432729821</v>
+        <v>150.0232790077</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.06955416642825955</v>
+        <v>0.06953889461124174</v>
       </c>
       <c r="T13">
         <v>0.548242369774636</v>
       </c>
       <c r="U13">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.2494</v>
       </c>
       <c r="W13">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.868771083410185</v>
+        <v>8.089390833412342</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.0664800626558909</v>
+        <v>0.06626834719318307</v>
       </c>
       <c r="C14">
-        <v>4079.139098198102</v>
+        <v>4101.502272633771</v>
       </c>
       <c r="D14">
-        <v>4426.735098198102</v>
+        <v>4449.098272633771</v>
       </c>
       <c r="E14">
         <v>-540.7040000000001</v>
@@ -2441,37 +2441,37 @@
         <v>227</v>
       </c>
       <c r="M14">
-        <v>32.32907400000001</v>
+        <v>31.0702428</v>
       </c>
       <c r="N14">
-        <v>194.670926</v>
+        <v>195.9297572</v>
       </c>
       <c r="O14">
-        <v>48.55092894440001</v>
+        <v>48.86488144568</v>
       </c>
       <c r="P14">
-        <v>146.1199970556</v>
+        <v>147.06487575432</v>
       </c>
       <c r="Q14">
-        <v>146.8199970556</v>
+        <v>147.76487575432</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.06976249392714876</v>
+        <v>0.06974708817407167</v>
       </c>
       <c r="T14">
         <v>0.55305053519796</v>
       </c>
       <c r="U14">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.2494</v>
       </c>
       <c r="W14">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.021543518382246</v>
+        <v>7.306025944541378</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06639193819063081</v>
+        <v>0.06616374438236099</v>
       </c>
       <c r="C15">
-        <v>4041.35428740349</v>
+        <v>4065.692597909636</v>
       </c>
       <c r="D15">
-        <v>4436.63328740349</v>
+        <v>4460.971597909635</v>
       </c>
       <c r="E15">
         <v>-493.0210000000001</v>
@@ -2523,37 +2523,37 @@
         <v>227</v>
       </c>
       <c r="M15">
-        <v>35.0231635</v>
+        <v>33.6594297</v>
       </c>
       <c r="N15">
-        <v>191.9768365</v>
+        <v>193.3405703</v>
       </c>
       <c r="O15">
-        <v>47.8790230231</v>
+        <v>48.21913823282</v>
       </c>
       <c r="P15">
-        <v>144.0978134769</v>
+        <v>145.12143206718</v>
       </c>
       <c r="Q15">
-        <v>144.7978134769</v>
+        <v>145.82143206718</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.06997561056394347</v>
+        <v>0.06996006779581723</v>
       </c>
       <c r="T15">
         <v>0.5579692331597512</v>
       </c>
       <c r="U15">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.2494</v>
       </c>
       <c r="W15">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.481424786198996</v>
+        <v>6.744023948807427</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06645093132537072</v>
+        <v>0.06605914157153892</v>
       </c>
       <c r="C16">
-        <v>3987.040255096876</v>
+        <v>4029.946465536756</v>
       </c>
       <c r="D16">
-        <v>4430.002255096875</v>
+        <v>4472.908465536756</v>
       </c>
       <c r="E16">
         <v>-445.338</v>
@@ -2605,45 +2605,45 @@
         <v>227</v>
       </c>
       <c r="M16">
-        <v>38.6518398</v>
+        <v>36.24861660000001</v>
       </c>
       <c r="N16">
-        <v>188.3481602</v>
+        <v>190.7513834</v>
       </c>
       <c r="O16">
-        <v>46.97403115388</v>
+        <v>47.57339501996</v>
       </c>
       <c r="P16">
-        <v>141.37412904612</v>
+        <v>143.17798838004</v>
       </c>
       <c r="Q16">
-        <v>142.07412904612</v>
+        <v>143.87798838004</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07019368340159386</v>
+        <v>0.07017800043202199</v>
       </c>
       <c r="T16">
         <v>0.5630023194462351</v>
       </c>
       <c r="U16">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.2494</v>
       </c>
       <c r="W16">
-        <v>0.04345974</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>5.872941654901508</v>
+        <v>6.262307952464039</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06637331526011062</v>
+        <v>0.06606712876071681</v>
       </c>
       <c r="C17">
-        <v>3948.085693576025</v>
+        <v>3981.349746190414</v>
       </c>
       <c r="D17">
-        <v>4438.730693576024</v>
+        <v>4471.994746190414</v>
       </c>
       <c r="E17">
         <v>-397.6550000000001</v>
@@ -2687,37 +2687,37 @@
         <v>227</v>
       </c>
       <c r="M17">
-        <v>41.4126855</v>
+        <v>39.5530485</v>
       </c>
       <c r="N17">
-        <v>185.5873145</v>
+        <v>187.4469515</v>
       </c>
       <c r="O17">
-        <v>46.2854762363</v>
+        <v>46.7492697041</v>
       </c>
       <c r="P17">
-        <v>139.3018382637</v>
+        <v>140.6976817959</v>
       </c>
       <c r="Q17">
-        <v>140.0018382637</v>
+        <v>141.3976817959</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07041688736483602</v>
+        <v>0.07040106089496097</v>
       </c>
       <c r="T17">
         <v>0.568153831292401</v>
       </c>
       <c r="U17">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.2494</v>
       </c>
       <c r="W17">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.481412211241408</v>
+        <v>5.739127794410082</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06629569919485052</v>
+        <v>0.06597003194989474</v>
       </c>
       <c r="C18">
-        <v>3909.165595262584</v>
+        <v>3944.79981581993</v>
       </c>
       <c r="D18">
-        <v>4447.493595262584</v>
+        <v>4483.127815819929</v>
       </c>
       <c r="E18">
         <v>-349.9720000000001</v>
@@ -2769,37 +2769,37 @@
         <v>227</v>
       </c>
       <c r="M18">
-        <v>44.1735312</v>
+        <v>42.1899184</v>
       </c>
       <c r="N18">
-        <v>182.8264688</v>
+        <v>184.8100816</v>
       </c>
       <c r="O18">
-        <v>45.59692131872</v>
+        <v>46.09163435104</v>
       </c>
       <c r="P18">
-        <v>137.22954748128</v>
+        <v>138.71844724896</v>
       </c>
       <c r="Q18">
-        <v>137.92954748128</v>
+        <v>139.41844724896</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07064540570815539</v>
+        <v>0.07062943232130327</v>
       </c>
       <c r="T18">
         <v>0.5734279981825233</v>
       </c>
       <c r="U18">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.2494</v>
       </c>
       <c r="W18">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.13882394803882</v>
+        <v>5.380432307259452</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06621808312959043</v>
+        <v>0.06587293513907266</v>
       </c>
       <c r="C19">
-        <v>3870.280164671158</v>
+        <v>3908.305455538081</v>
       </c>
       <c r="D19">
-        <v>4456.291164671157</v>
+        <v>4494.316455538081</v>
       </c>
       <c r="E19">
         <v>-302.289</v>
@@ -2851,37 +2851,37 @@
         <v>227</v>
       </c>
       <c r="M19">
-        <v>46.9343769</v>
+        <v>44.8267883</v>
       </c>
       <c r="N19">
-        <v>180.0656231</v>
+        <v>182.1732117</v>
       </c>
       <c r="O19">
-        <v>44.90836640114</v>
+        <v>45.43399899798</v>
       </c>
       <c r="P19">
-        <v>135.15725669886</v>
+        <v>136.73921270202</v>
       </c>
       <c r="Q19">
-        <v>135.85725669886</v>
+        <v>137.43921270202</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07087943051757883</v>
+        <v>0.07086330667358152</v>
       </c>
       <c r="T19">
         <v>0.5788292534314439</v>
       </c>
       <c r="U19">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.836540186389477</v>
+        <v>5.063936289185366</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06614046706433034</v>
+        <v>0.0657758383282506</v>
       </c>
       <c r="C20">
-        <v>3831.42960793775</v>
+        <v>3871.867082448281</v>
       </c>
       <c r="D20">
-        <v>4465.12360793775</v>
+        <v>4505.56108244828</v>
       </c>
       <c r="E20">
         <v>-254.6060000000001</v>
@@ -2933,37 +2933,37 @@
         <v>227</v>
       </c>
       <c r="M20">
-        <v>49.6952226</v>
+        <v>47.4636582</v>
       </c>
       <c r="N20">
-        <v>177.3047774</v>
+        <v>179.5363418</v>
       </c>
       <c r="O20">
-        <v>44.21981148356</v>
+        <v>44.77636364492</v>
       </c>
       <c r="P20">
-        <v>133.08496591644</v>
+        <v>134.75997815508</v>
       </c>
       <c r="Q20">
-        <v>133.78496591644</v>
+        <v>135.45997815508</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07111916324918334</v>
+        <v>0.07110288527835437</v>
       </c>
       <c r="T20">
         <v>0.5843622466132647</v>
       </c>
       <c r="U20">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.2494</v>
       </c>
       <c r="W20">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.56784350936784</v>
+        <v>4.782606495341735</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06643364739907023</v>
+        <v>0.0656787415174285</v>
       </c>
       <c r="C21">
-        <v>3750.565974312378</v>
+        <v>3835.485117838731</v>
       </c>
       <c r="D21">
-        <v>4431.942974312377</v>
+        <v>4516.86211783873</v>
       </c>
       <c r="E21">
         <v>-206.923</v>
@@ -3015,45 +3015,45 @@
         <v>227</v>
       </c>
       <c r="M21">
-        <v>54.81160850000001</v>
+        <v>50.10052810000001</v>
       </c>
       <c r="N21">
-        <v>172.1883915</v>
+        <v>176.8994719</v>
       </c>
       <c r="O21">
-        <v>42.9437848401</v>
+        <v>44.11872829185999</v>
       </c>
       <c r="P21">
-        <v>129.2446066599</v>
+        <v>132.78074360814</v>
       </c>
       <c r="Q21">
-        <v>129.9446066599</v>
+        <v>133.48074360814</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07136481530749411</v>
+        <v>0.07134837940423271</v>
       </c>
       <c r="T21">
         <v>0.590031856910686</v>
       </c>
       <c r="U21">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.04541129999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.141458464952729</v>
+        <v>4.530890364007959</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06678087093381016</v>
+        <v>0.06595694470660643</v>
       </c>
       <c r="C22">
-        <v>3664.218311850104</v>
+        <v>3755.5726329409</v>
       </c>
       <c r="D22">
-        <v>4393.278311850104</v>
+        <v>4484.632632940899</v>
       </c>
       <c r="E22">
         <v>-159.24</v>
@@ -3097,45 +3097,45 @@
         <v>227</v>
       </c>
       <c r="M22">
-        <v>60.27131200000001</v>
+        <v>55.12154800000001</v>
       </c>
       <c r="N22">
-        <v>166.728688</v>
+        <v>171.878452</v>
       </c>
       <c r="O22">
-        <v>41.5821347872</v>
+        <v>42.8664859288</v>
       </c>
       <c r="P22">
-        <v>125.1465532128</v>
+        <v>129.0119660712</v>
       </c>
       <c r="Q22">
-        <v>125.8465532128</v>
+        <v>129.7119660712</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07161660866726269</v>
+        <v>0.07160001088325803</v>
       </c>
       <c r="T22">
         <v>0.5958432074655432</v>
       </c>
       <c r="U22">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.2494</v>
       </c>
       <c r="W22">
-        <v>0.04743792</v>
+        <v>0.04338468</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.766302615081615</v>
+        <v>4.118171717528687</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06674303666855005</v>
+        <v>0.06643030389578433</v>
       </c>
       <c r="C23">
-        <v>3620.715520519655</v>
+        <v>3654.095959165703</v>
       </c>
       <c r="D23">
-        <v>4397.458520519654</v>
+        <v>4430.838959165702</v>
       </c>
       <c r="E23">
         <v>-111.5570000000001</v>
@@ -3179,37 +3179,37 @@
         <v>227</v>
       </c>
       <c r="M23">
-        <v>63.2848776</v>
+        <v>61.3823259</v>
       </c>
       <c r="N23">
-        <v>163.7151224</v>
+        <v>165.6176741</v>
       </c>
       <c r="O23">
-        <v>40.83055152656</v>
+        <v>41.30504792054</v>
       </c>
       <c r="P23">
-        <v>122.88457087344</v>
+        <v>124.31262617946</v>
       </c>
       <c r="Q23">
-        <v>123.58457087344</v>
+        <v>125.01262617946</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07187477654246842</v>
+        <v>0.07185801277947385</v>
       </c>
       <c r="T23">
         <v>0.6018016808192572</v>
       </c>
       <c r="U23">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.2494</v>
       </c>
       <c r="W23">
-        <v>0.04743792</v>
+        <v>0.04601178</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.586954871506301</v>
+        <v>3.698132918094588</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06748132280328996</v>
+        <v>0.06637824308496226</v>
       </c>
       <c r="C24">
-        <v>3492.871972606079</v>
+        <v>3612.266029338914</v>
       </c>
       <c r="D24">
-        <v>4317.297972606078</v>
+        <v>4436.692029338913</v>
       </c>
       <c r="E24">
         <v>-63.87400000000002</v>
@@ -3261,45 +3261,45 @@
         <v>227</v>
       </c>
       <c r="M24">
-        <v>71.2288654</v>
+        <v>64.3052938</v>
       </c>
       <c r="N24">
-        <v>155.7711346</v>
+        <v>162.6947062</v>
       </c>
       <c r="O24">
-        <v>38.84932096924</v>
+        <v>40.57605972628</v>
       </c>
       <c r="P24">
-        <v>116.92181363076</v>
+        <v>122.11864647372</v>
       </c>
       <c r="Q24">
-        <v>117.62181363076</v>
+        <v>122.81864647372</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07213956410678199</v>
+        <v>0.07212263010892597</v>
       </c>
       <c r="T24">
         <v>0.6079129355410153</v>
       </c>
       <c r="U24">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.05096574</v>
+        <v>0.04601178</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.186910232603536</v>
+        <v>3.530035967272106</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06747876673802986</v>
+        <v>0.06680956867414017</v>
       </c>
       <c r="C25">
-        <v>3445.461459478759</v>
+        <v>3516.551758991377</v>
       </c>
       <c r="D25">
-        <v>4317.570459478758</v>
+        <v>4388.660758991376</v>
       </c>
       <c r="E25">
         <v>-16.19100000000003</v>
@@ -3343,37 +3343,37 @@
         <v>227</v>
       </c>
       <c r="M25">
-        <v>74.4665411</v>
+        <v>70.29904690000001</v>
       </c>
       <c r="N25">
-        <v>152.5334589</v>
+        <v>156.7009531</v>
       </c>
       <c r="O25">
-        <v>38.04184464966</v>
+        <v>39.08121770314</v>
       </c>
       <c r="P25">
-        <v>114.49161425034</v>
+        <v>117.61973539686</v>
       </c>
       <c r="Q25">
-        <v>115.19161425034</v>
+        <v>118.31973539686</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07241122927016864</v>
+        <v>0.07239412061576646</v>
       </c>
       <c r="T25">
         <v>0.6141829241516502</v>
       </c>
       <c r="U25">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.2494</v>
       </c>
       <c r="W25">
-        <v>0.05096574</v>
+        <v>0.04811346</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.048348918142513</v>
+        <v>3.229062270544097</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06915154987276977</v>
+        <v>0.06677852466331809</v>
       </c>
       <c r="C26">
-        <v>3226.515754958617</v>
+        <v>3472.290979016546</v>
       </c>
       <c r="D26">
-        <v>4146.307754958617</v>
+        <v>4392.082979016545</v>
       </c>
       <c r="E26">
         <v>31.49199999999996</v>
@@ -3425,45 +3425,45 @@
         <v>227</v>
       </c>
       <c r="M26">
-        <v>88.3470624</v>
+        <v>73.35552720000001</v>
       </c>
       <c r="N26">
-        <v>138.6529376</v>
+        <v>153.6444728</v>
       </c>
       <c r="O26">
-        <v>34.58004263744</v>
+        <v>38.31893151632</v>
       </c>
       <c r="P26">
-        <v>104.07289496256</v>
+        <v>115.32554128368</v>
       </c>
       <c r="Q26">
-        <v>104.77289496256</v>
+        <v>116.02554128368</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07269004351680232</v>
+        <v>0.07267275560962906</v>
       </c>
       <c r="T26">
         <v>0.6206179124625649</v>
       </c>
       <c r="U26">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.05794631999999999</v>
+        <v>0.04811346</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.56941197401941</v>
+        <v>3.094518009271426</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07010075460750967</v>
+        <v>0.068211150652496</v>
       </c>
       <c r="C27">
-        <v>3087.560602911222</v>
+        <v>3272.04552758392</v>
       </c>
       <c r="D27">
-        <v>4055.035602911222</v>
+        <v>4239.52052758392</v>
       </c>
       <c r="E27">
         <v>79.17499999999995</v>
@@ -3507,45 +3507,45 @@
         <v>227</v>
       </c>
       <c r="M27">
-        <v>97.6309425</v>
+        <v>85.71019250000001</v>
       </c>
       <c r="N27">
-        <v>129.3690575</v>
+        <v>141.2898075</v>
       </c>
       <c r="O27">
-        <v>32.2646429405</v>
+        <v>35.2376779905</v>
       </c>
       <c r="P27">
-        <v>97.10441455949999</v>
+        <v>106.0521295095</v>
       </c>
       <c r="Q27">
-        <v>97.80441455949997</v>
+        <v>106.7521295095</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07297629281001289</v>
+        <v>0.07295882086999467</v>
       </c>
       <c r="T27">
         <v>0.6272245004617707</v>
       </c>
       <c r="U27">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0.2494</v>
       </c>
       <c r="W27">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.325082542350751</v>
+        <v>2.64845980832443</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07020328254224957</v>
+        <v>0.06823865344167393</v>
       </c>
       <c r="C28">
-        <v>3030.258770886615</v>
+        <v>3221.537333613426</v>
       </c>
       <c r="D28">
-        <v>4045.416770886615</v>
+        <v>4236.695333613426</v>
       </c>
       <c r="E28">
         <v>126.8579999999999</v>
@@ -3589,45 +3589,45 @@
         <v>227</v>
       </c>
       <c r="M28">
-        <v>101.5361802</v>
+        <v>89.13860020000001</v>
       </c>
       <c r="N28">
-        <v>125.4638198</v>
+        <v>137.8613998</v>
       </c>
       <c r="O28">
-        <v>31.29067665812</v>
+        <v>34.38263311012</v>
       </c>
       <c r="P28">
-        <v>94.17314314187999</v>
+        <v>103.47876668988</v>
       </c>
       <c r="Q28">
-        <v>94.87314314187998</v>
+        <v>104.17876668988</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07327027857060753</v>
+        <v>0.07325261762388369</v>
       </c>
       <c r="T28">
         <v>0.6340096448933875</v>
       </c>
       <c r="U28">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V28">
         <v>0.2494</v>
       </c>
       <c r="W28">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.235656290721876</v>
+        <v>2.546595969542721</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07030581047698947</v>
+        <v>0.06905653803085185</v>
       </c>
       <c r="C29">
-        <v>2973.002463976627</v>
+        <v>3091.525563464957</v>
       </c>
       <c r="D29">
-        <v>4035.843463976626</v>
+        <v>4154.366563464957</v>
       </c>
       <c r="E29">
         <v>174.5409999999999</v>
@@ -3671,37 +3671,37 @@
         <v>227</v>
       </c>
       <c r="M29">
-        <v>105.4414179</v>
+        <v>97.58802780000001</v>
       </c>
       <c r="N29">
-        <v>121.5585821</v>
+        <v>129.4119722</v>
       </c>
       <c r="O29">
-        <v>30.31671037574</v>
+        <v>32.27534586668</v>
       </c>
       <c r="P29">
-        <v>91.24187172425999</v>
+        <v>97.13662633331998</v>
       </c>
       <c r="Q29">
-        <v>91.94187172425998</v>
+        <v>97.83662633331997</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07357231873560202</v>
+        <v>0.07355446360390663</v>
       </c>
       <c r="T29">
         <v>0.6409806836929938</v>
       </c>
       <c r="U29">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.152854205880325</v>
+        <v>2.326105006089692</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07040833841172937</v>
+        <v>0.06911331422002975</v>
       </c>
       <c r="C30">
-        <v>2915.791359744541</v>
+        <v>3038.246044610336</v>
       </c>
       <c r="D30">
-        <v>4026.315359744541</v>
+        <v>4148.770044610335</v>
       </c>
       <c r="E30">
         <v>222.2240000000002</v>
@@ -3753,37 +3753,37 @@
         <v>227</v>
       </c>
       <c r="M30">
-        <v>109.3466556</v>
+        <v>101.2023992</v>
       </c>
       <c r="N30">
-        <v>117.6533444</v>
+        <v>125.7976008</v>
       </c>
       <c r="O30">
-        <v>29.34274409336</v>
+        <v>31.37392163952</v>
       </c>
       <c r="P30">
-        <v>88.31060030663998</v>
+        <v>94.42367916047998</v>
       </c>
       <c r="Q30">
-        <v>89.01060030663997</v>
+        <v>95.12367916047997</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07388274890517968</v>
+        <v>0.07386469419448578</v>
       </c>
       <c r="T30">
         <v>0.6481453624592558</v>
       </c>
       <c r="U30">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.2494</v>
       </c>
       <c r="W30">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.075966555670313</v>
+        <v>2.243029827300774</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07051086634646928</v>
+        <v>0.06917009040920767</v>
       </c>
       <c r="C31">
-        <v>2858.625138791396</v>
+        <v>2984.981584073622</v>
       </c>
       <c r="D31">
-        <v>4016.832138791396</v>
+        <v>4143.188584073621</v>
       </c>
       <c r="E31">
         <v>269.9069999999999</v>
@@ -3835,37 +3835,37 @@
         <v>227</v>
       </c>
       <c r="M31">
-        <v>113.2518933</v>
+        <v>104.8167706</v>
       </c>
       <c r="N31">
-        <v>113.7481067</v>
+        <v>122.1832294</v>
       </c>
       <c r="O31">
-        <v>28.36877781098</v>
+        <v>30.47249741236</v>
       </c>
       <c r="P31">
-        <v>85.37932888902</v>
+        <v>91.71073198763999</v>
       </c>
       <c r="Q31">
-        <v>86.07932888901999</v>
+        <v>92.41073198763998</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07420192358657644</v>
+        <v>0.07418366367494039</v>
       </c>
       <c r="T31">
         <v>0.6555118631625956</v>
       </c>
       <c r="U31">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.2494</v>
       </c>
       <c r="W31">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.00438150202651</v>
+        <v>2.165683971186954</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07428382828120919</v>
+        <v>0.06922686659838559</v>
       </c>
       <c r="C32">
-        <v>2490.556717145195</v>
+        <v>2931.732121161295</v>
       </c>
       <c r="D32">
-        <v>3696.446717145195</v>
+        <v>4137.622121161295</v>
       </c>
       <c r="E32">
         <v>317.5899999999999</v>
@@ -3917,45 +3917,45 @@
         <v>227</v>
       </c>
       <c r="M32">
-        <v>140.474118</v>
+        <v>108.431142</v>
       </c>
       <c r="N32">
-        <v>86.525882</v>
+        <v>118.568858</v>
       </c>
       <c r="O32">
-        <v>21.5795549708</v>
+        <v>29.5710731852</v>
       </c>
       <c r="P32">
-        <v>64.94632702919999</v>
+        <v>88.99778481479999</v>
       </c>
       <c r="Q32">
-        <v>65.64632702919998</v>
+        <v>89.69778481479997</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07453021754458455</v>
+        <v>0.07451174656912228</v>
       </c>
       <c r="T32">
         <v>0.6630888353146023</v>
       </c>
       <c r="U32">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.2494</v>
       </c>
       <c r="W32">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.615956043945405</v>
+        <v>2.093494505480722</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07450870401594908</v>
+        <v>0.06928364278756351</v>
       </c>
       <c r="C33">
-        <v>2425.384354280662</v>
+        <v>2878.497595505568</v>
       </c>
       <c r="D33">
-        <v>3678.957354280662</v>
+        <v>4132.070595505567</v>
       </c>
       <c r="E33">
         <v>365.2729999999999</v>
@@ -3999,45 +3999,45 @@
         <v>227</v>
       </c>
       <c r="M33">
-        <v>145.1565886</v>
+        <v>112.0455134</v>
       </c>
       <c r="N33">
-        <v>81.84341139999998</v>
+        <v>114.9544866</v>
       </c>
       <c r="O33">
-        <v>20.41174680316</v>
+        <v>28.66964895804</v>
       </c>
       <c r="P33">
-        <v>61.43166459683998</v>
+        <v>86.28483764196</v>
       </c>
       <c r="Q33">
-        <v>62.13166459683997</v>
+        <v>86.98483764195998</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07486802726949143</v>
+        <v>0.07484933911241089</v>
       </c>
       <c r="T33">
         <v>0.6708854298478265</v>
       </c>
       <c r="U33">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
         <v>0.2494</v>
       </c>
       <c r="W33">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.563828429624585</v>
+        <v>2.025962424658764</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07473357975068899</v>
+        <v>0.07275114537674143</v>
       </c>
       <c r="C34">
-        <v>2360.376710359489</v>
+        <v>2517.864264385772</v>
       </c>
       <c r="D34">
-        <v>3661.632710359489</v>
+        <v>3819.120264385772</v>
       </c>
       <c r="E34">
         <v>412.9559999999999</v>
@@ -4081,37 +4081,37 @@
         <v>227</v>
       </c>
       <c r="M34">
-        <v>149.8390592</v>
+        <v>137.32704</v>
       </c>
       <c r="N34">
-        <v>77.16094079999999</v>
+        <v>89.67296000000002</v>
       </c>
       <c r="O34">
-        <v>19.24393863552</v>
+        <v>22.36443622400001</v>
       </c>
       <c r="P34">
-        <v>57.91700216448</v>
+        <v>67.30852377600002</v>
       </c>
       <c r="Q34">
-        <v>58.61700216447998</v>
+        <v>68.008523776</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07521577257454264</v>
+        <v>0.07519686084814917</v>
       </c>
       <c r="T34">
         <v>0.6789113359849691</v>
       </c>
       <c r="U34">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V34">
         <v>0.2494</v>
       </c>
       <c r="W34">
-        <v>0.07370892</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.514958791198817</v>
+        <v>1.652988369952487</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09296104264005373</v>
+        <v>0.07291450676591935</v>
       </c>
       <c r="C35">
-        <v>1301.151691913071</v>
+        <v>2456.602608537588</v>
       </c>
       <c r="D35">
-        <v>2650.090691913072</v>
+        <v>3805.541608537589</v>
       </c>
       <c r="E35">
         <v>460.6390000000001</v>
@@ -4163,45 +4163,45 @@
         <v>227</v>
       </c>
       <c r="M35">
-        <v>257.4309804</v>
+        <v>141.61851</v>
       </c>
       <c r="N35">
-        <v>-30.43098040000001</v>
+        <v>85.38148999999999</v>
       </c>
       <c r="O35">
-        <v>-7.589486511760003</v>
+        <v>21.294143606</v>
       </c>
       <c r="P35">
-        <v>-22.84149388824001</v>
+        <v>64.08734639399998</v>
       </c>
       <c r="Q35">
-        <v>-22.14149388824002</v>
+        <v>64.78734639399997</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07588954517116246</v>
+        <v>0.07555475636704381</v>
       </c>
       <c r="T35">
-        <v>0.6944618999744767</v>
+        <v>0.6871768214097876</v>
       </c>
       <c r="U35">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V35">
-        <v>0.2199183637961237</v>
+        <v>0.2494</v>
       </c>
       <c r="W35">
-        <v>0.1276213556829542</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8817897505859011</v>
+        <v>1.60289781328726</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09413904264005371</v>
+        <v>0.07307786815509726</v>
       </c>
       <c r="C36">
-        <v>1206.984681093579</v>
+        <v>2395.437166818655</v>
       </c>
       <c r="D36">
-        <v>2603.606681093579</v>
+        <v>3792.059166818656</v>
       </c>
       <c r="E36">
         <v>508.3220000000001</v>
@@ -4245,45 +4245,45 @@
         <v>227</v>
       </c>
       <c r="M36">
-        <v>265.2319192</v>
+        <v>145.90998</v>
       </c>
       <c r="N36">
-        <v>-38.23191920000005</v>
+        <v>81.09001999999998</v>
       </c>
       <c r="O36">
-        <v>-9.535040648480013</v>
+        <v>20.223850988</v>
       </c>
       <c r="P36">
-        <v>-28.69687855152004</v>
+        <v>60.86616901199999</v>
       </c>
       <c r="Q36">
-        <v>-27.99687855152005</v>
+        <v>61.56616901199997</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.07634544737072552</v>
+        <v>0.07592349720469282</v>
       </c>
       <c r="T36">
-        <v>0.7049840499740899</v>
+        <v>0.6956927760899037</v>
       </c>
       <c r="U36">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
-        <v>0.2134501766256495</v>
+        <v>0.2494</v>
       </c>
       <c r="W36">
-        <v>0.1286795511040437</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.8558547579216098</v>
+        <v>1.555753759955282</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09531704264005371</v>
+        <v>0.07324122954427519</v>
       </c>
       <c r="C37">
-        <v>1114.420268755542</v>
+        <v>2334.366920224084</v>
       </c>
       <c r="D37">
-        <v>2558.725268755542</v>
+        <v>3778.671920224084</v>
       </c>
       <c r="E37">
         <v>556.0050000000001</v>
@@ -4327,45 +4327,45 @@
         <v>227</v>
       </c>
       <c r="M37">
-        <v>273.032858</v>
+        <v>150.20145</v>
       </c>
       <c r="N37">
-        <v>-46.03285800000003</v>
+        <v>76.79854999999998</v>
       </c>
       <c r="O37">
-        <v>-11.48059478520001</v>
+        <v>19.15355837</v>
       </c>
       <c r="P37">
-        <v>-34.55226321480002</v>
+        <v>57.64499162999998</v>
       </c>
       <c r="Q37">
-        <v>-33.85226321480003</v>
+        <v>58.34499162999997</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.07681537733027514</v>
+        <v>0.07630358391426953</v>
       </c>
       <c r="T37">
-        <v>0.7158299584352298</v>
+        <v>0.7044707601447926</v>
       </c>
       <c r="U37">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V37">
-        <v>0.2073516001506309</v>
+        <v>0.2494</v>
       </c>
       <c r="W37">
-        <v>0.1296772782153568</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.8314017648381352</v>
+        <v>1.511303652527988</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09649504264005371</v>
+        <v>0.09025365931247906</v>
       </c>
       <c r="C38">
-        <v>1023.376981755734</v>
+        <v>1270.908495818974</v>
       </c>
       <c r="D38">
-        <v>2515.364981755734</v>
+        <v>2762.896495818974</v>
       </c>
       <c r="E38">
         <v>603.6879999999999</v>
@@ -4409,37 +4409,37 @@
         <v>227</v>
       </c>
       <c r="M38">
-        <v>280.8337968</v>
+        <v>251.9951184</v>
       </c>
       <c r="N38">
-        <v>-53.83379679999996</v>
+        <v>-24.99511840000002</v>
       </c>
       <c r="O38">
-        <v>-13.42614892191999</v>
+        <v>-6.233782528960006</v>
       </c>
       <c r="P38">
-        <v>-40.40764787807997</v>
+        <v>-18.76133587104002</v>
       </c>
       <c r="Q38">
-        <v>-39.70764787807998</v>
+        <v>-18.06133587104003</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.07729999260106069</v>
+        <v>0.07699783115172529</v>
       </c>
       <c r="T38">
-        <v>0.7270148015357802</v>
+        <v>0.7205041836426164</v>
       </c>
       <c r="U38">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.2015918334797801</v>
+        <v>0.2246622885374116</v>
       </c>
       <c r="W38">
-        <v>0.130619576042708</v>
+        <v>0.113819576042708</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8083072713704095</v>
+        <v>0.900811100791546</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1173686398729555</v>
+        <v>0.09126365931247907</v>
       </c>
       <c r="C39">
-        <v>394.8145602635179</v>
+        <v>1179.824284224287</v>
       </c>
       <c r="D39">
-        <v>1934.485560263518</v>
+        <v>2719.495284224287</v>
       </c>
       <c r="E39">
         <v>651.3709999999999</v>
@@ -4491,45 +4491,45 @@
         <v>227</v>
       </c>
       <c r="M39">
-        <v>380.7296818</v>
+        <v>258.9949828</v>
       </c>
       <c r="N39">
-        <v>-153.7296818</v>
+        <v>-31.9949828</v>
       </c>
       <c r="O39">
-        <v>-38.34018264092001</v>
+        <v>-7.979548710320001</v>
       </c>
       <c r="P39">
-        <v>-115.38949915908</v>
+        <v>-24.01543408968</v>
       </c>
       <c r="Q39">
-        <v>-114.68949915908</v>
+        <v>-23.31543408968001</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.07840570237711203</v>
+        <v>0.07749303482080029</v>
       </c>
       <c r="T39">
-        <v>0.7525344066853087</v>
+        <v>0.7319407579861499</v>
       </c>
       <c r="U39">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.1486981517499327</v>
+        <v>0.2185903347931572</v>
       </c>
       <c r="W39">
-        <v>0.1837109388523645</v>
+        <v>0.1147109388523645</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.5962235435041408</v>
+        <v>0.876464854824207</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1190686398729555</v>
+        <v>0.09227365931247905</v>
       </c>
       <c r="C40">
-        <v>311.4199149406218</v>
+        <v>1090.082528323387</v>
       </c>
       <c r="D40">
-        <v>1898.773914940622</v>
+        <v>2677.436528323387</v>
       </c>
       <c r="E40">
         <v>699.0540000000001</v>
@@ -4573,45 +4573,45 @@
         <v>227</v>
       </c>
       <c r="M40">
-        <v>391.0196732000001</v>
+        <v>265.9948472</v>
       </c>
       <c r="N40">
-        <v>-164.0196732000001</v>
+        <v>-38.99484720000004</v>
       </c>
       <c r="O40">
-        <v>-40.90650649608001</v>
+        <v>-9.725314891680011</v>
       </c>
       <c r="P40">
-        <v>-123.11316670392</v>
+        <v>-29.26953230832003</v>
       </c>
       <c r="Q40">
-        <v>-122.4131667039201</v>
+        <v>-28.56953230832004</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.07893160080254932</v>
+        <v>0.07800421280178094</v>
       </c>
       <c r="T40">
-        <v>0.7646720584060394</v>
+        <v>0.7437462540827007</v>
       </c>
       <c r="U40">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1447850424933555</v>
+        <v>0.2128379575617584</v>
       </c>
       <c r="W40">
-        <v>0.1845553878299339</v>
+        <v>0.1155553878299339</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.5805334502540318</v>
+        <v>0.8533999902235698</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1207686398729555</v>
+        <v>0.09328365931247906</v>
       </c>
       <c r="C41">
-        <v>229.3198827742685</v>
+        <v>1001.6218908958</v>
       </c>
       <c r="D41">
-        <v>1864.356882774269</v>
+        <v>2636.658890895801</v>
       </c>
       <c r="E41">
         <v>746.7370000000001</v>
@@ -4655,45 +4655,45 @@
         <v>227</v>
       </c>
       <c r="M41">
-        <v>401.3096646000001</v>
+        <v>272.9947116000001</v>
       </c>
       <c r="N41">
-        <v>-174.3096646000001</v>
+        <v>-45.99471160000007</v>
       </c>
       <c r="O41">
-        <v>-43.47283035124002</v>
+        <v>-11.47108107304002</v>
       </c>
       <c r="P41">
-        <v>-130.8368342487601</v>
+        <v>-34.52363052696005</v>
       </c>
       <c r="Q41">
-        <v>-130.1368342487601</v>
+        <v>-33.82363052696007</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.07947474179931244</v>
+        <v>0.07853215071656425</v>
       </c>
       <c r="T41">
-        <v>0.7772076659208926</v>
+        <v>0.7559388156250401</v>
       </c>
       <c r="U41">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.1410726055063464</v>
+        <v>0.2073805740345337</v>
       </c>
       <c r="W41">
-        <v>0.1853565317317305</v>
+        <v>0.1163565317317305</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.5656479771705951</v>
+        <v>0.8315179391921962</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1224686398729554</v>
+        <v>0.09429365931247906</v>
       </c>
       <c r="C42">
-        <v>148.4453188989946</v>
+        <v>914.384715353689</v>
       </c>
       <c r="D42">
-        <v>1831.165318898995</v>
+        <v>2597.104715353689</v>
       </c>
       <c r="E42">
         <v>794.4200000000001</v>
@@ -4737,45 +4737,45 @@
         <v>227</v>
       </c>
       <c r="M42">
-        <v>411.5996560000001</v>
+        <v>279.9945760000001</v>
       </c>
       <c r="N42">
-        <v>-184.5996560000001</v>
+        <v>-52.99457600000005</v>
       </c>
       <c r="O42">
-        <v>-46.03915420640003</v>
+        <v>-13.21684725440001</v>
       </c>
       <c r="P42">
-        <v>-138.5605017936001</v>
+        <v>-39.77772874560004</v>
       </c>
       <c r="Q42">
-        <v>-137.8605017936001</v>
+        <v>-39.07772874560005</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08003598749596763</v>
+        <v>0.0790776865618403</v>
       </c>
       <c r="T42">
-        <v>0.790161127019574</v>
+        <v>0.7685377958854575</v>
       </c>
       <c r="U42">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1375457903686877</v>
+        <v>0.2021960596836704</v>
       </c>
       <c r="W42">
-        <v>0.1861176184384372</v>
+        <v>0.1171176184384372</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.5515067777413302</v>
+        <v>0.8107299907123914</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1241686398729555</v>
+        <v>0.1179161509720457</v>
       </c>
       <c r="C43">
-        <v>68.73191632574799</v>
+        <v>192.1433436039538</v>
       </c>
       <c r="D43">
-        <v>1799.134916325748</v>
+        <v>1922.546343603954</v>
       </c>
       <c r="E43">
         <v>842.1030000000001</v>
@@ -4819,37 +4819,37 @@
         <v>227</v>
       </c>
       <c r="M43">
-        <v>421.8896474000001</v>
+        <v>392.5646024000001</v>
       </c>
       <c r="N43">
-        <v>-194.8896474000001</v>
+        <v>-165.5646024000001</v>
       </c>
       <c r="O43">
-        <v>-48.60547806156001</v>
+        <v>-41.29181183856002</v>
       </c>
       <c r="P43">
-        <v>-146.2841693384401</v>
+        <v>-124.27279056144</v>
       </c>
       <c r="Q43">
-        <v>-145.5841693384401</v>
+        <v>-123.5727905614401</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08061625847047556</v>
+        <v>0.08044254846893351</v>
       </c>
       <c r="T43">
-        <v>0.8035536884944821</v>
+        <v>0.8000588560954618</v>
       </c>
       <c r="U43">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1341910149938417</v>
+        <v>0.144215244201549</v>
       </c>
       <c r="W43">
-        <v>0.186841578964329</v>
+        <v>0.171841578964329</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5380553929183709</v>
+        <v>0.5782487738634683</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1258686398729555</v>
+        <v>0.1194661509720456</v>
       </c>
       <c r="C44">
-        <v>-9.880209900434238</v>
+        <v>112.2441861509517</v>
       </c>
       <c r="D44">
-        <v>1768.205790099566</v>
+        <v>1890.330186150952</v>
       </c>
       <c r="E44">
         <v>889.7859999999998</v>
@@ -4901,37 +4901,37 @@
         <v>227</v>
       </c>
       <c r="M44">
-        <v>432.1796388</v>
+        <v>402.1393488</v>
       </c>
       <c r="N44">
-        <v>-205.1796388</v>
+        <v>-175.1393488</v>
       </c>
       <c r="O44">
-        <v>-51.17180191672001</v>
+        <v>-43.67975359072</v>
       </c>
       <c r="P44">
-        <v>-154.00783688328</v>
+        <v>-131.45959520928</v>
       </c>
       <c r="Q44">
-        <v>-153.30783688328</v>
+        <v>-130.75959520928</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08121653878893204</v>
+        <v>0.08103983378736337</v>
       </c>
       <c r="T44">
-        <v>0.8174080624340421</v>
+        <v>0.8138529743040042</v>
       </c>
       <c r="U44">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1309959908273217</v>
+        <v>0.140781547911036</v>
       </c>
       <c r="W44">
-        <v>0.187531065179464</v>
+        <v>0.172531065179464</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5252445502298384</v>
+        <v>0.5644809459143383</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1275686398729555</v>
+        <v>0.1210161509720457</v>
       </c>
       <c r="C45">
-        <v>-87.44689637492252</v>
+        <v>33.40692834097399</v>
       </c>
       <c r="D45">
-        <v>1738.322103625078</v>
+        <v>1859.175928340974</v>
       </c>
       <c r="E45">
         <v>937.4690000000001</v>
@@ -4983,37 +4983,37 @@
         <v>227</v>
       </c>
       <c r="M45">
-        <v>442.4696302000001</v>
+        <v>411.7140952</v>
       </c>
       <c r="N45">
-        <v>-215.4696302000001</v>
+        <v>-184.7140952</v>
       </c>
       <c r="O45">
-        <v>-53.73812577188003</v>
+        <v>-46.06769534288001</v>
       </c>
       <c r="P45">
-        <v>-161.7315044281201</v>
+        <v>-138.64639985712</v>
       </c>
       <c r="Q45">
-        <v>-161.0315044281201</v>
+        <v>-137.94639985712</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08183788157470277</v>
+        <v>0.08165807648538731</v>
       </c>
       <c r="T45">
-        <v>0.8317485547574464</v>
+        <v>0.8281310966602148</v>
       </c>
       <c r="U45">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1279495724359886</v>
+        <v>0.1375075584247328</v>
       </c>
       <c r="W45">
-        <v>0.1881884822683137</v>
+        <v>0.1731884822683137</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5130295606896095</v>
+        <v>0.5513534820558652</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1292686398729555</v>
+        <v>0.1225661509720457</v>
       </c>
       <c r="C46">
-        <v>-164.0202677458628</v>
+        <v>-44.42008160283785</v>
       </c>
       <c r="D46">
-        <v>1709.431732254137</v>
+        <v>1829.031918397162</v>
       </c>
       <c r="E46">
         <v>985.152</v>
@@ -5065,37 +5065,37 @@
         <v>227</v>
       </c>
       <c r="M46">
-        <v>452.7596216000001</v>
+        <v>421.2888416</v>
       </c>
       <c r="N46">
-        <v>-225.7596216000001</v>
+        <v>-194.2888416</v>
       </c>
       <c r="O46">
-        <v>-56.30444962704001</v>
+        <v>-48.45563709504</v>
       </c>
       <c r="P46">
-        <v>-169.45517197296</v>
+        <v>-145.83320450496</v>
       </c>
       <c r="Q46">
-        <v>-168.7551719729601</v>
+        <v>-145.13320450496</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08248141517425103</v>
+        <v>0.08229839927976923</v>
       </c>
       <c r="T46">
-        <v>0.8466012075209721</v>
+        <v>0.8429191519577187</v>
       </c>
       <c r="U46">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.125041627607898</v>
+        <v>0.1343823866423525</v>
       </c>
       <c r="W46">
-        <v>0.1888160167622157</v>
+        <v>0.1738160167622156</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5013697979466638</v>
+        <v>0.5388227211000501</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1446146077828128</v>
+        <v>0.1241161509720456</v>
       </c>
       <c r="C47">
-        <v>-434.7069921243692</v>
+        <v>-121.2851990507522</v>
       </c>
       <c r="D47">
-        <v>1486.428007875631</v>
+        <v>1799.849800949248</v>
       </c>
       <c r="E47">
         <v>1032.835</v>
@@ -5147,45 +5147,45 @@
         <v>227</v>
       </c>
       <c r="M47">
-        <v>527.4216630000001</v>
+        <v>430.863588</v>
       </c>
       <c r="N47">
-        <v>-300.4216630000001</v>
+        <v>-203.863588</v>
       </c>
       <c r="O47">
-        <v>-74.92516275220002</v>
+        <v>-50.84357884720001</v>
       </c>
       <c r="P47">
-        <v>-225.4965002478</v>
+        <v>-153.0200091528</v>
       </c>
       <c r="Q47">
-        <v>-224.7965002478001</v>
+        <v>-152.3200091528001</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08341374619534175</v>
+        <v>0.08296200653940139</v>
       </c>
       <c r="T47">
-        <v>0.8681192586788982</v>
+        <v>0.8582449547205863</v>
       </c>
       <c r="U47">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1073406800888267</v>
+        <v>0.1313961113836336</v>
       </c>
       <c r="W47">
-        <v>0.2194156608341664</v>
+        <v>0.1744156608341664</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.4303956699632188</v>
+        <v>0.5268488828533823</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1466146077828129</v>
+        <v>0.1256661509720456</v>
       </c>
       <c r="C48">
-        <v>-507.2395235309375</v>
+        <v>-197.2337418067136</v>
       </c>
       <c r="D48">
-        <v>1461.578476469063</v>
+        <v>1771.584258193287</v>
       </c>
       <c r="E48">
         <v>1080.518</v>
@@ -5229,45 +5229,45 @@
         <v>227</v>
       </c>
       <c r="M48">
-        <v>539.1421444000001</v>
+        <v>440.4383344</v>
       </c>
       <c r="N48">
-        <v>-312.1421444000001</v>
+        <v>-213.4383344</v>
       </c>
       <c r="O48">
-        <v>-77.84825081336004</v>
+        <v>-53.23152059936001</v>
       </c>
       <c r="P48">
-        <v>-234.2938935866401</v>
+        <v>-160.20681380064</v>
       </c>
       <c r="Q48">
-        <v>-233.5938935866401</v>
+        <v>-159.50681380064</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08411029705081104</v>
+        <v>0.0836501918456866</v>
       </c>
       <c r="T48">
-        <v>0.8841955412470259</v>
+        <v>0.8741383798080046</v>
       </c>
       <c r="U48">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1050071870434175</v>
+        <v>0.1285396741796415</v>
       </c>
       <c r="W48">
-        <v>0.219989233424728</v>
+        <v>0.174989233424728</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.4210392423553226</v>
+        <v>0.5153956462696132</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1486146077828128</v>
+        <v>0.1272161509720456</v>
       </c>
       <c r="C49">
-        <v>-578.9548665719328</v>
+        <v>-272.3082249361416</v>
       </c>
       <c r="D49">
-        <v>1437.546133428067</v>
+        <v>1744.192775063859</v>
       </c>
       <c r="E49">
         <v>1128.201</v>
@@ -5311,45 +5311,45 @@
         <v>227</v>
       </c>
       <c r="M49">
-        <v>550.8626258</v>
+        <v>450.0130808</v>
       </c>
       <c r="N49">
-        <v>-323.8626258</v>
+        <v>-223.0130808</v>
       </c>
       <c r="O49">
-        <v>-80.77133887452001</v>
+        <v>-55.61946235152001</v>
       </c>
       <c r="P49">
-        <v>-243.09128692548</v>
+        <v>-167.39361844848</v>
       </c>
       <c r="Q49">
-        <v>-242.39128692548</v>
+        <v>-166.69361844848</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08483313284422256</v>
+        <v>0.08436434640881277</v>
       </c>
       <c r="T49">
-        <v>0.9008784759875359</v>
+        <v>0.890631556785514</v>
       </c>
       <c r="U49">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1027729915744086</v>
+        <v>0.1258047874949683</v>
       </c>
       <c r="W49">
-        <v>0.2205383986710104</v>
+        <v>0.1755383986710103</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.4120809606030817</v>
+        <v>0.5044297814553661</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1506146077828129</v>
+        <v>0.1457568070637471</v>
       </c>
       <c r="C50">
-        <v>-649.8926795835901</v>
+        <v>-592.2254461224488</v>
       </c>
       <c r="D50">
-        <v>1414.29132041641</v>
+        <v>1471.958553877551</v>
       </c>
       <c r="E50">
         <v>1175.884</v>
@@ -5393,37 +5393,37 @@
         <v>227</v>
       </c>
       <c r="M50">
-        <v>562.5831072000001</v>
+        <v>539.6952672000001</v>
       </c>
       <c r="N50">
-        <v>-335.5831072000001</v>
+        <v>-312.6952672000001</v>
       </c>
       <c r="O50">
-        <v>-83.69442693568003</v>
+        <v>-77.98619963968002</v>
       </c>
       <c r="P50">
-        <v>-251.88868026432</v>
+        <v>-234.7090675603201</v>
       </c>
       <c r="Q50">
-        <v>-251.1886802643201</v>
+        <v>-234.0090675603201</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.08558377001430377</v>
+        <v>0.08547261478533121</v>
       </c>
       <c r="T50">
-        <v>0.9182030620642192</v>
+        <v>0.9162266694071871</v>
       </c>
       <c r="U50">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1006318875832751</v>
+        <v>0.1048995672941858</v>
       </c>
       <c r="W50">
-        <v>0.221064682032031</v>
+        <v>0.211064682032031</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4034959405905175</v>
+        <v>0.4206077277232791</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1526146077828128</v>
+        <v>0.1476568070637471</v>
       </c>
       <c r="C51">
-        <v>-720.0900955828743</v>
+        <v>-663.0813716512173</v>
       </c>
       <c r="D51">
-        <v>1391.776904417126</v>
+        <v>1448.785628348783</v>
       </c>
       <c r="E51">
         <v>1223.567</v>
@@ -5475,37 +5475,37 @@
         <v>227</v>
       </c>
       <c r="M51">
-        <v>574.3035886</v>
+        <v>550.9389186000001</v>
       </c>
       <c r="N51">
-        <v>-347.3035886</v>
+        <v>-323.9389186000001</v>
       </c>
       <c r="O51">
-        <v>-86.61751499684</v>
+        <v>-80.79036629884003</v>
       </c>
       <c r="P51">
-        <v>-260.68607360316</v>
+        <v>-243.1485523011601</v>
       </c>
       <c r="Q51">
-        <v>-259.98607360316</v>
+        <v>-242.4485523011601</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.08636384393615286</v>
+        <v>0.08625050919288671</v>
       </c>
       <c r="T51">
-        <v>0.9362070436733215</v>
+        <v>0.9341918982190927</v>
       </c>
       <c r="U51">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.09857817559177968</v>
+        <v>0.1027587597983861</v>
       </c>
       <c r="W51">
-        <v>0.2215694844395406</v>
+        <v>0.2115694844395406</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.395261329558058</v>
+        <v>0.412023896545253</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1546146077828128</v>
+        <v>0.1495568070637471</v>
       </c>
       <c r="C52">
-        <v>-789.5819201233535</v>
+        <v>-733.2189864695786</v>
       </c>
       <c r="D52">
-        <v>1369.968079876647</v>
+        <v>1426.331013530422</v>
       </c>
       <c r="E52">
         <v>1271.25</v>
@@ -5557,37 +5557,37 @@
         <v>227</v>
       </c>
       <c r="M52">
-        <v>586.0240700000001</v>
+        <v>562.1825700000001</v>
       </c>
       <c r="N52">
-        <v>-359.0240700000001</v>
+        <v>-335.1825700000001</v>
       </c>
       <c r="O52">
-        <v>-89.54060305800002</v>
+        <v>-83.59453295800002</v>
       </c>
       <c r="P52">
-        <v>-269.4834669420001</v>
+        <v>-251.5880370420001</v>
       </c>
       <c r="Q52">
-        <v>-268.7834669420001</v>
+        <v>-250.8880370420001</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.08717512081487591</v>
+        <v>0.08705951937674446</v>
       </c>
       <c r="T52">
-        <v>0.954931184546788</v>
+        <v>0.9528757361834747</v>
       </c>
       <c r="U52">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.09660661207994409</v>
+        <v>0.1007035846024184</v>
       </c>
       <c r="W52">
-        <v>0.2220540947507498</v>
+        <v>0.2120540947507498</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3873561029668968</v>
+        <v>0.403783418614348</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1566146077828128</v>
+        <v>0.1514568070637471</v>
       </c>
       <c r="C53">
-        <v>-858.4008108359169</v>
+        <v>-802.6711799517809</v>
       </c>
       <c r="D53">
-        <v>1348.832189164083</v>
+        <v>1404.561820048219</v>
       </c>
       <c r="E53">
         <v>1318.933</v>
@@ -5639,37 +5639,37 @@
         <v>227</v>
       </c>
       <c r="M53">
-        <v>597.7445514000001</v>
+        <v>573.4262214</v>
       </c>
       <c r="N53">
-        <v>-370.7445514000001</v>
+        <v>-346.4262214</v>
       </c>
       <c r="O53">
-        <v>-92.46369111916003</v>
+        <v>-86.39869961716001</v>
       </c>
       <c r="P53">
-        <v>-278.28086028084</v>
+        <v>-260.02752178284</v>
       </c>
       <c r="Q53">
-        <v>-277.5808602808401</v>
+        <v>-259.3275217828401</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.08801951103558767</v>
+        <v>0.08790155038443312</v>
       </c>
       <c r="T53">
-        <v>0.9744195760681511</v>
+        <v>0.9723221797790557</v>
       </c>
       <c r="U53">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.0947123647842589</v>
+        <v>0.09872900451217489</v>
       </c>
       <c r="W53">
-        <v>0.2225197007360292</v>
+        <v>0.2125197007360292</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3797608852616636</v>
+        <v>0.3958660966807334</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1586146077828128</v>
+        <v>0.1533568070637471</v>
       </c>
       <c r="C54">
-        <v>-926.5774406022699</v>
+        <v>-871.4688637770264</v>
       </c>
       <c r="D54">
-        <v>1328.33855939773</v>
+        <v>1383.447136222974</v>
       </c>
       <c r="E54">
         <v>1366.616</v>
@@ -5721,37 +5721,37 @@
         <v>227</v>
       </c>
       <c r="M54">
-        <v>609.4650328</v>
+        <v>584.6698728</v>
       </c>
       <c r="N54">
-        <v>-382.4650328</v>
+        <v>-357.6698728</v>
       </c>
       <c r="O54">
-        <v>-95.38677918032</v>
+        <v>-89.20286627632001</v>
       </c>
       <c r="P54">
-        <v>-287.07825361968</v>
+        <v>-268.46700652368</v>
       </c>
       <c r="Q54">
-        <v>-286.37825361968</v>
+        <v>-267.76700652368</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.08889908418216243</v>
+        <v>0.08877866601744214</v>
       </c>
       <c r="T54">
-        <v>0.9947199839029044</v>
+        <v>0.992578891857786</v>
       </c>
       <c r="U54">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.0928909731537924</v>
+        <v>0.09683036981001769</v>
       </c>
       <c r="W54">
-        <v>0.2229673987987978</v>
+        <v>0.2129673987987978</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3724577913143239</v>
+        <v>0.3882532871291807</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1606146077828128</v>
+        <v>0.1552568070637471</v>
       </c>
       <c r="C55">
-        <v>-994.140646075889</v>
+        <v>-939.6411183806661</v>
       </c>
       <c r="D55">
-        <v>1308.458353924111</v>
+        <v>1362.957881619334</v>
       </c>
       <c r="E55">
         <v>1414.299</v>
@@ -5803,37 +5803,37 @@
         <v>227</v>
       </c>
       <c r="M55">
-        <v>621.1855142000001</v>
+        <v>595.9135242000001</v>
       </c>
       <c r="N55">
-        <v>-394.1855142000001</v>
+        <v>-368.9135242000001</v>
       </c>
       <c r="O55">
-        <v>-98.30986724148002</v>
+        <v>-92.00703293548003</v>
       </c>
       <c r="P55">
-        <v>-295.8756469585201</v>
+        <v>-276.9064912645201</v>
       </c>
       <c r="Q55">
-        <v>-295.1756469585201</v>
+        <v>-276.2064912645201</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.08981608597327226</v>
+        <v>0.08969310571994092</v>
       </c>
       <c r="T55">
-        <v>1.015884238879562</v>
+        <v>1.013697591684548</v>
       </c>
       <c r="U55">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.09113831328296611</v>
+        <v>0.0950033817003947</v>
       </c>
       <c r="W55">
-        <v>0.2233982025950469</v>
+        <v>0.2133982025950469</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3654302858178272</v>
+        <v>0.3809277534097623</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1626146077828129</v>
+        <v>0.1571568070637471</v>
       </c>
       <c r="C56">
-        <v>-1061.117563062845</v>
+        <v>-1007.215326581412</v>
       </c>
       <c r="D56">
-        <v>1289.164436937155</v>
+        <v>1343.066673418589</v>
       </c>
       <c r="E56">
         <v>1461.982</v>
@@ -5885,37 +5885,37 @@
         <v>227</v>
       </c>
       <c r="M56">
-        <v>632.9059956000001</v>
+        <v>607.1571756000001</v>
       </c>
       <c r="N56">
-        <v>-405.9059956000001</v>
+        <v>-380.1571756000001</v>
       </c>
       <c r="O56">
-        <v>-101.23295530264</v>
+        <v>-94.81119959464002</v>
       </c>
       <c r="P56">
-        <v>-304.6730402973601</v>
+        <v>-285.3459760053601</v>
       </c>
       <c r="Q56">
-        <v>-303.9730402973601</v>
+        <v>-284.6459760053601</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09077295740747383</v>
+        <v>0.09064730367037441</v>
       </c>
       <c r="T56">
-        <v>1.037968678855204</v>
+        <v>1.035734495851603</v>
       </c>
       <c r="U56">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.08945056674068895</v>
+        <v>0.09324405981705405</v>
       </c>
       <c r="W56">
-        <v>0.2238130506951387</v>
+        <v>0.2138130506951386</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3586630583026823</v>
+        <v>0.3738735357540259</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1646146077828128</v>
+        <v>0.1590568070637471</v>
       </c>
       <c r="C57">
-        <v>-1127.53375009911</v>
+        <v>-1074.217295675811</v>
       </c>
       <c r="D57">
-        <v>1270.431249900891</v>
+        <v>1323.747704324189</v>
       </c>
       <c r="E57">
         <v>1509.665</v>
@@ -5967,37 +5967,37 @@
         <v>227</v>
       </c>
       <c r="M57">
-        <v>644.6264770000001</v>
+        <v>618.4008270000002</v>
       </c>
       <c r="N57">
-        <v>-417.6264770000001</v>
+        <v>-391.4008270000002</v>
       </c>
       <c r="O57">
-        <v>-104.1560433638</v>
+        <v>-97.61536625380005</v>
       </c>
       <c r="P57">
-        <v>-313.4704336362001</v>
+        <v>-293.7854607462001</v>
       </c>
       <c r="Q57">
-        <v>-312.7704336362001</v>
+        <v>-293.0854607462001</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09177235646097325</v>
+        <v>0.09164391041860495</v>
       </c>
       <c r="T57">
-        <v>1.061034649496431</v>
+        <v>1.058750817981639</v>
       </c>
       <c r="U57">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.08782419279994916</v>
+        <v>0.09154871327492579</v>
       </c>
       <c r="W57">
-        <v>0.2242128134097725</v>
+        <v>0.2142128134097725</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3521419117880881</v>
+        <v>0.3670758351039526</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1666146077828128</v>
+        <v>0.1609568070637471</v>
       </c>
       <c r="C58">
-        <v>-1193.413301407771</v>
+        <v>-1140.671369144737</v>
       </c>
       <c r="D58">
-        <v>1252.23469859223</v>
+        <v>1304.976630855264</v>
       </c>
       <c r="E58">
         <v>1557.348</v>
@@ -6049,37 +6049,37 @@
         <v>227</v>
       </c>
       <c r="M58">
-        <v>656.3469584000002</v>
+        <v>629.6444784000001</v>
       </c>
       <c r="N58">
-        <v>-429.3469584000002</v>
+        <v>-402.6444784000001</v>
       </c>
       <c r="O58">
-        <v>-107.0791314249601</v>
+        <v>-100.41953291296</v>
       </c>
       <c r="P58">
-        <v>-322.2678269750401</v>
+        <v>-302.2249454870401</v>
       </c>
       <c r="Q58">
-        <v>-321.5678269750401</v>
+        <v>-301.5249454870401</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09281718274417719</v>
+        <v>0.09268581747357324</v>
       </c>
       <c r="T58">
-        <v>1.085149073348623</v>
+        <v>1.08281333657213</v>
       </c>
       <c r="U58">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.08625590364280721</v>
+        <v>0.08991391482358783</v>
       </c>
       <c r="W58">
-        <v>0.224598298884598</v>
+        <v>0.214598298884598</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3458536633633007</v>
+        <v>0.3605209094770964</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1686146077828129</v>
+        <v>0.1628568070637471</v>
       </c>
       <c r="C59">
-        <v>-1258.778950285927</v>
+        <v>-1206.600528988611</v>
       </c>
       <c r="D59">
-        <v>1234.552049714073</v>
+        <v>1286.73047101139</v>
       </c>
       <c r="E59">
         <v>1605.031</v>
@@ -6131,37 +6131,37 @@
         <v>227</v>
       </c>
       <c r="M59">
-        <v>668.0674398000002</v>
+        <v>640.8881298000001</v>
       </c>
       <c r="N59">
-        <v>-441.0674398000002</v>
+        <v>-413.8881298000001</v>
       </c>
       <c r="O59">
-        <v>-110.0022194861201</v>
+        <v>-103.22369957212</v>
       </c>
       <c r="P59">
-        <v>-331.0652203138802</v>
+        <v>-310.6644302278801</v>
       </c>
       <c r="Q59">
-        <v>-330.3652203138802</v>
+        <v>-309.9644302278801</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09391060559869294</v>
+        <v>0.09377618532179588</v>
       </c>
       <c r="T59">
-        <v>1.110385098310219</v>
+        <v>1.107995042073808</v>
       </c>
       <c r="U59">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08474264217538953</v>
+        <v>0.08833647772141963</v>
       </c>
       <c r="W59">
-        <v>0.2249702585532893</v>
+        <v>0.2149702585532893</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.33978605523412</v>
+        <v>0.3541959812406561</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1706146077828128</v>
+        <v>0.1647568070637471</v>
       </c>
       <c r="C60">
-        <v>-1323.652163854067</v>
+        <v>-1272.02648959591</v>
       </c>
       <c r="D60">
-        <v>1217.361836145933</v>
+        <v>1268.98751040409</v>
       </c>
       <c r="E60">
         <v>1652.714</v>
@@ -6213,37 +6213,37 @@
         <v>227</v>
       </c>
       <c r="M60">
-        <v>679.7879212</v>
+        <v>652.1317812</v>
       </c>
       <c r="N60">
-        <v>-452.7879212</v>
+        <v>-425.1317812</v>
       </c>
       <c r="O60">
-        <v>-112.92530754728</v>
+        <v>-106.02786623128</v>
       </c>
       <c r="P60">
-        <v>-339.86261365272</v>
+        <v>-319.10391496872</v>
       </c>
       <c r="Q60">
-        <v>-339.16261365272</v>
+        <v>-318.40391496872</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09505609620818561</v>
+        <v>0.09491847544850529</v>
       </c>
       <c r="T60">
-        <v>1.136822838746176</v>
+        <v>1.134375876408898</v>
       </c>
       <c r="U60">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08328156213788285</v>
+        <v>0.08681343500208483</v>
       </c>
       <c r="W60">
-        <v>0.2253293920265084</v>
+        <v>0.2153293920265084</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3339276749714628</v>
+        <v>0.3480891539778862</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1726146077828128</v>
+        <v>0.1666568070637471</v>
       </c>
       <c r="C61">
-        <v>-1388.053229998274</v>
+        <v>-1336.969783951094</v>
       </c>
       <c r="D61">
-        <v>1200.643770001726</v>
+        <v>1251.727216048906</v>
       </c>
       <c r="E61">
         <v>1700.397</v>
@@ -6295,37 +6295,37 @@
         <v>227</v>
       </c>
       <c r="M61">
-        <v>691.5084026000001</v>
+        <v>663.3754326000001</v>
       </c>
       <c r="N61">
-        <v>-464.5084026000001</v>
+        <v>-436.3754326000001</v>
       </c>
       <c r="O61">
-        <v>-115.84839560844</v>
+        <v>-108.83203289044</v>
       </c>
       <c r="P61">
-        <v>-348.6600069915601</v>
+        <v>-327.54339970956</v>
       </c>
       <c r="Q61">
-        <v>-347.9600069915601</v>
+        <v>-326.8433997095601</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.09625746440838526</v>
+        <v>0.09611648704481029</v>
       </c>
       <c r="T61">
-        <v>1.164550225057059</v>
+        <v>1.162043580711554</v>
       </c>
       <c r="U61">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08187001023724075</v>
+        <v>0.08534202084950711</v>
       </c>
       <c r="W61">
-        <v>0.2256763514836863</v>
+        <v>0.2156763514836862</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3282678838702516</v>
+        <v>0.3421893378087695</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1746146077828128</v>
+        <v>0.1685568070637471</v>
       </c>
       <c r="C62">
-        <v>-1452.001337245601</v>
+        <v>-1401.449842901522</v>
       </c>
       <c r="D62">
-        <v>1184.378662754399</v>
+        <v>1234.930157098479</v>
       </c>
       <c r="E62">
         <v>1748.08</v>
@@ -6377,37 +6377,37 @@
         <v>227</v>
       </c>
       <c r="M62">
-        <v>703.2288840000001</v>
+        <v>674.619084</v>
       </c>
       <c r="N62">
-        <v>-476.2288840000001</v>
+        <v>-447.619084</v>
       </c>
       <c r="O62">
-        <v>-118.7714836696</v>
+        <v>-111.6361995496</v>
       </c>
       <c r="P62">
-        <v>-357.4574003304001</v>
+        <v>-335.9828844504</v>
       </c>
       <c r="Q62">
-        <v>-356.7574003304001</v>
+        <v>-335.2828844504</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.09751890101859489</v>
+        <v>0.09737439922093057</v>
       </c>
       <c r="T62">
-        <v>1.193663980683485</v>
+        <v>1.191094670229343</v>
       </c>
       <c r="U62">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08050551006662006</v>
+        <v>0.08391965383534866</v>
       </c>
       <c r="W62">
-        <v>0.2260117456256248</v>
+        <v>0.2160117456256248</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.322796752472414</v>
+        <v>0.3364861821786234</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1766146077828128</v>
+        <v>0.1704568070637471</v>
       </c>
       <c r="C63">
-        <v>-1515.514648233795</v>
+        <v>-1465.485068126738</v>
       </c>
       <c r="D63">
-        <v>1168.548351766206</v>
+        <v>1218.577931873262</v>
       </c>
       <c r="E63">
         <v>1795.763</v>
@@ -6459,37 +6459,37 @@
         <v>227</v>
       </c>
       <c r="M63">
-        <v>714.9493654</v>
+        <v>685.8627354</v>
       </c>
       <c r="N63">
-        <v>-487.9493654</v>
+        <v>-458.8627354</v>
       </c>
       <c r="O63">
-        <v>-121.69457173076</v>
+        <v>-114.44036620876</v>
       </c>
       <c r="P63">
-        <v>-366.25479366924</v>
+        <v>-344.42236919124</v>
       </c>
       <c r="Q63">
-        <v>-365.55479366924</v>
+        <v>-343.72236919124</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.09884502668573836</v>
+        <v>0.09869681971377495</v>
       </c>
       <c r="T63">
-        <v>1.224270749418959</v>
+        <v>1.221635559209583</v>
       </c>
       <c r="U63">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07918574760651154</v>
+        <v>0.08254392180526098</v>
       </c>
       <c r="W63">
-        <v>0.2263361432383195</v>
+        <v>0.2163361432383195</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3175050024318827</v>
+        <v>0.3309700152576623</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1786146077828129</v>
+        <v>0.1723568070637471</v>
       </c>
       <c r="C64">
-        <v>-1578.610367366794</v>
+        <v>-1529.092899386222</v>
       </c>
       <c r="D64">
-        <v>1153.135632633206</v>
+        <v>1202.653100613778</v>
       </c>
       <c r="E64">
         <v>1843.446</v>
@@ -6541,37 +6541,37 @@
         <v>227</v>
       </c>
       <c r="M64">
-        <v>726.6698468000001</v>
+        <v>697.1063868</v>
       </c>
       <c r="N64">
-        <v>-499.6698468000001</v>
+        <v>-470.1063868</v>
       </c>
       <c r="O64">
-        <v>-124.61765979192</v>
+        <v>-117.24453286792</v>
       </c>
       <c r="P64">
-        <v>-375.0521870080801</v>
+        <v>-352.86185393208</v>
       </c>
       <c r="Q64">
-        <v>-374.3521870080801</v>
+        <v>-352.16185393208</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1002409484406262</v>
+        <v>0.1000888412851901</v>
       </c>
       <c r="T64">
-        <v>1.256488400719458</v>
+        <v>1.253783863399309</v>
       </c>
       <c r="U64">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07790855812898717</v>
+        <v>0.08121256822775677</v>
       </c>
       <c r="W64">
-        <v>0.226650076411895</v>
+        <v>0.216650076411895</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.312383954005562</v>
+        <v>0.3256317892051194</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1806146077828129</v>
+        <v>0.1742568070637471</v>
       </c>
       <c r="C65">
-        <v>-1641.30480318582</v>
+        <v>-1592.289876562238</v>
       </c>
       <c r="D65">
-        <v>1138.12419681418</v>
+        <v>1187.139123437762</v>
       </c>
       <c r="E65">
         <v>1891.129</v>
@@ -6623,37 +6623,37 @@
         <v>227</v>
       </c>
       <c r="M65">
-        <v>738.3903282</v>
+        <v>708.3500382</v>
       </c>
       <c r="N65">
-        <v>-511.3903282</v>
+        <v>-481.3500382</v>
       </c>
       <c r="O65">
-        <v>-127.54074785308</v>
+        <v>-120.04869952708</v>
       </c>
       <c r="P65">
-        <v>-383.84958034692</v>
+        <v>-361.30133867292</v>
       </c>
       <c r="Q65">
-        <v>-383.14958034692</v>
+        <v>-360.60133867292</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.101712325425508</v>
+        <v>0.1015561072658709</v>
       </c>
       <c r="T65">
-        <v>1.290447546684849</v>
+        <v>1.287669913761452</v>
       </c>
       <c r="U65">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07667191434916198</v>
+        <v>0.0799234798431892</v>
       </c>
       <c r="W65">
-        <v>0.226954043452976</v>
+        <v>0.216954043452976</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3074254785451562</v>
+        <v>0.320463030646308</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1826146077828129</v>
+        <v>0.1761568070637471</v>
       </c>
       <c r="C66">
-        <v>-1703.613425931416</v>
+        <v>-1655.091696961805</v>
       </c>
       <c r="D66">
-        <v>1123.498574068584</v>
+        <v>1172.020303038195</v>
       </c>
       <c r="E66">
         <v>1938.812</v>
@@ -6705,37 +6705,37 @@
         <v>227</v>
       </c>
       <c r="M66">
-        <v>750.1108096</v>
+        <v>719.5936896000001</v>
       </c>
       <c r="N66">
-        <v>-523.1108096</v>
+        <v>-492.5936896000001</v>
       </c>
       <c r="O66">
-        <v>-130.46383591424</v>
+        <v>-122.85286618624</v>
       </c>
       <c r="P66">
-        <v>-392.64697368576</v>
+        <v>-369.74082341376</v>
       </c>
       <c r="Q66">
-        <v>-391.94697368576</v>
+        <v>-369.0408234137601</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1032654455762166</v>
+        <v>0.1031048880232562</v>
       </c>
       <c r="T66">
-        <v>1.326293311870539</v>
+        <v>1.323438522477048</v>
       </c>
       <c r="U66">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07547391568745632</v>
+        <v>0.07867467547063937</v>
       </c>
       <c r="W66">
-        <v>0.2272485115240233</v>
+        <v>0.2172485115240232</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3026219554428882</v>
+        <v>0.3154557957924593</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1846146077828129</v>
+        <v>0.1780568070637471</v>
       </c>
       <c r="C67">
-        <v>-1765.550920723546</v>
+        <v>-1717.513268295111</v>
       </c>
       <c r="D67">
-        <v>1109.244079276455</v>
+        <v>1157.281731704889</v>
       </c>
       <c r="E67">
         <v>1986.495</v>
@@ -6787,37 +6787,37 @@
         <v>227</v>
       </c>
       <c r="M67">
-        <v>761.8312910000002</v>
+        <v>730.8373410000002</v>
       </c>
       <c r="N67">
-        <v>-534.8312910000002</v>
+        <v>-503.8373410000002</v>
       </c>
       <c r="O67">
-        <v>-133.3869239754001</v>
+        <v>-125.6570328454</v>
       </c>
       <c r="P67">
-        <v>-401.4443670246001</v>
+        <v>-378.1803081546001</v>
       </c>
       <c r="Q67">
-        <v>-400.7443670246001</v>
+        <v>-377.4803081546001</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1049073154498227</v>
+        <v>0.1047421705382064</v>
       </c>
       <c r="T67">
-        <v>1.364187406495412</v>
+        <v>1.361251051690678</v>
       </c>
       <c r="U67">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0743127785230339</v>
+        <v>0.07746429584801413</v>
       </c>
       <c r="W67">
-        <v>0.2275339190390383</v>
+        <v>0.2175339190390383</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2979662330514591</v>
+        <v>0.3106026297033445</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1866146077828129</v>
+        <v>0.1799568070637471</v>
       </c>
       <c r="C68">
-        <v>-1827.131236744041</v>
+        <v>-1779.568757706237</v>
       </c>
       <c r="D68">
-        <v>1095.346763255959</v>
+        <v>1142.909242293763</v>
       </c>
       <c r="E68">
         <v>2034.178</v>
@@ -6869,37 +6869,37 @@
         <v>227</v>
       </c>
       <c r="M68">
-        <v>773.5517724000001</v>
+        <v>742.0809924000001</v>
       </c>
       <c r="N68">
-        <v>-546.5517724000001</v>
+        <v>-515.0809924000001</v>
       </c>
       <c r="O68">
-        <v>-136.31001203656</v>
+        <v>-128.46119950456</v>
       </c>
       <c r="P68">
-        <v>-410.2417603634401</v>
+        <v>-386.6197928954401</v>
       </c>
       <c r="Q68">
-        <v>-409.5417603634401</v>
+        <v>-385.9197928954401</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1066457659042293</v>
+        <v>0.1064757637893301</v>
       </c>
       <c r="T68">
-        <v>1.404310565509983</v>
+        <v>1.401287847328639</v>
       </c>
       <c r="U68">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07318682733329096</v>
+        <v>0.0762905943957715</v>
       </c>
       <c r="W68">
-        <v>0.2278106778414771</v>
+        <v>0.2178106778414771</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2934515931567401</v>
+        <v>0.3058965292532939</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1886146077828129</v>
+        <v>0.1818568070637471</v>
       </c>
       <c r="C69">
-        <v>-1888.367632767675</v>
+        <v>-1841.27163719517</v>
       </c>
       <c r="D69">
-        <v>1081.793367232326</v>
+        <v>1128.889362804831</v>
       </c>
       <c r="E69">
         <v>2081.861</v>
@@ -6951,37 +6951,37 @@
         <v>227</v>
       </c>
       <c r="M69">
-        <v>785.2722538000002</v>
+        <v>753.3246438000001</v>
       </c>
       <c r="N69">
-        <v>-558.2722538000002</v>
+        <v>-526.3246438000001</v>
       </c>
       <c r="O69">
-        <v>-139.23310009772</v>
+        <v>-131.26536616372</v>
       </c>
       <c r="P69">
-        <v>-419.0391537022801</v>
+        <v>-395.0592776362801</v>
       </c>
       <c r="Q69">
-        <v>-418.3391537022802</v>
+        <v>-394.3592776362801</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1084895769922362</v>
+        <v>0.1083144232980977</v>
       </c>
       <c r="T69">
-        <v>1.446865431131497</v>
+        <v>1.443751115429507</v>
       </c>
       <c r="U69">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07209448662682393</v>
+        <v>0.07515192880777491</v>
       </c>
       <c r="W69">
-        <v>0.2280791751871267</v>
+        <v>0.2180791751871267</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2890717186320125</v>
+        <v>0.3013309094136924</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1906146077828129</v>
+        <v>0.1837568070637471</v>
       </c>
       <c r="C70">
-        <v>-1949.272719354229</v>
+        <v>-1902.634725737218</v>
       </c>
       <c r="D70">
-        <v>1068.571280645772</v>
+        <v>1115.209274262783</v>
       </c>
       <c r="E70">
         <v>2129.544</v>
@@ -7033,37 +7033,37 @@
         <v>227</v>
       </c>
       <c r="M70">
-        <v>796.9927352000002</v>
+        <v>764.5682952000001</v>
       </c>
       <c r="N70">
-        <v>-569.9927352000002</v>
+        <v>-537.5682952000001</v>
       </c>
       <c r="O70">
-        <v>-142.15618815888</v>
+        <v>-134.06953282288</v>
       </c>
       <c r="P70">
-        <v>-427.8365470411202</v>
+        <v>-403.49876237712</v>
       </c>
       <c r="Q70">
-        <v>-427.1365470411202</v>
+        <v>-402.7987623771201</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1104486262732436</v>
+        <v>0.1102679990261632</v>
       </c>
       <c r="T70">
-        <v>1.492079975854356</v>
+        <v>1.488868337786679</v>
       </c>
       <c r="U70">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07103427358819417</v>
+        <v>0.07404675338413116</v>
       </c>
       <c r="W70">
-        <v>0.2283397755520219</v>
+        <v>0.2183397755520219</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2848206639462476</v>
+        <v>0.29689957251055</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1926146077828129</v>
+        <v>0.1856568070637471</v>
       </c>
       <c r="C71">
-        <v>-2009.858497983818</v>
+        <v>-1963.670228376636</v>
       </c>
       <c r="D71">
-        <v>1055.668502016182</v>
+        <v>1101.856771623364</v>
       </c>
       <c r="E71">
         <v>2177.227</v>
@@ -7115,37 +7115,37 @@
         <v>227</v>
       </c>
       <c r="M71">
-        <v>808.7132166000001</v>
+        <v>775.8119466000002</v>
       </c>
       <c r="N71">
-        <v>-581.7132166000001</v>
+        <v>-548.8119466000002</v>
       </c>
       <c r="O71">
-        <v>-145.07927622004</v>
+        <v>-136.8736994820401</v>
       </c>
       <c r="P71">
-        <v>-436.6339403799601</v>
+        <v>-411.9382471179601</v>
       </c>
       <c r="Q71">
-        <v>-435.9339403799601</v>
+        <v>-411.2382471179602</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1125340658304451</v>
+        <v>0.1123476118979749</v>
       </c>
       <c r="T71">
-        <v>1.540211587978691</v>
+        <v>1.536896348683024</v>
       </c>
       <c r="U71">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07000479136227833</v>
+        <v>0.07297361203073796</v>
       </c>
       <c r="W71">
-        <v>0.228592822283152</v>
+        <v>0.218592822283152</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2806928282368818</v>
+        <v>0.2925966801553246</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1946146077828129</v>
+        <v>0.1875568070637471</v>
       </c>
       <c r="C72">
-        <v>-2070.136397390718</v>
+        <v>-2024.389772545044</v>
       </c>
       <c r="D72">
-        <v>1043.073602609283</v>
+        <v>1088.820227454957</v>
       </c>
       <c r="E72">
         <v>2224.91</v>
@@ -7197,37 +7197,37 @@
         <v>227</v>
       </c>
       <c r="M72">
-        <v>820.4336980000002</v>
+        <v>787.0555980000001</v>
       </c>
       <c r="N72">
-        <v>-593.4336980000002</v>
+        <v>-560.0555980000001</v>
       </c>
       <c r="O72">
-        <v>-148.0023642812</v>
+        <v>-139.6778661412</v>
       </c>
       <c r="P72">
-        <v>-445.4313337188001</v>
+        <v>-420.3777318588001</v>
       </c>
       <c r="Q72">
-        <v>-444.7313337188002</v>
+        <v>-419.6777318588001</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1147585346914599</v>
+        <v>0.1145658656279074</v>
       </c>
       <c r="T72">
-        <v>1.591551974244647</v>
+        <v>1.588126226972458</v>
       </c>
       <c r="U72">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06900472291424577</v>
+        <v>0.07193113185887026</v>
       </c>
       <c r="W72">
-        <v>0.2288386391076784</v>
+        <v>0.2188386391076784</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2766829306906405</v>
+        <v>0.2884167275816771</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1966146077828128</v>
+        <v>0.1894568070637471</v>
       </c>
       <c r="C73">
-        <v>-2130.117307326934</v>
+        <v>-2084.804441831796</v>
       </c>
       <c r="D73">
-        <v>1030.775692673066</v>
+        <v>1076.088558168204</v>
       </c>
       <c r="E73">
         <v>2272.593</v>
@@ -7279,37 +7279,37 @@
         <v>227</v>
       </c>
       <c r="M73">
-        <v>832.1541794000001</v>
+        <v>798.2992494</v>
       </c>
       <c r="N73">
-        <v>-605.1541794000001</v>
+        <v>-571.2992494</v>
       </c>
       <c r="O73">
-        <v>-150.92545234236</v>
+        <v>-142.48203280036</v>
       </c>
       <c r="P73">
-        <v>-454.2287270576401</v>
+        <v>-428.81721659964</v>
       </c>
       <c r="Q73">
-        <v>-453.5287270576401</v>
+        <v>-428.11721659964</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1171364151980619</v>
+        <v>0.1169371023736973</v>
       </c>
       <c r="T73">
-        <v>1.646433076804807</v>
+        <v>1.642889200316335</v>
       </c>
       <c r="U73">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06803282540841132</v>
+        <v>0.07091801732564676</v>
       </c>
       <c r="W73">
-        <v>0.2290775315146125</v>
+        <v>0.2190775315146125</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.272785988004857</v>
+        <v>0.2843545201509493</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1986146077828128</v>
+        <v>0.1913568070637471</v>
       </c>
       <c r="C74">
-        <v>-2189.811609965148</v>
+        <v>-2144.924807412465</v>
       </c>
       <c r="D74">
-        <v>1018.764390034852</v>
+        <v>1063.651192587535</v>
       </c>
       <c r="E74">
         <v>2320.276</v>
@@ -7361,37 +7361,37 @@
         <v>227</v>
       </c>
       <c r="M74">
-        <v>843.8746608</v>
+        <v>809.5429008</v>
       </c>
       <c r="N74">
-        <v>-616.8746608</v>
+        <v>-582.5429008</v>
       </c>
       <c r="O74">
-        <v>-153.84854040352</v>
+        <v>-145.28619945952</v>
       </c>
       <c r="P74">
-        <v>-463.02612039648</v>
+        <v>-437.25670134048</v>
       </c>
       <c r="Q74">
-        <v>-462.32612039648</v>
+        <v>-436.55670134048</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1196841443122784</v>
+        <v>0.119477713172758</v>
       </c>
       <c r="T74">
-        <v>1.705234258119264</v>
+        <v>1.701563814613347</v>
       </c>
       <c r="U74">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06708792505551674</v>
+        <v>0.06993304486279055</v>
       </c>
       <c r="W74">
-        <v>0.229309788021354</v>
+        <v>0.219309788021354</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2689972937270118</v>
+        <v>0.2804051518155195</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2006146077828128</v>
+        <v>0.1932568070637471</v>
       </c>
       <c r="C75">
-        <v>-2249.229209131387</v>
+        <v>-2204.760957322726</v>
       </c>
       <c r="D75">
-        <v>1007.029790868614</v>
+        <v>1051.498042677274</v>
       </c>
       <c r="E75">
         <v>2367.959</v>
@@ -7443,37 +7443,37 @@
         <v>227</v>
       </c>
       <c r="M75">
-        <v>855.5951422000001</v>
+        <v>820.7865522</v>
       </c>
       <c r="N75">
-        <v>-628.5951422000001</v>
+        <v>-593.7865522</v>
       </c>
       <c r="O75">
-        <v>-156.77162846468</v>
+        <v>-148.09036611868</v>
       </c>
       <c r="P75">
-        <v>-471.82351373532</v>
+        <v>-445.69618608132</v>
       </c>
       <c r="Q75">
-        <v>-471.12351373532</v>
+        <v>-444.99618608132</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1224205941016221</v>
+        <v>0.1222065173643416</v>
       </c>
       <c r="T75">
-        <v>1.768391082494052</v>
+        <v>1.764584696636064</v>
       </c>
       <c r="U75">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06616891238352335</v>
+        <v>0.06897505794686191</v>
       </c>
       <c r="W75">
-        <v>0.22953568133613</v>
+        <v>0.21953568133613</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2653123992923951</v>
+        <v>0.2765639853522932</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2026146077828128</v>
+        <v>0.1951568070637471</v>
       </c>
       <c r="C76">
-        <v>-2308.379557540399</v>
+        <v>-2264.322523748042</v>
       </c>
       <c r="D76">
-        <v>995.562442459601</v>
+        <v>1039.619476251958</v>
       </c>
       <c r="E76">
         <v>2415.642</v>
@@ -7525,37 +7525,37 @@
         <v>227</v>
       </c>
       <c r="M76">
-        <v>867.3156236000001</v>
+        <v>832.0302036</v>
       </c>
       <c r="N76">
-        <v>-640.3156236000001</v>
+        <v>-605.0302036</v>
       </c>
       <c r="O76">
-        <v>-159.69471652584</v>
+        <v>-150.89453277784</v>
       </c>
       <c r="P76">
-        <v>-480.6209070741601</v>
+        <v>-454.13567082216</v>
       </c>
       <c r="Q76">
-        <v>-479.9209070741601</v>
+        <v>-453.43567082216</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1253675400286075</v>
+        <v>0.1251452295706624</v>
       </c>
       <c r="T76">
-        <v>1.836406124128438</v>
+        <v>1.832453338814374</v>
       </c>
       <c r="U76">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0652747378918541</v>
+        <v>0.06804296256920161</v>
       </c>
       <c r="W76">
-        <v>0.2297554694261823</v>
+        <v>0.2197554694261823</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2617270965992546</v>
+        <v>0.2728266341988838</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2046146077828128</v>
+        <v>0.1970568070637471</v>
       </c>
       <c r="C77">
-        <v>-2367.271682191166</v>
+        <v>-2323.618708484289</v>
       </c>
       <c r="D77">
-        <v>984.3533178088346</v>
+        <v>1028.006291515712</v>
       </c>
       <c r="E77">
         <v>2463.325</v>
@@ -7607,37 +7607,37 @@
         <v>227</v>
       </c>
       <c r="M77">
-        <v>879.0361050000001</v>
+        <v>843.2738550000001</v>
       </c>
       <c r="N77">
-        <v>-652.0361050000001</v>
+        <v>-616.2738550000001</v>
       </c>
       <c r="O77">
-        <v>-162.6178045870001</v>
+        <v>-153.698699437</v>
       </c>
       <c r="P77">
-        <v>-489.4183004130001</v>
+        <v>-462.5751555630001</v>
       </c>
       <c r="Q77">
-        <v>-488.7183004130001</v>
+        <v>-461.8751555630001</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1285502416297518</v>
+        <v>0.1283190387534889</v>
       </c>
       <c r="T77">
-        <v>1.909862369093576</v>
+        <v>1.905751472366949</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06440440805329604</v>
+        <v>0.06713572306827892</v>
       </c>
       <c r="W77">
-        <v>0.2299693965004999</v>
+        <v>0.2199693965004998</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2582374019779312</v>
+        <v>0.2691889457428986</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2066146077828129</v>
+        <v>0.1989568070637471</v>
       </c>
       <c r="C78">
-        <v>-2425.914208065921</v>
+        <v>-2382.658306710768</v>
       </c>
       <c r="D78">
-        <v>973.3937919340791</v>
+        <v>1016.649693289233</v>
       </c>
       <c r="E78">
         <v>2511.008</v>
@@ -7689,37 +7689,37 @@
         <v>227</v>
       </c>
       <c r="M78">
-        <v>890.7565864000002</v>
+        <v>854.5175064000001</v>
       </c>
       <c r="N78">
-        <v>-663.7565864000002</v>
+        <v>-627.5175064000001</v>
       </c>
       <c r="O78">
-        <v>-165.5408926481601</v>
+        <v>-156.50286609616</v>
       </c>
       <c r="P78">
-        <v>-498.2156937518401</v>
+        <v>-471.0146403038401</v>
       </c>
       <c r="Q78">
-        <v>-497.5156937518402</v>
+        <v>-470.3146403038401</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1319981683643248</v>
+        <v>0.1317573320348843</v>
       </c>
       <c r="T78">
-        <v>1.989439967805809</v>
+        <v>1.985157783715572</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06355698163154215</v>
+        <v>0.06625235829106473</v>
       </c>
       <c r="W78">
-        <v>0.230177693914967</v>
+        <v>0.2201776939149669</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2548395414255901</v>
+        <v>0.2656469859304921</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2086146077828128</v>
+        <v>0.2008568070637471</v>
       </c>
       <c r="C79">
-        <v>-2484.315380263466</v>
+        <v>-2441.449729204688</v>
       </c>
       <c r="D79">
-        <v>962.6756197365341</v>
+        <v>1005.541270795312</v>
       </c>
       <c r="E79">
         <v>2558.691</v>
@@ -7771,37 +7771,37 @@
         <v>227</v>
       </c>
       <c r="M79">
-        <v>902.4770678000001</v>
+        <v>865.7611578000001</v>
       </c>
       <c r="N79">
-        <v>-675.4770678000001</v>
+        <v>-638.7611578000001</v>
       </c>
       <c r="O79">
-        <v>-168.46398070932</v>
+        <v>-159.30703275532</v>
       </c>
       <c r="P79">
-        <v>-507.0130870906801</v>
+        <v>-479.45412504468</v>
       </c>
       <c r="Q79">
-        <v>-506.3130870906801</v>
+        <v>-478.7541250446801</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1357459148149477</v>
+        <v>0.1354946073407488</v>
       </c>
       <c r="T79">
-        <v>2.075937357710409</v>
+        <v>2.071468991703206</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06273156628567797</v>
+        <v>0.06539193805351842</v>
       </c>
       <c r="W79">
-        <v>0.2303805810069804</v>
+        <v>0.2203805810069804</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2515299369914915</v>
+        <v>0.2621970250742519</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2106146077828129</v>
+        <v>0.2027568070637471</v>
       </c>
       <c r="C80">
-        <v>-2542.483084686116</v>
+        <v>-2500.001023115027</v>
       </c>
       <c r="D80">
-        <v>952.1909153138839</v>
+        <v>994.6729768849729</v>
       </c>
       <c r="E80">
         <v>2606.374</v>
@@ -7853,37 +7853,37 @@
         <v>227</v>
       </c>
       <c r="M80">
-        <v>914.1975492000001</v>
+        <v>877.0048092000001</v>
       </c>
       <c r="N80">
-        <v>-687.1975492000001</v>
+        <v>-650.0048092000001</v>
       </c>
       <c r="O80">
-        <v>-171.3870687704801</v>
+        <v>-162.11119941448</v>
       </c>
       <c r="P80">
-        <v>-515.8104804295201</v>
+        <v>-487.8936097855201</v>
       </c>
       <c r="Q80">
-        <v>-515.1104804295201</v>
+        <v>-487.1936097855201</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1398343654883544</v>
+        <v>0.1395716349471465</v>
       </c>
       <c r="T80">
-        <v>2.170298146697246</v>
+        <v>2.16562667314426</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06192731543586159</v>
+        <v>0.06455357987334512</v>
       </c>
       <c r="W80">
-        <v>0.2305782658658652</v>
+        <v>0.2205782658658652</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2483051942095492</v>
+        <v>0.2588355247527871</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2126146077828129</v>
+        <v>0.2046568070637471</v>
       </c>
       <c r="C81">
-        <v>-2600.424867389393</v>
+        <v>-2558.319891403604</v>
       </c>
       <c r="D81">
-        <v>941.9321326106074</v>
+        <v>984.0371085963966</v>
       </c>
       <c r="E81">
         <v>2654.057</v>
@@ -7935,37 +7935,37 @@
         <v>227</v>
       </c>
       <c r="M81">
-        <v>925.9180306000002</v>
+        <v>888.2484606000002</v>
       </c>
       <c r="N81">
-        <v>-698.9180306000002</v>
+        <v>-661.2484606000002</v>
       </c>
       <c r="O81">
-        <v>-174.3101568316401</v>
+        <v>-164.9153660736401</v>
       </c>
       <c r="P81">
-        <v>-524.6078737683602</v>
+        <v>-496.3330945263601</v>
       </c>
       <c r="Q81">
-        <v>-523.9078737683601</v>
+        <v>-495.6330945263601</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1443121924163712</v>
+        <v>0.1440369508970106</v>
       </c>
       <c r="T81">
-        <v>2.273645677492353</v>
+        <v>2.268751752817797</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06114342536705321</v>
+        <v>0.06373644595089771</v>
       </c>
       <c r="W81">
-        <v>0.2307709460447784</v>
+        <v>0.2207709460447783</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2451620904853777</v>
+        <v>0.2555591257052835</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2146146077828128</v>
+        <v>0.2065568070637471</v>
       </c>
       <c r="C82">
-        <v>-2658.147952694207</v>
+        <v>-2616.413711052063</v>
       </c>
       <c r="D82">
-        <v>931.8920473057935</v>
+        <v>973.6262889479375</v>
       </c>
       <c r="E82">
         <v>2701.74</v>
@@ -8017,37 +8017,37 @@
         <v>227</v>
       </c>
       <c r="M82">
-        <v>937.6385120000001</v>
+        <v>899.4921120000001</v>
       </c>
       <c r="N82">
-        <v>-710.6385120000001</v>
+        <v>-672.4921120000001</v>
       </c>
       <c r="O82">
-        <v>-177.2332448928</v>
+        <v>-167.7195327328</v>
       </c>
       <c r="P82">
-        <v>-533.4052671072001</v>
+        <v>-504.7725792672001</v>
       </c>
       <c r="Q82">
-        <v>-532.7052671072001</v>
+        <v>-504.0725792672001</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1492378020371898</v>
+        <v>0.1489487984418612</v>
       </c>
       <c r="T82">
-        <v>2.38732796136697</v>
+        <v>2.382189340458687</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06037913254996505</v>
+        <v>0.06293974037651148</v>
       </c>
       <c r="W82">
-        <v>0.2309588092192186</v>
+        <v>0.2209588092192186</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2420975643543105</v>
+        <v>0.2523646366339675</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2166146077828128</v>
+        <v>0.2084568070637471</v>
       </c>
       <c r="C83">
-        <v>-2715.659260152924</v>
+        <v>-2674.289550125221</v>
       </c>
       <c r="D83">
-        <v>922.0637398470768</v>
+        <v>963.4334498747789</v>
       </c>
       <c r="E83">
         <v>2749.423</v>
@@ -8099,37 +8099,37 @@
         <v>227</v>
       </c>
       <c r="M83">
-        <v>949.3589934000001</v>
+        <v>910.7357634000001</v>
       </c>
       <c r="N83">
-        <v>-722.3589934000001</v>
+        <v>-683.7357634000001</v>
       </c>
       <c r="O83">
-        <v>-180.15633295396</v>
+        <v>-170.52369939196</v>
       </c>
       <c r="P83">
-        <v>-542.2026604460401</v>
+        <v>-513.2120640080401</v>
       </c>
       <c r="Q83">
-        <v>-541.5026604460402</v>
+        <v>-512.5120640080402</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1546818968812524</v>
+        <v>0.1543776825703802</v>
       </c>
       <c r="T83">
-        <v>2.512976801438917</v>
+        <v>2.507567726798618</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0596337111604593</v>
+        <v>0.06216270654470271</v>
       </c>
       <c r="W83">
-        <v>0.2311420337967591</v>
+        <v>0.2211420337967591</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2391087055351215</v>
+        <v>0.2492490238360172</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2186146077828128</v>
+        <v>0.2103568070637471</v>
       </c>
       <c r="C84">
-        <v>-2772.965420453007</v>
+        <v>-2731.954183773699</v>
       </c>
       <c r="D84">
-        <v>912.4405795469929</v>
+        <v>953.4518162263013</v>
       </c>
       <c r="E84">
         <v>2797.106</v>
@@ -8181,37 +8181,37 @@
         <v>227</v>
       </c>
       <c r="M84">
-        <v>961.0794748000002</v>
+        <v>921.9794148000001</v>
       </c>
       <c r="N84">
-        <v>-734.0794748000002</v>
+        <v>-694.9794148000001</v>
       </c>
       <c r="O84">
-        <v>-183.0794210151201</v>
+        <v>-173.32786605112</v>
       </c>
       <c r="P84">
-        <v>-551.0000537848802</v>
+        <v>-521.65154874888</v>
       </c>
       <c r="Q84">
-        <v>-550.3000537848802</v>
+        <v>-520.95154874888</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1607308911524331</v>
+        <v>0.1604097760465124</v>
       </c>
       <c r="T84">
-        <v>2.652586623741079</v>
+        <v>2.646877044954097</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0589064707804537</v>
+        <v>0.06140462475757219</v>
       </c>
       <c r="W84">
-        <v>0.2313207894821645</v>
+        <v>0.2213207894821645</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2361927457115225</v>
+        <v>0.2462094015941146</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2206146077828129</v>
+        <v>0.2122568070637471</v>
       </c>
       <c r="C85">
-        <v>-2830.072790335096</v>
+        <v>-2789.414109251985</v>
       </c>
       <c r="D85">
-        <v>903.0162096649042</v>
+        <v>943.6748907480149</v>
       </c>
       <c r="E85">
         <v>2844.789</v>
@@ -8263,37 +8263,37 @@
         <v>227</v>
       </c>
       <c r="M85">
-        <v>972.7999562000001</v>
+        <v>933.2230662000001</v>
       </c>
       <c r="N85">
-        <v>-745.7999562000001</v>
+        <v>-706.2230662000001</v>
       </c>
       <c r="O85">
-        <v>-186.00250907628</v>
+        <v>-176.13203271028</v>
       </c>
       <c r="P85">
-        <v>-559.7974471237201</v>
+        <v>-530.0910334897201</v>
       </c>
       <c r="Q85">
-        <v>-559.09744712372</v>
+        <v>-529.39103348972</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1674915318084586</v>
+        <v>0.1671515275786602</v>
       </c>
       <c r="T85">
-        <v>2.808621131019966</v>
+        <v>2.802575694657279</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05819675426502655</v>
+        <v>0.06066481000145686</v>
       </c>
       <c r="W85">
-        <v>0.2314952378016565</v>
+        <v>0.2214952378016565</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2333470499800584</v>
+        <v>0.2432430232616554</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2226146077828128</v>
+        <v>0.2141568070637471</v>
       </c>
       <c r="C86">
-        <v>-2886.987466595997</v>
+        <v>-2846.675560021888</v>
       </c>
       <c r="D86">
-        <v>893.7845334040024</v>
+        <v>934.0964399781117</v>
       </c>
       <c r="E86">
         <v>2892.472</v>
@@ -8345,37 +8345,37 @@
         <v>227</v>
       </c>
       <c r="M86">
-        <v>984.5204376</v>
+        <v>944.4667176</v>
       </c>
       <c r="N86">
-        <v>-757.5204376</v>
+        <v>-717.4667176</v>
       </c>
       <c r="O86">
-        <v>-188.92559713744</v>
+        <v>-178.93619936944</v>
       </c>
       <c r="P86">
-        <v>-568.59484046256</v>
+        <v>-538.53051823056</v>
       </c>
       <c r="Q86">
-        <v>-567.8948404625601</v>
+        <v>-537.8305182305601</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1750972525464872</v>
+        <v>0.1747359980523264</v>
       </c>
       <c r="T86">
-        <v>2.984159951708712</v>
+        <v>2.977736675573357</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05750393576187148</v>
+        <v>0.0599426098823919</v>
       </c>
       <c r="W86">
-        <v>0.231665532589732</v>
+        <v>0.221665532589732</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2305691089088672</v>
+        <v>0.2403472729847309</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2246146077828128</v>
+        <v>0.2160568070637471</v>
       </c>
       <c r="C87">
-        <v>-2943.715299241473</v>
+        <v>-2903.744519005704</v>
       </c>
       <c r="D87">
-        <v>884.7397007585267</v>
+        <v>924.7104809942959</v>
       </c>
       <c r="E87">
         <v>2940.155</v>
@@ -8427,37 +8427,37 @@
         <v>227</v>
       </c>
       <c r="M87">
-        <v>996.2409190000001</v>
+        <v>955.710369</v>
       </c>
       <c r="N87">
-        <v>-769.2409190000001</v>
+        <v>-728.710369</v>
       </c>
       <c r="O87">
-        <v>-191.8486851986</v>
+        <v>-181.7403660286</v>
       </c>
       <c r="P87">
-        <v>-577.3922338014</v>
+        <v>-546.9700029713999</v>
       </c>
       <c r="Q87">
-        <v>-576.6922338014001</v>
+        <v>-546.2700029713999</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1837170693829197</v>
+        <v>0.1833317312558148</v>
       </c>
       <c r="T87">
-        <v>3.183103948489293</v>
+        <v>3.176252453944915</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05682741887055535</v>
+        <v>0.05923740270730494</v>
       </c>
       <c r="W87">
-        <v>0.2318318204416175</v>
+        <v>0.2218318204416175</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2278565311569981</v>
+        <v>0.23751965800844</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2266146077828128</v>
+        <v>0.2179568070637471</v>
       </c>
       <c r="C88">
-        <v>-3000.261903848383</v>
+        <v>-2960.62673104831</v>
       </c>
       <c r="D88">
-        <v>875.876096151618</v>
+        <v>915.5112689516907</v>
       </c>
       <c r="E88">
         <v>2987.838</v>
@@ -8509,37 +8509,37 @@
         <v>227</v>
       </c>
       <c r="M88">
-        <v>1007.9614004</v>
+        <v>966.9540204000001</v>
       </c>
       <c r="N88">
-        <v>-780.9614004000001</v>
+        <v>-739.9540204000001</v>
       </c>
       <c r="O88">
-        <v>-194.77177325976</v>
+        <v>-184.54453268776</v>
       </c>
       <c r="P88">
-        <v>-586.1896271402401</v>
+        <v>-555.4094877122401</v>
       </c>
       <c r="Q88">
-        <v>-585.4896271402401</v>
+        <v>-554.7094877122402</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.1935682886245569</v>
+        <v>0.1931554263455159</v>
       </c>
       <c r="T88">
-        <v>3.410468516238529</v>
+        <v>3.403127629226694</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05616663493020004</v>
+        <v>0.05854859569908046</v>
       </c>
       <c r="W88">
-        <v>0.2319942411341568</v>
+        <v>0.2219942411341568</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2252070366086609</v>
+        <v>0.2347578015199697</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2286146077828128</v>
+        <v>0.2198568070637471</v>
       </c>
       <c r="C89">
-        <v>-3056.632673191129</v>
+        <v>-3017.327714642735</v>
       </c>
       <c r="D89">
-        <v>867.1883268088711</v>
+        <v>906.4932853572654</v>
       </c>
       <c r="E89">
         <v>3035.521</v>
@@ -8591,37 +8591,37 @@
         <v>227</v>
       </c>
       <c r="M89">
-        <v>1019.6818818</v>
+        <v>978.1976718000001</v>
       </c>
       <c r="N89">
-        <v>-792.6818818000002</v>
+        <v>-751.1976718000001</v>
       </c>
       <c r="O89">
-        <v>-197.69486132092</v>
+        <v>-187.34869934692</v>
       </c>
       <c r="P89">
-        <v>-594.9870204790801</v>
+        <v>-563.84897245308</v>
       </c>
       <c r="Q89">
-        <v>-594.2870204790802</v>
+        <v>-563.14897245308</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2049350800572151</v>
+        <v>0.2044904591413248</v>
       </c>
       <c r="T89">
-        <v>3.672812248256877</v>
+        <v>3.664906677628748</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05552104142525521</v>
+        <v>0.05787562333472322</v>
       </c>
       <c r="W89">
-        <v>0.2321529280176723</v>
+        <v>0.2221529280176723</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2226184499809752</v>
+        <v>0.2320594359852575</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2306146077828128</v>
+        <v>0.2217568070637471</v>
       </c>
       <c r="C90">
-        <v>-3112.832788182965</v>
+        <v>-3073.852772969494</v>
       </c>
       <c r="D90">
-        <v>858.6712118170357</v>
+        <v>897.6512270305059</v>
       </c>
       <c r="E90">
         <v>3083.204</v>
@@ -8673,37 +8673,37 @@
         <v>227</v>
       </c>
       <c r="M90">
-        <v>1031.4023632</v>
+        <v>989.4413232000001</v>
       </c>
       <c r="N90">
-        <v>-804.4023632000001</v>
+        <v>-762.4413232000001</v>
       </c>
       <c r="O90">
-        <v>-200.61794938208</v>
+        <v>-190.15286600608</v>
       </c>
       <c r="P90">
-        <v>-603.78441381792</v>
+        <v>-572.2884571939201</v>
       </c>
       <c r="Q90">
-        <v>-603.08441381792</v>
+        <v>-571.58845719392</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2181963367286497</v>
+        <v>0.2177146640697686</v>
       </c>
       <c r="T90">
-        <v>3.978879935611618</v>
+        <v>3.970315567431145</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05489012049996823</v>
+        <v>0.05721794579682863</v>
       </c>
       <c r="W90">
-        <v>0.2323080083811078</v>
+        <v>0.2223080083811078</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.220088694867555</v>
+        <v>0.2294223969399705</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2326146077828128</v>
+        <v>0.2236568070637471</v>
       </c>
       <c r="C91">
-        <v>-3168.867228178799</v>
+        <v>-3130.207004296088</v>
       </c>
       <c r="D91">
-        <v>850.3197718212006</v>
+        <v>888.9799957039123</v>
       </c>
       <c r="E91">
         <v>3130.887</v>
@@ -8755,37 +8755,37 @@
         <v>227</v>
       </c>
       <c r="M91">
-        <v>1043.1228446</v>
+        <v>1000.6849746</v>
       </c>
       <c r="N91">
-        <v>-816.1228446000002</v>
+        <v>-773.6849746000001</v>
       </c>
       <c r="O91">
-        <v>-203.5410374432401</v>
+        <v>-192.95703266524</v>
       </c>
       <c r="P91">
-        <v>-612.5818071567602</v>
+        <v>-580.7279419347601</v>
       </c>
       <c r="Q91">
-        <v>-611.8818071567603</v>
+        <v>-580.0279419347601</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2338687309767088</v>
+        <v>0.233343269894293</v>
       </c>
       <c r="T91">
-        <v>4.340596293394491</v>
+        <v>4.331253346288521</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05427337757300229</v>
+        <v>0.05657504752944852</v>
       </c>
       <c r="W91">
-        <v>0.232459603792556</v>
+        <v>0.2224596037925561</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2176157881836499</v>
+        <v>0.2268446171990719</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2346146077828129</v>
+        <v>0.2255568070637471</v>
       </c>
       <c r="C92">
-        <v>-3224.740780682576</v>
+        <v>-3186.395311779515</v>
       </c>
       <c r="D92">
-        <v>842.1292193174243</v>
+        <v>880.4746882204854</v>
       </c>
       <c r="E92">
         <v>3178.57</v>
@@ -8837,37 +8837,37 @@
         <v>227</v>
       </c>
       <c r="M92">
-        <v>1054.843326</v>
+        <v>1011.928626</v>
       </c>
       <c r="N92">
-        <v>-827.8433260000002</v>
+        <v>-784.9286260000001</v>
       </c>
       <c r="O92">
-        <v>-206.4641255044</v>
+        <v>-195.7611993244</v>
       </c>
       <c r="P92">
-        <v>-621.3792004956001</v>
+        <v>-589.1674266756002</v>
       </c>
       <c r="Q92">
-        <v>-620.6792004956001</v>
+        <v>-588.4674266756001</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2526756040743796</v>
+        <v>0.2520975968837223</v>
       </c>
       <c r="T92">
-        <v>4.774655922733941</v>
+        <v>4.764378680917374</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05367034004441337</v>
+        <v>0.05594643589023244</v>
       </c>
       <c r="W92">
-        <v>0.2326078304170832</v>
+        <v>0.2226078304170832</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2151978349816094</v>
+        <v>0.2243241214524155</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2366146077828129</v>
+        <v>0.2274568070637471</v>
       </c>
       <c r="C93">
-        <v>-3280.458050498966</v>
+        <v>-3242.422412711413</v>
       </c>
       <c r="D93">
-        <v>834.094949501034</v>
+        <v>872.1305872885875</v>
       </c>
       <c r="E93">
         <v>3226.253</v>
@@ -8919,37 +8919,37 @@
         <v>227</v>
       </c>
       <c r="M93">
-        <v>1066.5638074</v>
+        <v>1023.1722774</v>
       </c>
       <c r="N93">
-        <v>-839.5638074000001</v>
+        <v>-796.1722774000001</v>
       </c>
       <c r="O93">
-        <v>-209.38721356556</v>
+        <v>-198.56536598356</v>
       </c>
       <c r="P93">
-        <v>-630.17659383444</v>
+        <v>-597.6069114164401</v>
       </c>
       <c r="Q93">
-        <v>-629.4765938344401</v>
+        <v>-596.9069114164402</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2756617823048663</v>
+        <v>0.2750195520930248</v>
       </c>
       <c r="T93">
-        <v>5.305173247482157</v>
+        <v>5.293754089908194</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05308055608788136</v>
+        <v>0.05533163989143867</v>
       </c>
       <c r="W93">
-        <v>0.2327527993135988</v>
+        <v>0.2227527993135988</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2128330236081851</v>
+        <v>0.2218590212166747</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2386146077828128</v>
+        <v>0.2293568070637471</v>
       </c>
       <c r="C94">
-        <v>-3336.023468366154</v>
+        <v>-3298.292847242438</v>
       </c>
       <c r="D94">
-        <v>826.2125316338464</v>
+        <v>863.9431527575617</v>
       </c>
       <c r="E94">
         <v>3273.936</v>
@@ -9001,37 +9001,37 @@
         <v>227</v>
       </c>
       <c r="M94">
-        <v>1078.2842888</v>
+        <v>1034.4159288</v>
       </c>
       <c r="N94">
-        <v>-851.2842888000002</v>
+        <v>-807.4159288000001</v>
       </c>
       <c r="O94">
-        <v>-212.3103016267201</v>
+        <v>-201.36953264272</v>
       </c>
       <c r="P94">
-        <v>-638.9739871732802</v>
+        <v>-606.04639615728</v>
       </c>
       <c r="Q94">
-        <v>-638.2739871732801</v>
+        <v>-605.34639615728</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3043945050929746</v>
+        <v>0.303671996104653</v>
       </c>
       <c r="T94">
-        <v>5.968319903417428</v>
+        <v>5.955473351146719</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05250359352170873</v>
+        <v>0.05473020902305347</v>
       </c>
       <c r="W94">
-        <v>0.232894616712364</v>
+        <v>0.222894616712364</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2105196211776613</v>
+        <v>0.2194475101164934</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2406146077828128</v>
+        <v>0.2312568070637471</v>
       </c>
       <c r="C95">
-        <v>-3391.441299103709</v>
+        <v>-3354.010986619808</v>
       </c>
       <c r="D95">
-        <v>818.477700896291</v>
+        <v>855.9080133801921</v>
       </c>
       <c r="E95">
         <v>3321.619</v>
@@ -9083,37 +9083,37 @@
         <v>227</v>
       </c>
       <c r="M95">
-        <v>1090.0047702</v>
+        <v>1045.6595802</v>
       </c>
       <c r="N95">
-        <v>-863.0047702000002</v>
+        <v>-818.6595802000002</v>
       </c>
       <c r="O95">
-        <v>-215.23338968788</v>
+        <v>-204.17369930188</v>
       </c>
       <c r="P95">
-        <v>-647.7713805121201</v>
+        <v>-614.4858808981201</v>
       </c>
       <c r="Q95">
-        <v>-647.0713805121202</v>
+        <v>-613.78588089812</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3413365772491139</v>
+        <v>0.340510852691032</v>
       </c>
       <c r="T95">
-        <v>6.820937032477062</v>
+        <v>6.806255258453394</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05193903875265811</v>
+        <v>0.05414171215183784</v>
       </c>
       <c r="W95">
-        <v>0.2330333842745966</v>
+        <v>0.2230333842745967</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2082559693370413</v>
+        <v>0.2170878594700796</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2426146077828129</v>
+        <v>0.2331568070637471</v>
       </c>
       <c r="C96">
-        <v>-3446.715649307029</v>
+        <v>-3409.581040969383</v>
       </c>
       <c r="D96">
-        <v>810.8863506929712</v>
+        <v>848.0209590306174</v>
       </c>
       <c r="E96">
         <v>3369.302</v>
@@ -9165,37 +9165,37 @@
         <v>227</v>
       </c>
       <c r="M96">
-        <v>1101.7252516</v>
+        <v>1056.9032316</v>
       </c>
       <c r="N96">
-        <v>-874.7252516000001</v>
+        <v>-829.9032316</v>
       </c>
       <c r="O96">
-        <v>-218.15647774904</v>
+        <v>-206.97786596104</v>
       </c>
       <c r="P96">
-        <v>-656.56877385096</v>
+        <v>-622.92536563896</v>
       </c>
       <c r="Q96">
-        <v>-655.86877385096</v>
+        <v>-622.2253656389601</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.3905926734572997</v>
+        <v>0.3896293281395374</v>
       </c>
       <c r="T96">
-        <v>7.957759871223241</v>
+        <v>7.940631134862295</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05138649578720431</v>
+        <v>0.05356573649064809</v>
       </c>
       <c r="W96">
-        <v>0.2331691993355052</v>
+        <v>0.2231691993355052</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2060404803015409</v>
+        <v>0.2147784141565681</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2446146077828129</v>
+        <v>0.2350568070637472</v>
       </c>
       <c r="C97">
-        <v>-3501.850474617525</v>
+        <v>-3465.007066651425</v>
       </c>
       <c r="D97">
-        <v>803.4345253824748</v>
+        <v>840.2779333485752</v>
       </c>
       <c r="E97">
         <v>3416.985</v>
@@ -9247,37 +9247,37 @@
         <v>227</v>
       </c>
       <c r="M97">
-        <v>1113.445733</v>
+        <v>1068.146883</v>
       </c>
       <c r="N97">
-        <v>-886.4457330000002</v>
+        <v>-841.1468830000001</v>
       </c>
       <c r="O97">
-        <v>-221.0795658102001</v>
+        <v>-209.7820326202</v>
       </c>
       <c r="P97">
-        <v>-665.3661671898002</v>
+        <v>-631.3648503798001</v>
       </c>
       <c r="Q97">
-        <v>-664.6661671898003</v>
+        <v>-630.6648503798001</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.4595512081487598</v>
+        <v>0.4583951937674451</v>
       </c>
       <c r="T97">
-        <v>9.549311845467894</v>
+        <v>9.52875736183476</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05084558530523373</v>
+        <v>0.05300188663285178</v>
       </c>
       <c r="W97">
-        <v>0.2333021551319736</v>
+        <v>0.2233021551319736</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.203871633140472</v>
+        <v>0.2125175887443936</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2466146077828129</v>
+        <v>0.2369568070637471</v>
       </c>
       <c r="C98">
-        <v>-3556.849586595597</v>
+        <v>-3520.292973217019</v>
       </c>
       <c r="D98">
-        <v>796.1184134044034</v>
+        <v>832.6750267829811</v>
       </c>
       <c r="E98">
         <v>3464.668</v>
@@ -9329,37 +9329,37 @@
         <v>227</v>
       </c>
       <c r="M98">
-        <v>1125.1662144</v>
+        <v>1079.3905344</v>
       </c>
       <c r="N98">
-        <v>-898.1662144000002</v>
+        <v>-852.3905344000002</v>
       </c>
       <c r="O98">
-        <v>-224.0026538713601</v>
+        <v>-212.5861992793601</v>
       </c>
       <c r="P98">
-        <v>-674.1635605286401</v>
+        <v>-639.8043351206402</v>
       </c>
       <c r="Q98">
-        <v>-673.4635605286401</v>
+        <v>-639.1043351206401</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.5629890101859485</v>
+        <v>0.5615439922093052</v>
       </c>
       <c r="T98">
-        <v>11.93663980683484</v>
+        <v>11.91094670229342</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05031594379163754</v>
+        <v>0.05244978364709291</v>
       </c>
       <c r="W98">
-        <v>0.2334323410160155</v>
+        <v>0.2234323410160155</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2017479702952588</v>
+        <v>0.2103038638616396</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2486146077828128</v>
+        <v>0.2388568070637471</v>
       </c>
       <c r="C99">
-        <v>-3611.716659221471</v>
+        <v>-3575.442529990228</v>
       </c>
       <c r="D99">
-        <v>788.9343407785294</v>
+        <v>825.2084700097723</v>
       </c>
       <c r="E99">
         <v>3512.351</v>
@@ -9411,37 +9411,37 @@
         <v>227</v>
       </c>
       <c r="M99">
-        <v>1136.8866958</v>
+        <v>1090.6341858</v>
       </c>
       <c r="N99">
-        <v>-909.8866958000001</v>
+        <v>-863.6341858000001</v>
       </c>
       <c r="O99">
-        <v>-226.92574193252</v>
+        <v>-215.39036593852</v>
       </c>
       <c r="P99">
-        <v>-682.96095386748</v>
+        <v>-648.24381986148</v>
       </c>
       <c r="Q99">
-        <v>-682.2609538674801</v>
+        <v>-647.54381986148</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.7353853469145981</v>
+        <v>0.7334586562790737</v>
       </c>
       <c r="T99">
-        <v>15.91551974244646</v>
+        <v>15.88126226972456</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04979722272162066</v>
+        <v>0.05190906422805072</v>
       </c>
       <c r="W99">
-        <v>0.2335598426550257</v>
+        <v>0.2235598426550257</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1996680943128334</v>
+        <v>0.2081357827909011</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2506146077828129</v>
+        <v>0.2407568070637471</v>
       </c>
       <c r="C100">
-        <v>-3666.455235047219</v>
+        <v>-3630.459372299259</v>
       </c>
       <c r="D100">
-        <v>781.8787649527817</v>
+        <v>817.8746277007414</v>
       </c>
       <c r="E100">
         <v>3560.034</v>
@@ -9493,37 +9493,37 @@
         <v>227</v>
       </c>
       <c r="M100">
-        <v>1148.6071772</v>
+        <v>1101.8778372</v>
       </c>
       <c r="N100">
-        <v>-921.6071772</v>
+        <v>-874.8778372000002</v>
       </c>
       <c r="O100">
-        <v>-229.84882999368</v>
+        <v>-218.1945325976801</v>
       </c>
       <c r="P100">
-        <v>-691.75834720632</v>
+        <v>-656.68330460232</v>
       </c>
       <c r="Q100">
-        <v>-691.0583472063199</v>
+        <v>-655.98330460232</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.080178020371897</v>
+        <v>1.077287984418611</v>
       </c>
       <c r="T100">
-        <v>23.87327961366968</v>
+        <v>23.82189340458684</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04928908779588984</v>
+        <v>0.05137937989919305</v>
       </c>
       <c r="W100">
-        <v>0.2336847422197703</v>
+        <v>0.2236847422197703</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.197630664779029</v>
+        <v>0.2060119482726265</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2526146077828129</v>
+        <v>0.2426568070637471</v>
       </c>
       <c r="C101">
-        <v>-3721.06873102159</v>
+        <v>-3685.347007378296</v>
       </c>
       <c r="D101">
-        <v>774.9482689784101</v>
+        <v>810.6699926217045</v>
       </c>
       <c r="E101">
         <v>3607.717</v>
@@ -9575,37 +9575,37 @@
         <v>227</v>
       </c>
       <c r="M101">
-        <v>1160.3276586</v>
+        <v>1113.1214886</v>
       </c>
       <c r="N101">
-        <v>-933.3276586000002</v>
+        <v>-886.1214886</v>
       </c>
       <c r="O101">
-        <v>-232.7719180548401</v>
+        <v>-220.99869925684</v>
       </c>
       <c r="P101">
-        <v>-700.5557405451601</v>
+        <v>-665.12278934316</v>
       </c>
       <c r="Q101">
-        <v>-699.8557405451602</v>
+        <v>-664.42278934316</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.114556040743794</v>
+        <v>2.108775968837221</v>
       </c>
       <c r="T101">
-        <v>47.74655922733936</v>
+        <v>47.64378680917368</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.04879121822219398</v>
+        <v>0.05086039626384768</v>
       </c>
       <c r="W101">
-        <v>0.2338071185609847</v>
+        <v>0.2238071185609847</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.1956343954378267</v>
+        <v>0.2039310195021959</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_r_e_i_t.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06752358092304805</v>
+        <v>0.06738895411222597</v>
       </c>
       <c r="C2">
-        <v>4535.995704998334</v>
+        <v>4502.672192318373</v>
       </c>
       <c r="D2">
-        <v>4311.395704998334</v>
+        <v>4325.755192318373</v>
       </c>
       <c r="E2">
-        <v>-1112.9</v>
+        <v>-1065.217</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>47.683</v>
       </c>
       <c r="G2">
         <v>224.6</v>
@@ -1457,28 +1457,28 @@
         <v>227</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.3984549</v>
       </c>
       <c r="N2">
-        <v>227</v>
+        <v>224.6015451</v>
       </c>
       <c r="O2">
-        <v>56.6138</v>
+        <v>56.01562534794</v>
       </c>
       <c r="P2">
-        <v>170.3862</v>
+        <v>168.58591975206</v>
       </c>
       <c r="Q2">
-        <v>171.0862</v>
+        <v>169.28591975206</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06752358092304805</v>
+        <v>0.06768828516386462</v>
       </c>
       <c r="T2">
-        <v>0.5016993284768603</v>
+        <v>0.505503121567312</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>94.64426452213048</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06738895411222597</v>
+        <v>0.06725432730140389</v>
       </c>
       <c r="C3">
-        <v>4502.672192318373</v>
+        <v>4469.44465037994</v>
       </c>
       <c r="D3">
-        <v>4325.755192318373</v>
+        <v>4340.21065037994</v>
       </c>
       <c r="E3">
-        <v>-1065.217</v>
+        <v>-1017.534</v>
       </c>
       <c r="F3">
-        <v>47.683</v>
+        <v>95.366</v>
       </c>
       <c r="G3">
         <v>224.6</v>
@@ -1539,28 +1539,28 @@
         <v>227</v>
       </c>
       <c r="M3">
-        <v>2.3984549</v>
+        <v>4.7969098</v>
       </c>
       <c r="N3">
-        <v>224.6015451</v>
+        <v>222.2030902</v>
       </c>
       <c r="O3">
-        <v>56.01562534794</v>
+        <v>55.41745069588</v>
       </c>
       <c r="P3">
-        <v>168.58591975206</v>
+        <v>166.78563950412</v>
       </c>
       <c r="Q3">
-        <v>169.28591975206</v>
+        <v>167.48563950412</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06768828516386462</v>
+        <v>0.06785635071571826</v>
       </c>
       <c r="T3">
-        <v>0.505503121567312</v>
+        <v>0.5093845430881814</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>94.64426452213048</v>
+        <v>47.32213226106524</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06725432730140389</v>
+        <v>0.0671197004905818</v>
       </c>
       <c r="C4">
-        <v>4469.44465037994</v>
+        <v>4436.314044530693</v>
       </c>
       <c r="D4">
-        <v>4340.21065037994</v>
+        <v>4354.763044530692</v>
       </c>
       <c r="E4">
-        <v>-1017.534</v>
+        <v>-969.8510000000001</v>
       </c>
       <c r="F4">
-        <v>95.366</v>
+        <v>143.049</v>
       </c>
       <c r="G4">
         <v>224.6</v>
@@ -1621,28 +1621,28 @@
         <v>227</v>
       </c>
       <c r="M4">
-        <v>4.7969098</v>
+        <v>7.1953647</v>
       </c>
       <c r="N4">
-        <v>222.2030902</v>
+        <v>219.8046353</v>
       </c>
       <c r="O4">
-        <v>55.41745069588</v>
+        <v>54.81927604382</v>
       </c>
       <c r="P4">
-        <v>166.78563950412</v>
+        <v>164.98535925618</v>
       </c>
       <c r="Q4">
-        <v>167.48563950412</v>
+        <v>165.68535925618</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06785635071571826</v>
+        <v>0.06802788153668227</v>
       </c>
       <c r="T4">
-        <v>0.5093845430881814</v>
+        <v>0.5133459939187591</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>47.32213226106524</v>
+        <v>31.54808817404349</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0671197004905818</v>
+        <v>0.06698507367975973</v>
       </c>
       <c r="C5">
-        <v>4436.314044530693</v>
+        <v>4403.281353108786</v>
       </c>
       <c r="D5">
-        <v>4354.763044530692</v>
+        <v>4369.413353108785</v>
       </c>
       <c r="E5">
-        <v>-969.8510000000001</v>
+        <v>-922.1680000000001</v>
       </c>
       <c r="F5">
-        <v>143.049</v>
+        <v>190.732</v>
       </c>
       <c r="G5">
         <v>224.6</v>
@@ -1703,28 +1703,28 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>7.1953647</v>
+        <v>9.5938196</v>
       </c>
       <c r="N5">
-        <v>219.8046353</v>
+        <v>217.4061804</v>
       </c>
       <c r="O5">
-        <v>54.81927604382</v>
+        <v>54.22110139176001</v>
       </c>
       <c r="P5">
-        <v>164.98535925618</v>
+        <v>163.18507900824</v>
       </c>
       <c r="Q5">
-        <v>165.68535925618</v>
+        <v>163.88507900824</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06802788153668227</v>
+        <v>0.06820298591641638</v>
       </c>
       <c r="T5">
-        <v>0.5133459939187591</v>
+        <v>0.5173899749749741</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.54808817404349</v>
+        <v>23.66106613053262</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06698507367975973</v>
+        <v>0.06685044686893764</v>
       </c>
       <c r="C6">
-        <v>4403.281353108786</v>
+        <v>4370.347567662136</v>
       </c>
       <c r="D6">
-        <v>4369.413353108785</v>
+        <v>4384.162567662136</v>
       </c>
       <c r="E6">
-        <v>-922.1680000000001</v>
+        <v>-874.4850000000001</v>
       </c>
       <c r="F6">
-        <v>190.732</v>
+        <v>238.415</v>
       </c>
       <c r="G6">
         <v>224.6</v>
@@ -1785,28 +1785,28 @@
         <v>227</v>
       </c>
       <c r="M6">
-        <v>9.5938196</v>
+        <v>11.9922745</v>
       </c>
       <c r="N6">
-        <v>217.4061804</v>
+        <v>215.0077255</v>
       </c>
       <c r="O6">
-        <v>54.22110139176001</v>
+        <v>53.6229267397</v>
       </c>
       <c r="P6">
-        <v>163.18507900824</v>
+        <v>161.3847987603</v>
       </c>
       <c r="Q6">
-        <v>163.88507900824</v>
+        <v>162.0847987603</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06820298591641638</v>
+        <v>0.06838177670414489</v>
       </c>
       <c r="T6">
-        <v>0.5173899749749741</v>
+        <v>0.5215190924744777</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.66106613053262</v>
+        <v>18.92885290442609</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06685044686893764</v>
+        <v>0.06671582005811556</v>
       </c>
       <c r="C7">
-        <v>4370.347567662136</v>
+        <v>4337.513693172114</v>
       </c>
       <c r="D7">
-        <v>4384.162567662136</v>
+        <v>4399.011693172114</v>
       </c>
       <c r="E7">
-        <v>-874.4850000000001</v>
+        <v>-826.8020000000001</v>
       </c>
       <c r="F7">
-        <v>238.415</v>
+        <v>286.098</v>
       </c>
       <c r="G7">
         <v>224.6</v>
@@ -1867,28 +1867,28 @@
         <v>227</v>
       </c>
       <c r="M7">
-        <v>11.9922745</v>
+        <v>14.3907294</v>
       </c>
       <c r="N7">
-        <v>215.0077255</v>
+        <v>212.6092706</v>
       </c>
       <c r="O7">
-        <v>53.6229267397</v>
+        <v>53.02475208764</v>
       </c>
       <c r="P7">
-        <v>161.3847987603</v>
+        <v>159.58451851236</v>
       </c>
       <c r="Q7">
-        <v>162.0847987603</v>
+        <v>160.28451851236</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06838177670414489</v>
+        <v>0.06856437155118678</v>
       </c>
       <c r="T7">
-        <v>0.5215190924744777</v>
+        <v>0.5257360635378006</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.92885290442609</v>
+        <v>15.77404408702175</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06671582005811556</v>
+        <v>0.06658119324729349</v>
       </c>
       <c r="C8">
-        <v>4337.513693172114</v>
+        <v>4304.780748281824</v>
       </c>
       <c r="D8">
-        <v>4399.011693172114</v>
+        <v>4413.961748281824</v>
       </c>
       <c r="E8">
-        <v>-826.8020000000001</v>
+        <v>-779.1190000000001</v>
       </c>
       <c r="F8">
-        <v>286.098</v>
+        <v>333.781</v>
       </c>
       <c r="G8">
         <v>224.6</v>
@@ -1949,28 +1949,28 @@
         <v>227</v>
       </c>
       <c r="M8">
-        <v>14.3907294</v>
+        <v>16.7891843</v>
       </c>
       <c r="N8">
-        <v>212.6092706</v>
+        <v>210.2108157</v>
       </c>
       <c r="O8">
-        <v>53.02475208764</v>
+        <v>52.42657743558001</v>
       </c>
       <c r="P8">
-        <v>159.58451851236</v>
+        <v>157.78423826442</v>
       </c>
       <c r="Q8">
-        <v>160.28451851236</v>
+        <v>158.48423826442</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06856437155118678</v>
+        <v>0.06875089316913277</v>
       </c>
       <c r="T8">
-        <v>0.5257360635378006</v>
+        <v>0.5300437221508724</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.77404408702175</v>
+        <v>13.52060921744721</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06658119324729347</v>
+        <v>0.06653663843647141</v>
       </c>
       <c r="C9">
-        <v>4304.780748281826</v>
+        <v>4262.067881506794</v>
       </c>
       <c r="D9">
-        <v>4413.961748281826</v>
+        <v>4418.931881506794</v>
       </c>
       <c r="E9">
-        <v>-779.119</v>
+        <v>-731.4360000000001</v>
       </c>
       <c r="F9">
-        <v>333.7810000000001</v>
+        <v>381.464</v>
       </c>
       <c r="G9">
         <v>224.6</v>
@@ -2031,45 +2031,45 @@
         <v>227</v>
       </c>
       <c r="M9">
-        <v>16.7891843</v>
+        <v>19.7598352</v>
       </c>
       <c r="N9">
-        <v>210.2108157</v>
+        <v>207.2401648</v>
       </c>
       <c r="O9">
-        <v>52.42657743558001</v>
+        <v>51.68569710112001</v>
       </c>
       <c r="P9">
-        <v>157.78423826442</v>
+        <v>155.55446769888</v>
       </c>
       <c r="Q9">
-        <v>158.48423826442</v>
+        <v>156.25446769888</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06875089316913277</v>
+        <v>0.06894146960486022</v>
       </c>
       <c r="T9">
-        <v>0.5300437221508724</v>
+        <v>0.5344450255164022</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.2494</v>
       </c>
       <c r="W9">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.52060921744721</v>
+        <v>11.48795006144586</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06653663843647141</v>
+        <v>0.06641327062564932</v>
       </c>
       <c r="C10">
-        <v>4262.067881506794</v>
+        <v>4228.205267725571</v>
       </c>
       <c r="D10">
-        <v>4418.931881506794</v>
+        <v>4432.75226772557</v>
       </c>
       <c r="E10">
-        <v>-731.4360000000001</v>
+        <v>-683.7530000000002</v>
       </c>
       <c r="F10">
-        <v>381.464</v>
+        <v>429.147</v>
       </c>
       <c r="G10">
         <v>224.6</v>
@@ -2113,28 +2113,28 @@
         <v>227</v>
       </c>
       <c r="M10">
-        <v>19.7598352</v>
+        <v>22.2298146</v>
       </c>
       <c r="N10">
-        <v>207.2401648</v>
+        <v>204.7701854</v>
       </c>
       <c r="O10">
-        <v>51.68569710112001</v>
+        <v>51.06968423876</v>
       </c>
       <c r="P10">
-        <v>155.55446769888</v>
+        <v>153.70050116124</v>
       </c>
       <c r="Q10">
-        <v>156.25446769888</v>
+        <v>154.40050116124</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06894146960486022</v>
+        <v>0.06913623453368056</v>
       </c>
       <c r="T10">
-        <v>0.5344450255164022</v>
+        <v>0.5389430608240315</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.48795006144586</v>
+        <v>10.21151116572965</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06641327062564932</v>
+        <v>0.06641750481482724</v>
       </c>
       <c r="C11">
-        <v>4228.205267725571</v>
+        <v>4180.046496560328</v>
       </c>
       <c r="D11">
-        <v>4432.75226772557</v>
+        <v>4432.276496560327</v>
       </c>
       <c r="E11">
-        <v>-683.7530000000002</v>
+        <v>-636.0700000000002</v>
       </c>
       <c r="F11">
-        <v>429.147</v>
+        <v>476.83</v>
       </c>
       <c r="G11">
         <v>224.6</v>
@@ -2195,45 +2195,45 @@
         <v>227</v>
       </c>
       <c r="M11">
-        <v>22.2298146</v>
+        <v>25.510405</v>
       </c>
       <c r="N11">
-        <v>204.7701854</v>
+        <v>201.489595</v>
       </c>
       <c r="O11">
-        <v>51.06968423876</v>
+        <v>50.251504993</v>
       </c>
       <c r="P11">
-        <v>153.70050116124</v>
+        <v>151.238090007</v>
       </c>
       <c r="Q11">
-        <v>154.40050116124</v>
+        <v>151.938090007</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06913623453368056</v>
+        <v>0.06933532757203026</v>
       </c>
       <c r="T11">
-        <v>0.5389430608240315</v>
+        <v>0.5435410524718304</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.2494</v>
       </c>
       <c r="W11">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.21151116572965</v>
+        <v>8.898329916753577</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06641750481482724</v>
+        <v>0.06630689720400515</v>
       </c>
       <c r="C12">
-        <v>4180.046496560328</v>
+        <v>4144.825435503832</v>
       </c>
       <c r="D12">
-        <v>4432.276496560327</v>
+        <v>4444.738435503831</v>
       </c>
       <c r="E12">
-        <v>-636.0700000000001</v>
+        <v>-588.3870000000001</v>
       </c>
       <c r="F12">
-        <v>476.83</v>
+        <v>524.513</v>
       </c>
       <c r="G12">
         <v>224.6</v>
@@ -2277,28 +2277,28 @@
         <v>227</v>
       </c>
       <c r="M12">
-        <v>25.510405</v>
+        <v>28.0614455</v>
       </c>
       <c r="N12">
-        <v>201.489595</v>
+        <v>198.9385545</v>
       </c>
       <c r="O12">
-        <v>50.251504993</v>
+        <v>49.61527549230001</v>
       </c>
       <c r="P12">
-        <v>151.238090007</v>
+        <v>149.3232790077</v>
       </c>
       <c r="Q12">
-        <v>151.938090007</v>
+        <v>150.0232790077</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.06933532757203026</v>
+        <v>0.06953889461124174</v>
       </c>
       <c r="T12">
-        <v>0.5435410524718304</v>
+        <v>0.548242369774636</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.898329916753575</v>
+        <v>8.089390833412342</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06630689720400515</v>
+        <v>0.06626834719318307</v>
       </c>
       <c r="C13">
-        <v>4144.825435503832</v>
+        <v>4101.502272633771</v>
       </c>
       <c r="D13">
-        <v>4444.738435503831</v>
+        <v>4449.098272633771</v>
       </c>
       <c r="E13">
-        <v>-588.3870000000001</v>
+        <v>-540.7040000000001</v>
       </c>
       <c r="F13">
-        <v>524.513</v>
+        <v>572.196</v>
       </c>
       <c r="G13">
         <v>224.6</v>
@@ -2359,45 +2359,45 @@
         <v>227</v>
       </c>
       <c r="M13">
-        <v>28.0614455</v>
+        <v>31.0702428</v>
       </c>
       <c r="N13">
-        <v>198.9385545</v>
+        <v>195.9297572</v>
       </c>
       <c r="O13">
-        <v>49.61527549230001</v>
+        <v>48.86488144568</v>
       </c>
       <c r="P13">
-        <v>149.3232790077</v>
+        <v>147.06487575432</v>
       </c>
       <c r="Q13">
-        <v>150.0232790077</v>
+        <v>147.76487575432</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06953889461124174</v>
+        <v>0.06974708817407167</v>
       </c>
       <c r="T13">
-        <v>0.548242369774636</v>
+        <v>0.55305053519796</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.2494</v>
       </c>
       <c r="W13">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>8.089390833412342</v>
+        <v>7.306025944541378</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06626834719318307</v>
+        <v>0.06616374438236099</v>
       </c>
       <c r="C14">
-        <v>4101.502272633771</v>
+        <v>4065.692597909636</v>
       </c>
       <c r="D14">
-        <v>4449.098272633771</v>
+        <v>4460.971597909635</v>
       </c>
       <c r="E14">
-        <v>-540.7040000000001</v>
+        <v>-493.0210000000001</v>
       </c>
       <c r="F14">
-        <v>572.196</v>
+        <v>619.879</v>
       </c>
       <c r="G14">
         <v>224.6</v>
@@ -2441,28 +2441,28 @@
         <v>227</v>
       </c>
       <c r="M14">
-        <v>31.0702428</v>
+        <v>33.6594297</v>
       </c>
       <c r="N14">
-        <v>195.9297572</v>
+        <v>193.3405703</v>
       </c>
       <c r="O14">
-        <v>48.86488144568</v>
+        <v>48.21913823282</v>
       </c>
       <c r="P14">
-        <v>147.06487575432</v>
+        <v>145.12143206718</v>
       </c>
       <c r="Q14">
-        <v>147.76487575432</v>
+        <v>145.82143206718</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06974708817407167</v>
+        <v>0.06996006779581723</v>
       </c>
       <c r="T14">
-        <v>0.55305053519796</v>
+        <v>0.5579692331597512</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.306025944541378</v>
+        <v>6.744023948807427</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06616374438236099</v>
+        <v>0.06605914157153892</v>
       </c>
       <c r="C15">
-        <v>4065.692597909636</v>
+        <v>4029.946465536756</v>
       </c>
       <c r="D15">
-        <v>4460.971597909635</v>
+        <v>4472.908465536756</v>
       </c>
       <c r="E15">
-        <v>-493.0210000000001</v>
+        <v>-445.338</v>
       </c>
       <c r="F15">
-        <v>619.879</v>
+        <v>667.5620000000001</v>
       </c>
       <c r="G15">
         <v>224.6</v>
@@ -2523,28 +2523,28 @@
         <v>227</v>
       </c>
       <c r="M15">
-        <v>33.6594297</v>
+        <v>36.24861660000001</v>
       </c>
       <c r="N15">
-        <v>193.3405703</v>
+        <v>190.7513834</v>
       </c>
       <c r="O15">
-        <v>48.21913823282</v>
+        <v>47.57339501996</v>
       </c>
       <c r="P15">
-        <v>145.12143206718</v>
+        <v>143.17798838004</v>
       </c>
       <c r="Q15">
-        <v>145.82143206718</v>
+        <v>143.87798838004</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.06996006779581723</v>
+        <v>0.07017800043202199</v>
       </c>
       <c r="T15">
-        <v>0.5579692331597512</v>
+        <v>0.5630023194462351</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.744023948807427</v>
+        <v>6.262307952464039</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06605914157153892</v>
+        <v>0.06606712876071683</v>
       </c>
       <c r="C16">
-        <v>4029.946465536756</v>
+        <v>3981.349746190413</v>
       </c>
       <c r="D16">
-        <v>4472.908465536756</v>
+        <v>4471.994746190412</v>
       </c>
       <c r="E16">
-        <v>-445.338</v>
+        <v>-397.655</v>
       </c>
       <c r="F16">
-        <v>667.5620000000001</v>
+        <v>715.2450000000001</v>
       </c>
       <c r="G16">
         <v>224.6</v>
@@ -2605,45 +2605,45 @@
         <v>227</v>
       </c>
       <c r="M16">
-        <v>36.24861660000001</v>
+        <v>39.55304850000001</v>
       </c>
       <c r="N16">
-        <v>190.7513834</v>
+        <v>187.4469515</v>
       </c>
       <c r="O16">
-        <v>47.57339501996</v>
+        <v>46.74926970409999</v>
       </c>
       <c r="P16">
-        <v>143.17798838004</v>
+        <v>140.6976817959</v>
       </c>
       <c r="Q16">
-        <v>143.87798838004</v>
+        <v>141.3976817959</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07017800043202199</v>
+        <v>0.07040106089496097</v>
       </c>
       <c r="T16">
-        <v>0.5630023194462351</v>
+        <v>0.568153831292401</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.2494</v>
       </c>
       <c r="W16">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.262307952464039</v>
+        <v>5.739127794410081</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06606712876071681</v>
+        <v>0.06597003194989474</v>
       </c>
       <c r="C17">
-        <v>3981.349746190414</v>
+        <v>3944.79981581993</v>
       </c>
       <c r="D17">
-        <v>4471.994746190414</v>
+        <v>4483.127815819929</v>
       </c>
       <c r="E17">
-        <v>-397.6550000000001</v>
+        <v>-349.9720000000001</v>
       </c>
       <c r="F17">
-        <v>715.245</v>
+        <v>762.928</v>
       </c>
       <c r="G17">
         <v>224.6</v>
@@ -2687,28 +2687,28 @@
         <v>227</v>
       </c>
       <c r="M17">
-        <v>39.5530485</v>
+        <v>42.1899184</v>
       </c>
       <c r="N17">
-        <v>187.4469515</v>
+        <v>184.8100816</v>
       </c>
       <c r="O17">
-        <v>46.7492697041</v>
+        <v>46.09163435104</v>
       </c>
       <c r="P17">
-        <v>140.6976817959</v>
+        <v>138.71844724896</v>
       </c>
       <c r="Q17">
-        <v>141.3976817959</v>
+        <v>139.41844724896</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07040106089496097</v>
+        <v>0.07062943232130327</v>
       </c>
       <c r="T17">
-        <v>0.568153831292401</v>
+        <v>0.5734279981825233</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.739127794410082</v>
+        <v>5.380432307259452</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06597003194989474</v>
+        <v>0.06587293513907266</v>
       </c>
       <c r="C18">
-        <v>3944.79981581993</v>
+        <v>3908.305455538081</v>
       </c>
       <c r="D18">
-        <v>4483.127815819929</v>
+        <v>4494.316455538081</v>
       </c>
       <c r="E18">
-        <v>-349.9720000000001</v>
+        <v>-302.289</v>
       </c>
       <c r="F18">
-        <v>762.928</v>
+        <v>810.6110000000001</v>
       </c>
       <c r="G18">
         <v>224.6</v>
@@ -2769,28 +2769,28 @@
         <v>227</v>
       </c>
       <c r="M18">
-        <v>42.1899184</v>
+        <v>44.8267883</v>
       </c>
       <c r="N18">
-        <v>184.8100816</v>
+        <v>182.1732117</v>
       </c>
       <c r="O18">
-        <v>46.09163435104</v>
+        <v>45.43399899798</v>
       </c>
       <c r="P18">
-        <v>138.71844724896</v>
+        <v>136.73921270202</v>
       </c>
       <c r="Q18">
-        <v>139.41844724896</v>
+        <v>137.43921270202</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07062943232130327</v>
+        <v>0.07086330667358152</v>
       </c>
       <c r="T18">
-        <v>0.5734279981825233</v>
+        <v>0.5788292534314439</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.380432307259452</v>
+        <v>5.063936289185366</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06587293513907266</v>
+        <v>0.06577583832825058</v>
       </c>
       <c r="C19">
-        <v>3908.305455538081</v>
+        <v>3871.867082448282</v>
       </c>
       <c r="D19">
-        <v>4494.316455538081</v>
+        <v>4505.561082448281</v>
       </c>
       <c r="E19">
-        <v>-302.289</v>
+        <v>-254.606</v>
       </c>
       <c r="F19">
-        <v>810.6110000000001</v>
+        <v>858.2940000000001</v>
       </c>
       <c r="G19">
         <v>224.6</v>
@@ -2851,28 +2851,28 @@
         <v>227</v>
       </c>
       <c r="M19">
-        <v>44.8267883</v>
+        <v>47.4636582</v>
       </c>
       <c r="N19">
-        <v>182.1732117</v>
+        <v>179.5363418</v>
       </c>
       <c r="O19">
-        <v>45.43399899798</v>
+        <v>44.77636364492</v>
       </c>
       <c r="P19">
-        <v>136.73921270202</v>
+        <v>134.75997815508</v>
       </c>
       <c r="Q19">
-        <v>137.43921270202</v>
+        <v>135.45997815508</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07086330667358152</v>
+        <v>0.07110288527835437</v>
       </c>
       <c r="T19">
-        <v>0.5788292534314439</v>
+        <v>0.5843622466132647</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.063936289185366</v>
+        <v>4.782606495341735</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0657758383282506</v>
+        <v>0.0656787415174285</v>
       </c>
       <c r="C20">
-        <v>3871.867082448281</v>
+        <v>3835.485117838731</v>
       </c>
       <c r="D20">
-        <v>4505.56108244828</v>
+        <v>4516.86211783873</v>
       </c>
       <c r="E20">
-        <v>-254.6060000000001</v>
+        <v>-206.923</v>
       </c>
       <c r="F20">
-        <v>858.294</v>
+        <v>905.9770000000001</v>
       </c>
       <c r="G20">
         <v>224.6</v>
@@ -2933,28 +2933,28 @@
         <v>227</v>
       </c>
       <c r="M20">
-        <v>47.4636582</v>
+        <v>50.10052810000001</v>
       </c>
       <c r="N20">
-        <v>179.5363418</v>
+        <v>176.8994719</v>
       </c>
       <c r="O20">
-        <v>44.77636364492</v>
+        <v>44.11872829185999</v>
       </c>
       <c r="P20">
-        <v>134.75997815508</v>
+        <v>132.78074360814</v>
       </c>
       <c r="Q20">
-        <v>135.45997815508</v>
+        <v>133.48074360814</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07110288527835437</v>
+        <v>0.07134837940423271</v>
       </c>
       <c r="T20">
-        <v>0.5843622466132647</v>
+        <v>0.590031856910686</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.782606495341735</v>
+        <v>4.530890364007959</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0656787415174285</v>
+        <v>0.06595694470660643</v>
       </c>
       <c r="C21">
-        <v>3835.485117838731</v>
+        <v>3755.5726329409</v>
       </c>
       <c r="D21">
-        <v>4516.86211783873</v>
+        <v>4484.632632940899</v>
       </c>
       <c r="E21">
-        <v>-206.923</v>
+        <v>-159.24</v>
       </c>
       <c r="F21">
-        <v>905.9770000000001</v>
+        <v>953.6600000000001</v>
       </c>
       <c r="G21">
         <v>224.6</v>
@@ -3015,45 +3015,45 @@
         <v>227</v>
       </c>
       <c r="M21">
-        <v>50.10052810000001</v>
+        <v>55.12154800000001</v>
       </c>
       <c r="N21">
-        <v>176.8994719</v>
+        <v>171.878452</v>
       </c>
       <c r="O21">
-        <v>44.11872829185999</v>
+        <v>42.8664859288</v>
       </c>
       <c r="P21">
-        <v>132.78074360814</v>
+        <v>129.0119660712</v>
       </c>
       <c r="Q21">
-        <v>133.48074360814</v>
+        <v>129.7119660712</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07134837940423271</v>
+        <v>0.07160001088325803</v>
       </c>
       <c r="T21">
-        <v>0.590031856910686</v>
+        <v>0.5958432074655432</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.530890364007959</v>
+        <v>4.118171717528687</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06595694470660643</v>
+        <v>0.06643030389578433</v>
       </c>
       <c r="C22">
-        <v>3755.5726329409</v>
+        <v>3654.095959165702</v>
       </c>
       <c r="D22">
-        <v>4484.632632940899</v>
+        <v>4430.838959165702</v>
       </c>
       <c r="E22">
-        <v>-159.24</v>
+        <v>-111.5569999999999</v>
       </c>
       <c r="F22">
-        <v>953.6600000000001</v>
+        <v>1001.343</v>
       </c>
       <c r="G22">
         <v>224.6</v>
@@ -3097,45 +3097,45 @@
         <v>227</v>
       </c>
       <c r="M22">
-        <v>55.12154800000001</v>
+        <v>61.38232590000001</v>
       </c>
       <c r="N22">
-        <v>171.878452</v>
+        <v>165.6176741</v>
       </c>
       <c r="O22">
-        <v>42.8664859288</v>
+        <v>41.30504792054</v>
       </c>
       <c r="P22">
-        <v>129.0119660712</v>
+        <v>124.31262617946</v>
       </c>
       <c r="Q22">
-        <v>129.7119660712</v>
+        <v>125.01262617946</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07160001088325803</v>
+        <v>0.07185801277947385</v>
       </c>
       <c r="T22">
-        <v>0.5958432074655432</v>
+        <v>0.6018016808192572</v>
       </c>
       <c r="U22">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V22">
         <v>0.2494</v>
       </c>
       <c r="W22">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.118171717528687</v>
+        <v>3.698132918094587</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06643030389578433</v>
+        <v>0.06637824308496226</v>
       </c>
       <c r="C23">
-        <v>3654.095959165703</v>
+        <v>3612.266029338914</v>
       </c>
       <c r="D23">
-        <v>4430.838959165702</v>
+        <v>4436.692029338913</v>
       </c>
       <c r="E23">
-        <v>-111.5570000000001</v>
+        <v>-63.87400000000002</v>
       </c>
       <c r="F23">
-        <v>1001.343</v>
+        <v>1049.026</v>
       </c>
       <c r="G23">
         <v>224.6</v>
@@ -3179,28 +3179,28 @@
         <v>227</v>
       </c>
       <c r="M23">
-        <v>61.3823259</v>
+        <v>64.3052938</v>
       </c>
       <c r="N23">
-        <v>165.6176741</v>
+        <v>162.6947062</v>
       </c>
       <c r="O23">
-        <v>41.30504792054</v>
+        <v>40.57605972628</v>
       </c>
       <c r="P23">
-        <v>124.31262617946</v>
+        <v>122.11864647372</v>
       </c>
       <c r="Q23">
-        <v>125.01262617946</v>
+        <v>122.81864647372</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07185801277947385</v>
+        <v>0.07212263010892597</v>
       </c>
       <c r="T23">
-        <v>0.6018016808192572</v>
+        <v>0.6079129355410153</v>
       </c>
       <c r="U23">
         <v>0.0613</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.698132918094588</v>
+        <v>3.530035967272106</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06637824308496226</v>
+        <v>0.06680956867414017</v>
       </c>
       <c r="C24">
-        <v>3612.266029338914</v>
+        <v>3516.551758991377</v>
       </c>
       <c r="D24">
-        <v>4436.692029338913</v>
+        <v>4388.660758991376</v>
       </c>
       <c r="E24">
-        <v>-63.87400000000002</v>
+        <v>-16.19100000000003</v>
       </c>
       <c r="F24">
-        <v>1049.026</v>
+        <v>1096.709</v>
       </c>
       <c r="G24">
         <v>224.6</v>
@@ -3261,45 +3261,45 @@
         <v>227</v>
       </c>
       <c r="M24">
-        <v>64.3052938</v>
+        <v>70.29904690000001</v>
       </c>
       <c r="N24">
-        <v>162.6947062</v>
+        <v>156.7009531</v>
       </c>
       <c r="O24">
-        <v>40.57605972628</v>
+        <v>39.08121770314</v>
       </c>
       <c r="P24">
-        <v>122.11864647372</v>
+        <v>117.61973539686</v>
       </c>
       <c r="Q24">
-        <v>122.81864647372</v>
+        <v>118.31973539686</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07212263010892597</v>
+        <v>0.07239412061576646</v>
       </c>
       <c r="T24">
-        <v>0.6079129355410153</v>
+        <v>0.6141829241516502</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.530035967272106</v>
+        <v>3.229062270544097</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06680956867414017</v>
+        <v>0.06677852466331809</v>
       </c>
       <c r="C25">
-        <v>3516.551758991377</v>
+        <v>3472.290979016546</v>
       </c>
       <c r="D25">
-        <v>4388.660758991376</v>
+        <v>4392.082979016545</v>
       </c>
       <c r="E25">
-        <v>-16.19100000000003</v>
+        <v>31.49199999999996</v>
       </c>
       <c r="F25">
-        <v>1096.709</v>
+        <v>1144.392</v>
       </c>
       <c r="G25">
         <v>224.6</v>
@@ -3343,28 +3343,28 @@
         <v>227</v>
       </c>
       <c r="M25">
-        <v>70.29904690000001</v>
+        <v>73.35552720000001</v>
       </c>
       <c r="N25">
-        <v>156.7009531</v>
+        <v>153.6444728</v>
       </c>
       <c r="O25">
-        <v>39.08121770314</v>
+        <v>38.31893151632</v>
       </c>
       <c r="P25">
-        <v>117.61973539686</v>
+        <v>115.32554128368</v>
       </c>
       <c r="Q25">
-        <v>118.31973539686</v>
+        <v>116.02554128368</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07239412061576646</v>
+        <v>0.07267275560962906</v>
       </c>
       <c r="T25">
-        <v>0.6141829241516502</v>
+        <v>0.6206179124625649</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.229062270544097</v>
+        <v>3.094518009271426</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06677852466331809</v>
+        <v>0.068211150652496</v>
       </c>
       <c r="C26">
-        <v>3472.290979016546</v>
+        <v>3272.04552758392</v>
       </c>
       <c r="D26">
-        <v>4392.082979016545</v>
+        <v>4239.52052758392</v>
       </c>
       <c r="E26">
-        <v>31.49199999999996</v>
+        <v>79.17499999999995</v>
       </c>
       <c r="F26">
-        <v>1144.392</v>
+        <v>1192.075</v>
       </c>
       <c r="G26">
         <v>224.6</v>
@@ -3425,45 +3425,45 @@
         <v>227</v>
       </c>
       <c r="M26">
-        <v>73.35552720000001</v>
+        <v>85.71019250000001</v>
       </c>
       <c r="N26">
-        <v>153.6444728</v>
+        <v>141.2898075</v>
       </c>
       <c r="O26">
-        <v>38.31893151632</v>
+        <v>35.2376779905</v>
       </c>
       <c r="P26">
-        <v>115.32554128368</v>
+        <v>106.0521295095</v>
       </c>
       <c r="Q26">
-        <v>116.02554128368</v>
+        <v>106.7521295095</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07267275560962906</v>
+        <v>0.07295882086999467</v>
       </c>
       <c r="T26">
-        <v>0.6206179124625649</v>
+        <v>0.6272245004617707</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.094518009271426</v>
+        <v>2.64845980832443</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.068211150652496</v>
+        <v>0.06823865344167393</v>
       </c>
       <c r="C27">
-        <v>3272.04552758392</v>
+        <v>3221.537333613426</v>
       </c>
       <c r="D27">
-        <v>4239.52052758392</v>
+        <v>4236.695333613426</v>
       </c>
       <c r="E27">
-        <v>79.17499999999995</v>
+        <v>126.8579999999999</v>
       </c>
       <c r="F27">
-        <v>1192.075</v>
+        <v>1239.758</v>
       </c>
       <c r="G27">
         <v>224.6</v>
@@ -3507,28 +3507,28 @@
         <v>227</v>
       </c>
       <c r="M27">
-        <v>85.71019250000001</v>
+        <v>89.13860020000001</v>
       </c>
       <c r="N27">
-        <v>141.2898075</v>
+        <v>137.8613998</v>
       </c>
       <c r="O27">
-        <v>35.2376779905</v>
+        <v>34.38263311012</v>
       </c>
       <c r="P27">
-        <v>106.0521295095</v>
+        <v>103.47876668988</v>
       </c>
       <c r="Q27">
-        <v>106.7521295095</v>
+        <v>104.17876668988</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07295882086999467</v>
+        <v>0.07325261762388369</v>
       </c>
       <c r="T27">
-        <v>0.6272245004617707</v>
+        <v>0.6340096448933875</v>
       </c>
       <c r="U27">
         <v>0.07190000000000001</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.64845980832443</v>
+        <v>2.546595969542721</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06823865344167393</v>
+        <v>0.06905653803085185</v>
       </c>
       <c r="C28">
-        <v>3221.537333613426</v>
+        <v>3091.525563464957</v>
       </c>
       <c r="D28">
-        <v>4236.695333613426</v>
+        <v>4154.366563464957</v>
       </c>
       <c r="E28">
-        <v>126.8579999999999</v>
+        <v>174.5409999999999</v>
       </c>
       <c r="F28">
-        <v>1239.758</v>
+        <v>1287.441</v>
       </c>
       <c r="G28">
         <v>224.6</v>
@@ -3589,45 +3589,45 @@
         <v>227</v>
       </c>
       <c r="M28">
-        <v>89.13860020000001</v>
+        <v>97.58802780000001</v>
       </c>
       <c r="N28">
-        <v>137.8613998</v>
+        <v>129.4119722</v>
       </c>
       <c r="O28">
-        <v>34.38263311012</v>
+        <v>32.27534586668</v>
       </c>
       <c r="P28">
-        <v>103.47876668988</v>
+        <v>97.13662633331998</v>
       </c>
       <c r="Q28">
-        <v>104.17876668988</v>
+        <v>97.83662633331997</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07325261762388369</v>
+        <v>0.07355446360390663</v>
       </c>
       <c r="T28">
-        <v>0.6340096448933875</v>
+        <v>0.6409806836929938</v>
       </c>
       <c r="U28">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.2494</v>
       </c>
       <c r="W28">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.546595969542721</v>
+        <v>2.326105006089692</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06905653803085185</v>
+        <v>0.06911331422002975</v>
       </c>
       <c r="C29">
-        <v>3091.525563464957</v>
+        <v>3038.246044610336</v>
       </c>
       <c r="D29">
-        <v>4154.366563464957</v>
+        <v>4148.770044610335</v>
       </c>
       <c r="E29">
-        <v>174.5409999999999</v>
+        <v>222.2240000000002</v>
       </c>
       <c r="F29">
-        <v>1287.441</v>
+        <v>1335.124</v>
       </c>
       <c r="G29">
         <v>224.6</v>
@@ -3671,28 +3671,28 @@
         <v>227</v>
       </c>
       <c r="M29">
-        <v>97.58802780000001</v>
+        <v>101.2023992</v>
       </c>
       <c r="N29">
-        <v>129.4119722</v>
+        <v>125.7976008</v>
       </c>
       <c r="O29">
-        <v>32.27534586668</v>
+        <v>31.37392163952</v>
       </c>
       <c r="P29">
-        <v>97.13662633331998</v>
+        <v>94.42367916047998</v>
       </c>
       <c r="Q29">
-        <v>97.83662633331997</v>
+        <v>95.12367916047997</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07355446360390663</v>
+        <v>0.07386469419448578</v>
       </c>
       <c r="T29">
-        <v>0.6409806836929938</v>
+        <v>0.6481453624592558</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.326105006089692</v>
+        <v>2.243029827300774</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06911331422002975</v>
+        <v>0.06917009040920769</v>
       </c>
       <c r="C30">
-        <v>3038.246044610336</v>
+        <v>2984.981584073621</v>
       </c>
       <c r="D30">
-        <v>4148.770044610335</v>
+        <v>4143.18858407362</v>
       </c>
       <c r="E30">
-        <v>222.2240000000002</v>
+        <v>269.9070000000002</v>
       </c>
       <c r="F30">
-        <v>1335.124</v>
+        <v>1382.807</v>
       </c>
       <c r="G30">
         <v>224.6</v>
@@ -3753,28 +3753,28 @@
         <v>227</v>
       </c>
       <c r="M30">
-        <v>101.2023992</v>
+        <v>104.8167706</v>
       </c>
       <c r="N30">
-        <v>125.7976008</v>
+        <v>122.1832294</v>
       </c>
       <c r="O30">
-        <v>31.37392163952</v>
+        <v>30.47249741236</v>
       </c>
       <c r="P30">
-        <v>94.42367916047998</v>
+        <v>91.71073198763997</v>
       </c>
       <c r="Q30">
-        <v>95.12367916047997</v>
+        <v>92.41073198763996</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07386469419448578</v>
+        <v>0.07418366367494039</v>
       </c>
       <c r="T30">
-        <v>0.6481453624592558</v>
+        <v>0.6555118631625957</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.243029827300774</v>
+        <v>2.165683971186954</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06917009040920767</v>
+        <v>0.06922686659838559</v>
       </c>
       <c r="C31">
-        <v>2984.981584073622</v>
+        <v>2931.732121161295</v>
       </c>
       <c r="D31">
-        <v>4143.188584073621</v>
+        <v>4137.622121161295</v>
       </c>
       <c r="E31">
-        <v>269.9069999999999</v>
+        <v>317.5899999999999</v>
       </c>
       <c r="F31">
-        <v>1382.807</v>
+        <v>1430.49</v>
       </c>
       <c r="G31">
         <v>224.6</v>
@@ -3835,28 +3835,28 @@
         <v>227</v>
       </c>
       <c r="M31">
-        <v>104.8167706</v>
+        <v>108.431142</v>
       </c>
       <c r="N31">
-        <v>122.1832294</v>
+        <v>118.568858</v>
       </c>
       <c r="O31">
-        <v>30.47249741236</v>
+        <v>29.5710731852</v>
       </c>
       <c r="P31">
-        <v>91.71073198763999</v>
+        <v>88.99778481479999</v>
       </c>
       <c r="Q31">
-        <v>92.41073198763998</v>
+        <v>89.69778481479997</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07418366367494039</v>
+        <v>0.07451174656912228</v>
       </c>
       <c r="T31">
-        <v>0.6555118631625956</v>
+        <v>0.6630888353146023</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.165683971186954</v>
+        <v>2.093494505480722</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06922686659838559</v>
+        <v>0.06928364278756351</v>
       </c>
       <c r="C32">
-        <v>2931.732121161295</v>
+        <v>2878.497595505568</v>
       </c>
       <c r="D32">
-        <v>4137.622121161295</v>
+        <v>4132.070595505567</v>
       </c>
       <c r="E32">
-        <v>317.5899999999999</v>
+        <v>365.2729999999999</v>
       </c>
       <c r="F32">
-        <v>1430.49</v>
+        <v>1478.173</v>
       </c>
       <c r="G32">
         <v>224.6</v>
@@ -3917,28 +3917,28 @@
         <v>227</v>
       </c>
       <c r="M32">
-        <v>108.431142</v>
+        <v>112.0455134</v>
       </c>
       <c r="N32">
-        <v>118.568858</v>
+        <v>114.9544866</v>
       </c>
       <c r="O32">
-        <v>29.5710731852</v>
+        <v>28.66964895804</v>
       </c>
       <c r="P32">
-        <v>88.99778481479999</v>
+        <v>86.28483764196</v>
       </c>
       <c r="Q32">
-        <v>89.69778481479997</v>
+        <v>86.98483764195998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07451174656912228</v>
+        <v>0.07484933911241089</v>
       </c>
       <c r="T32">
-        <v>0.6630888353146023</v>
+        <v>0.6708854298478265</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.093494505480722</v>
+        <v>2.025962424658764</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06928364278756351</v>
+        <v>0.07275114537674143</v>
       </c>
       <c r="C33">
-        <v>2878.497595505568</v>
+        <v>2517.864264385772</v>
       </c>
       <c r="D33">
-        <v>4132.070595505567</v>
+        <v>3819.120264385772</v>
       </c>
       <c r="E33">
-        <v>365.2729999999999</v>
+        <v>412.9559999999999</v>
       </c>
       <c r="F33">
-        <v>1478.173</v>
+        <v>1525.856</v>
       </c>
       <c r="G33">
         <v>224.6</v>
@@ -3999,45 +3999,45 @@
         <v>227</v>
       </c>
       <c r="M33">
-        <v>112.0455134</v>
+        <v>137.32704</v>
       </c>
       <c r="N33">
-        <v>114.9544866</v>
+        <v>89.67296000000002</v>
       </c>
       <c r="O33">
-        <v>28.66964895804</v>
+        <v>22.36443622400001</v>
       </c>
       <c r="P33">
-        <v>86.28483764196</v>
+        <v>67.30852377600002</v>
       </c>
       <c r="Q33">
-        <v>86.98483764195998</v>
+        <v>68.008523776</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07484933911241089</v>
+        <v>0.07519686084814917</v>
       </c>
       <c r="T33">
-        <v>0.6708854298478265</v>
+        <v>0.6789113359849691</v>
       </c>
       <c r="U33">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V33">
         <v>0.2494</v>
       </c>
       <c r="W33">
-        <v>0.05689548</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.025962424658764</v>
+        <v>1.652988369952487</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07275114537674143</v>
+        <v>0.07291450676591935</v>
       </c>
       <c r="C34">
-        <v>2517.864264385772</v>
+        <v>2456.602608537588</v>
       </c>
       <c r="D34">
-        <v>3819.120264385772</v>
+        <v>3805.541608537589</v>
       </c>
       <c r="E34">
-        <v>412.9559999999999</v>
+        <v>460.6390000000001</v>
       </c>
       <c r="F34">
-        <v>1525.856</v>
+        <v>1573.539</v>
       </c>
       <c r="G34">
         <v>224.6</v>
@@ -4081,28 +4081,28 @@
         <v>227</v>
       </c>
       <c r="M34">
-        <v>137.32704</v>
+        <v>141.61851</v>
       </c>
       <c r="N34">
-        <v>89.67296000000002</v>
+        <v>85.38148999999999</v>
       </c>
       <c r="O34">
-        <v>22.36443622400001</v>
+        <v>21.294143606</v>
       </c>
       <c r="P34">
-        <v>67.30852377600002</v>
+        <v>64.08734639399998</v>
       </c>
       <c r="Q34">
-        <v>68.008523776</v>
+        <v>64.78734639399997</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07519686084814917</v>
+        <v>0.07555475636704381</v>
       </c>
       <c r="T34">
-        <v>0.6789113359849691</v>
+        <v>0.6871768214097876</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.652988369952487</v>
+        <v>1.60289781328726</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07291450676591935</v>
+        <v>0.07307786815509726</v>
       </c>
       <c r="C35">
-        <v>2456.602608537588</v>
+        <v>2395.437166818655</v>
       </c>
       <c r="D35">
-        <v>3805.541608537589</v>
+        <v>3792.059166818656</v>
       </c>
       <c r="E35">
-        <v>460.6390000000001</v>
+        <v>508.3220000000001</v>
       </c>
       <c r="F35">
-        <v>1573.539</v>
+        <v>1621.222</v>
       </c>
       <c r="G35">
         <v>224.6</v>
@@ -4163,28 +4163,28 @@
         <v>227</v>
       </c>
       <c r="M35">
-        <v>141.61851</v>
+        <v>145.90998</v>
       </c>
       <c r="N35">
-        <v>85.38148999999999</v>
+        <v>81.09001999999998</v>
       </c>
       <c r="O35">
-        <v>21.294143606</v>
+        <v>20.223850988</v>
       </c>
       <c r="P35">
-        <v>64.08734639399998</v>
+        <v>60.86616901199999</v>
       </c>
       <c r="Q35">
-        <v>64.78734639399997</v>
+        <v>61.56616901199997</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07555475636704381</v>
+        <v>0.07592349720469282</v>
       </c>
       <c r="T35">
-        <v>0.6871768214097876</v>
+        <v>0.6956927760899037</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.60289781328726</v>
+        <v>1.555753759955282</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07307786815509726</v>
+        <v>0.07324122954427519</v>
       </c>
       <c r="C36">
-        <v>2395.437166818655</v>
+        <v>2334.366920224084</v>
       </c>
       <c r="D36">
-        <v>3792.059166818656</v>
+        <v>3778.671920224084</v>
       </c>
       <c r="E36">
-        <v>508.3220000000001</v>
+        <v>556.0050000000001</v>
       </c>
       <c r="F36">
-        <v>1621.222</v>
+        <v>1668.905</v>
       </c>
       <c r="G36">
         <v>224.6</v>
@@ -4245,28 +4245,28 @@
         <v>227</v>
       </c>
       <c r="M36">
-        <v>145.90998</v>
+        <v>150.20145</v>
       </c>
       <c r="N36">
-        <v>81.09001999999998</v>
+        <v>76.79854999999998</v>
       </c>
       <c r="O36">
-        <v>20.223850988</v>
+        <v>19.15355837</v>
       </c>
       <c r="P36">
-        <v>60.86616901199999</v>
+        <v>57.64499162999998</v>
       </c>
       <c r="Q36">
-        <v>61.56616901199997</v>
+        <v>58.34499162999997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07592349720469282</v>
+        <v>0.07630358391426953</v>
       </c>
       <c r="T36">
-        <v>0.6956927760899037</v>
+        <v>0.7044707601447926</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.555753759955282</v>
+        <v>1.511303652527988</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07324122954427519</v>
+        <v>0.09025365931247906</v>
       </c>
       <c r="C37">
-        <v>2334.366920224084</v>
+        <v>1270.908495818974</v>
       </c>
       <c r="D37">
-        <v>3778.671920224084</v>
+        <v>2762.896495818974</v>
       </c>
       <c r="E37">
-        <v>556.0050000000001</v>
+        <v>603.6880000000001</v>
       </c>
       <c r="F37">
-        <v>1668.905</v>
+        <v>1716.588</v>
       </c>
       <c r="G37">
         <v>224.6</v>
@@ -4327,45 +4327,45 @@
         <v>227</v>
       </c>
       <c r="M37">
-        <v>150.20145</v>
+        <v>251.9951184000001</v>
       </c>
       <c r="N37">
-        <v>76.79854999999998</v>
+        <v>-24.99511840000005</v>
       </c>
       <c r="O37">
-        <v>19.15355837</v>
+        <v>-6.233782528960013</v>
       </c>
       <c r="P37">
-        <v>57.64499162999998</v>
+        <v>-18.76133587104004</v>
       </c>
       <c r="Q37">
-        <v>58.34499162999997</v>
+        <v>-18.06133587104005</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07630358391426953</v>
+        <v>0.07699783115172529</v>
       </c>
       <c r="T37">
-        <v>0.7044707601447926</v>
+        <v>0.7205041836426164</v>
       </c>
       <c r="U37">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.2494</v>
+        <v>0.2246622885374115</v>
       </c>
       <c r="W37">
-        <v>0.06755399999999999</v>
+        <v>0.113819576042708</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.511303652527988</v>
+        <v>0.9008111007915459</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09025365931247906</v>
+        <v>0.09126365931247907</v>
       </c>
       <c r="C38">
-        <v>1270.908495818974</v>
+        <v>1179.824284224287</v>
       </c>
       <c r="D38">
-        <v>2762.896495818974</v>
+        <v>2719.495284224287</v>
       </c>
       <c r="E38">
-        <v>603.6879999999999</v>
+        <v>651.3709999999999</v>
       </c>
       <c r="F38">
-        <v>1716.588</v>
+        <v>1764.271</v>
       </c>
       <c r="G38">
         <v>224.6</v>
@@ -4409,37 +4409,37 @@
         <v>227</v>
       </c>
       <c r="M38">
-        <v>251.9951184</v>
+        <v>258.9949828</v>
       </c>
       <c r="N38">
-        <v>-24.99511840000002</v>
+        <v>-31.9949828</v>
       </c>
       <c r="O38">
-        <v>-6.233782528960006</v>
+        <v>-7.979548710320001</v>
       </c>
       <c r="P38">
-        <v>-18.76133587104002</v>
+        <v>-24.01543408968</v>
       </c>
       <c r="Q38">
-        <v>-18.06133587104003</v>
+        <v>-23.31543408968001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07699783115172529</v>
+        <v>0.07749303482080029</v>
       </c>
       <c r="T38">
-        <v>0.7205041836426164</v>
+        <v>0.7319407579861499</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.2246622885374116</v>
+        <v>0.2185903347931572</v>
       </c>
       <c r="W38">
-        <v>0.113819576042708</v>
+        <v>0.1147109388523645</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.900811100791546</v>
+        <v>0.876464854824207</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09126365931247907</v>
+        <v>0.09227365931247905</v>
       </c>
       <c r="C39">
-        <v>1179.824284224287</v>
+        <v>1090.082528323387</v>
       </c>
       <c r="D39">
-        <v>2719.495284224287</v>
+        <v>2677.436528323387</v>
       </c>
       <c r="E39">
-        <v>651.3709999999999</v>
+        <v>699.0540000000001</v>
       </c>
       <c r="F39">
-        <v>1764.271</v>
+        <v>1811.954</v>
       </c>
       <c r="G39">
         <v>224.6</v>
@@ -4491,37 +4491,37 @@
         <v>227</v>
       </c>
       <c r="M39">
-        <v>258.9949828</v>
+        <v>265.9948472</v>
       </c>
       <c r="N39">
-        <v>-31.9949828</v>
+        <v>-38.99484720000004</v>
       </c>
       <c r="O39">
-        <v>-7.979548710320001</v>
+        <v>-9.725314891680011</v>
       </c>
       <c r="P39">
-        <v>-24.01543408968</v>
+        <v>-29.26953230832003</v>
       </c>
       <c r="Q39">
-        <v>-23.31543408968001</v>
+        <v>-28.56953230832004</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07749303482080029</v>
+        <v>0.07800421280178094</v>
       </c>
       <c r="T39">
-        <v>0.7319407579861499</v>
+        <v>0.7437462540827007</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.2185903347931572</v>
+        <v>0.2128379575617584</v>
       </c>
       <c r="W39">
-        <v>0.1147109388523645</v>
+        <v>0.1155553878299339</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.876464854824207</v>
+        <v>0.8533999902235698</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09227365931247905</v>
+        <v>0.09328365931247906</v>
       </c>
       <c r="C40">
-        <v>1090.082528323387</v>
+        <v>1001.6218908958</v>
       </c>
       <c r="D40">
-        <v>2677.436528323387</v>
+        <v>2636.658890895801</v>
       </c>
       <c r="E40">
-        <v>699.0540000000001</v>
+        <v>746.7370000000001</v>
       </c>
       <c r="F40">
-        <v>1811.954</v>
+        <v>1859.637</v>
       </c>
       <c r="G40">
         <v>224.6</v>
@@ -4573,37 +4573,37 @@
         <v>227</v>
       </c>
       <c r="M40">
-        <v>265.9948472</v>
+        <v>272.9947116000001</v>
       </c>
       <c r="N40">
-        <v>-38.99484720000004</v>
+        <v>-45.99471160000007</v>
       </c>
       <c r="O40">
-        <v>-9.725314891680011</v>
+        <v>-11.47108107304002</v>
       </c>
       <c r="P40">
-        <v>-29.26953230832003</v>
+        <v>-34.52363052696005</v>
       </c>
       <c r="Q40">
-        <v>-28.56953230832004</v>
+        <v>-33.82363052696007</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07800421280178094</v>
+        <v>0.07853215071656425</v>
       </c>
       <c r="T40">
-        <v>0.7437462540827007</v>
+        <v>0.7559388156250401</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.2128379575617584</v>
+        <v>0.2073805740345337</v>
       </c>
       <c r="W40">
-        <v>0.1155553878299339</v>
+        <v>0.1163565317317305</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8533999902235698</v>
+        <v>0.8315179391921962</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09328365931247906</v>
+        <v>0.09429365931247906</v>
       </c>
       <c r="C41">
-        <v>1001.6218908958</v>
+        <v>914.384715353689</v>
       </c>
       <c r="D41">
-        <v>2636.658890895801</v>
+        <v>2597.104715353689</v>
       </c>
       <c r="E41">
-        <v>746.7370000000001</v>
+        <v>794.4200000000001</v>
       </c>
       <c r="F41">
-        <v>1859.637</v>
+        <v>1907.32</v>
       </c>
       <c r="G41">
         <v>224.6</v>
@@ -4655,37 +4655,37 @@
         <v>227</v>
       </c>
       <c r="M41">
-        <v>272.9947116000001</v>
+        <v>279.9945760000001</v>
       </c>
       <c r="N41">
-        <v>-45.99471160000007</v>
+        <v>-52.99457600000005</v>
       </c>
       <c r="O41">
-        <v>-11.47108107304002</v>
+        <v>-13.21684725440001</v>
       </c>
       <c r="P41">
-        <v>-34.52363052696005</v>
+        <v>-39.77772874560004</v>
       </c>
       <c r="Q41">
-        <v>-33.82363052696007</v>
+        <v>-39.07772874560005</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07853215071656425</v>
+        <v>0.0790776865618403</v>
       </c>
       <c r="T41">
-        <v>0.7559388156250401</v>
+        <v>0.7685377958854575</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.2073805740345337</v>
+        <v>0.2021960596836704</v>
       </c>
       <c r="W41">
-        <v>0.1163565317317305</v>
+        <v>0.1171176184384372</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8315179391921962</v>
+        <v>0.8107299907123914</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09429365931247906</v>
+        <v>0.1179161509720457</v>
       </c>
       <c r="C42">
-        <v>914.384715353689</v>
+        <v>192.1433436039538</v>
       </c>
       <c r="D42">
-        <v>2597.104715353689</v>
+        <v>1922.546343603954</v>
       </c>
       <c r="E42">
-        <v>794.4200000000001</v>
+        <v>842.1030000000001</v>
       </c>
       <c r="F42">
-        <v>1907.32</v>
+        <v>1955.003</v>
       </c>
       <c r="G42">
         <v>224.6</v>
@@ -4737,45 +4737,45 @@
         <v>227</v>
       </c>
       <c r="M42">
-        <v>279.9945760000001</v>
+        <v>392.5646024000001</v>
       </c>
       <c r="N42">
-        <v>-52.99457600000005</v>
+        <v>-165.5646024000001</v>
       </c>
       <c r="O42">
-        <v>-13.21684725440001</v>
+        <v>-41.29181183856002</v>
       </c>
       <c r="P42">
-        <v>-39.77772874560004</v>
+        <v>-124.27279056144</v>
       </c>
       <c r="Q42">
-        <v>-39.07772874560005</v>
+        <v>-123.5727905614401</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0790776865618403</v>
+        <v>0.08044254846893351</v>
       </c>
       <c r="T42">
-        <v>0.7685377958854575</v>
+        <v>0.8000588560954618</v>
       </c>
       <c r="U42">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.2021960596836704</v>
+        <v>0.144215244201549</v>
       </c>
       <c r="W42">
-        <v>0.1171176184384372</v>
+        <v>0.171841578964329</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8107299907123914</v>
+        <v>0.5782487738634683</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1179161509720457</v>
+        <v>0.1194661509720456</v>
       </c>
       <c r="C43">
-        <v>192.1433436039538</v>
+        <v>112.2441861509512</v>
       </c>
       <c r="D43">
-        <v>1922.546343603954</v>
+        <v>1890.330186150952</v>
       </c>
       <c r="E43">
-        <v>842.1030000000001</v>
+        <v>889.7860000000003</v>
       </c>
       <c r="F43">
-        <v>1955.003</v>
+        <v>2002.686</v>
       </c>
       <c r="G43">
         <v>224.6</v>
@@ -4819,37 +4819,37 @@
         <v>227</v>
       </c>
       <c r="M43">
-        <v>392.5646024000001</v>
+        <v>402.1393488000001</v>
       </c>
       <c r="N43">
-        <v>-165.5646024000001</v>
+        <v>-175.1393488000001</v>
       </c>
       <c r="O43">
-        <v>-41.29181183856002</v>
+        <v>-43.67975359072003</v>
       </c>
       <c r="P43">
-        <v>-124.27279056144</v>
+        <v>-131.4595952092801</v>
       </c>
       <c r="Q43">
-        <v>-123.5727905614401</v>
+        <v>-130.7595952092801</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08044254846893351</v>
+        <v>0.08103983378736339</v>
       </c>
       <c r="T43">
-        <v>0.8000588560954618</v>
+        <v>0.8138529743040043</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.144215244201549</v>
+        <v>0.1407815479110359</v>
       </c>
       <c r="W43">
-        <v>0.171841578964329</v>
+        <v>0.172531065179464</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5782487738634683</v>
+        <v>0.5644809459143381</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1194661509720456</v>
+        <v>0.1210161509720457</v>
       </c>
       <c r="C44">
-        <v>112.2441861509517</v>
+        <v>33.40692834097399</v>
       </c>
       <c r="D44">
-        <v>1890.330186150952</v>
+        <v>1859.175928340974</v>
       </c>
       <c r="E44">
-        <v>889.7859999999998</v>
+        <v>937.4690000000001</v>
       </c>
       <c r="F44">
-        <v>2002.686</v>
+        <v>2050.369</v>
       </c>
       <c r="G44">
         <v>224.6</v>
@@ -4901,37 +4901,37 @@
         <v>227</v>
       </c>
       <c r="M44">
-        <v>402.1393488</v>
+        <v>411.7140952</v>
       </c>
       <c r="N44">
-        <v>-175.1393488</v>
+        <v>-184.7140952</v>
       </c>
       <c r="O44">
-        <v>-43.67975359072</v>
+        <v>-46.06769534288001</v>
       </c>
       <c r="P44">
-        <v>-131.45959520928</v>
+        <v>-138.64639985712</v>
       </c>
       <c r="Q44">
-        <v>-130.75959520928</v>
+        <v>-137.94639985712</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08103983378736337</v>
+        <v>0.08165807648538731</v>
       </c>
       <c r="T44">
-        <v>0.8138529743040042</v>
+        <v>0.8281310966602148</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.140781547911036</v>
+        <v>0.1375075584247328</v>
       </c>
       <c r="W44">
-        <v>0.172531065179464</v>
+        <v>0.1731884822683137</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5644809459143383</v>
+        <v>0.5513534820558652</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1210161509720457</v>
+        <v>0.1225661509720457</v>
       </c>
       <c r="C45">
-        <v>33.40692834097399</v>
+        <v>-44.42008160283785</v>
       </c>
       <c r="D45">
-        <v>1859.175928340974</v>
+        <v>1829.031918397162</v>
       </c>
       <c r="E45">
-        <v>937.4690000000001</v>
+        <v>985.152</v>
       </c>
       <c r="F45">
-        <v>2050.369</v>
+        <v>2098.052</v>
       </c>
       <c r="G45">
         <v>224.6</v>
@@ -4983,37 +4983,37 @@
         <v>227</v>
       </c>
       <c r="M45">
-        <v>411.7140952</v>
+        <v>421.2888416</v>
       </c>
       <c r="N45">
-        <v>-184.7140952</v>
+        <v>-194.2888416</v>
       </c>
       <c r="O45">
-        <v>-46.06769534288001</v>
+        <v>-48.45563709504</v>
       </c>
       <c r="P45">
-        <v>-138.64639985712</v>
+        <v>-145.83320450496</v>
       </c>
       <c r="Q45">
-        <v>-137.94639985712</v>
+        <v>-145.13320450496</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08165807648538731</v>
+        <v>0.08229839927976923</v>
       </c>
       <c r="T45">
-        <v>0.8281310966602148</v>
+        <v>0.8429191519577187</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1375075584247328</v>
+        <v>0.1343823866423525</v>
       </c>
       <c r="W45">
-        <v>0.1731884822683137</v>
+        <v>0.1738160167622156</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5513534820558652</v>
+        <v>0.5388227211000501</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1225661509720457</v>
+        <v>0.1241161509720456</v>
       </c>
       <c r="C46">
-        <v>-44.42008160283785</v>
+        <v>-121.2851990507522</v>
       </c>
       <c r="D46">
-        <v>1829.031918397162</v>
+        <v>1799.849800949248</v>
       </c>
       <c r="E46">
-        <v>985.152</v>
+        <v>1032.835</v>
       </c>
       <c r="F46">
-        <v>2098.052</v>
+        <v>2145.735</v>
       </c>
       <c r="G46">
         <v>224.6</v>
@@ -5065,37 +5065,37 @@
         <v>227</v>
       </c>
       <c r="M46">
-        <v>421.2888416</v>
+        <v>430.863588</v>
       </c>
       <c r="N46">
-        <v>-194.2888416</v>
+        <v>-203.863588</v>
       </c>
       <c r="O46">
-        <v>-48.45563709504</v>
+        <v>-50.84357884720001</v>
       </c>
       <c r="P46">
-        <v>-145.83320450496</v>
+        <v>-153.0200091528</v>
       </c>
       <c r="Q46">
-        <v>-145.13320450496</v>
+        <v>-152.3200091528001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08229839927976923</v>
+        <v>0.08296200653940139</v>
       </c>
       <c r="T46">
-        <v>0.8429191519577187</v>
+        <v>0.8582449547205863</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1343823866423525</v>
+        <v>0.1313961113836336</v>
       </c>
       <c r="W46">
-        <v>0.1738160167622156</v>
+        <v>0.1744156608341664</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5388227211000501</v>
+        <v>0.5268488828533823</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1241161509720456</v>
+        <v>0.1256661509720456</v>
       </c>
       <c r="C47">
-        <v>-121.2851990507522</v>
+        <v>-197.2337418067136</v>
       </c>
       <c r="D47">
-        <v>1799.849800949248</v>
+        <v>1771.584258193287</v>
       </c>
       <c r="E47">
-        <v>1032.835</v>
+        <v>1080.518</v>
       </c>
       <c r="F47">
-        <v>2145.735</v>
+        <v>2193.418</v>
       </c>
       <c r="G47">
         <v>224.6</v>
@@ -5147,37 +5147,37 @@
         <v>227</v>
       </c>
       <c r="M47">
-        <v>430.863588</v>
+        <v>440.4383344</v>
       </c>
       <c r="N47">
-        <v>-203.863588</v>
+        <v>-213.4383344</v>
       </c>
       <c r="O47">
-        <v>-50.84357884720001</v>
+        <v>-53.23152059936001</v>
       </c>
       <c r="P47">
-        <v>-153.0200091528</v>
+        <v>-160.20681380064</v>
       </c>
       <c r="Q47">
-        <v>-152.3200091528001</v>
+        <v>-159.50681380064</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08296200653940139</v>
+        <v>0.0836501918456866</v>
       </c>
       <c r="T47">
-        <v>0.8582449547205863</v>
+        <v>0.8741383798080046</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1313961113836336</v>
+        <v>0.1285396741796415</v>
       </c>
       <c r="W47">
-        <v>0.1744156608341664</v>
+        <v>0.174989233424728</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5268488828533823</v>
+        <v>0.5153956462696132</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1256661509720456</v>
+        <v>0.1272161509720456</v>
       </c>
       <c r="C48">
-        <v>-197.2337418067136</v>
+        <v>-272.3082249361416</v>
       </c>
       <c r="D48">
-        <v>1771.584258193287</v>
+        <v>1744.192775063859</v>
       </c>
       <c r="E48">
-        <v>1080.518</v>
+        <v>1128.201</v>
       </c>
       <c r="F48">
-        <v>2193.418</v>
+        <v>2241.101</v>
       </c>
       <c r="G48">
         <v>224.6</v>
@@ -5229,37 +5229,37 @@
         <v>227</v>
       </c>
       <c r="M48">
-        <v>440.4383344</v>
+        <v>450.0130808</v>
       </c>
       <c r="N48">
-        <v>-213.4383344</v>
+        <v>-223.0130808</v>
       </c>
       <c r="O48">
-        <v>-53.23152059936001</v>
+        <v>-55.61946235152001</v>
       </c>
       <c r="P48">
-        <v>-160.20681380064</v>
+        <v>-167.39361844848</v>
       </c>
       <c r="Q48">
-        <v>-159.50681380064</v>
+        <v>-166.69361844848</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0836501918456866</v>
+        <v>0.08436434640881277</v>
       </c>
       <c r="T48">
-        <v>0.8741383798080046</v>
+        <v>0.890631556785514</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1285396741796415</v>
+        <v>0.1258047874949683</v>
       </c>
       <c r="W48">
-        <v>0.174989233424728</v>
+        <v>0.1755383986710103</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5153956462696132</v>
+        <v>0.5044297814553661</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1272161509720456</v>
+        <v>0.1457568070637471</v>
       </c>
       <c r="C49">
-        <v>-272.3082249361416</v>
+        <v>-592.2254461224488</v>
       </c>
       <c r="D49">
-        <v>1744.192775063859</v>
+        <v>1471.958553877551</v>
       </c>
       <c r="E49">
-        <v>1128.201</v>
+        <v>1175.884</v>
       </c>
       <c r="F49">
-        <v>2241.101</v>
+        <v>2288.784</v>
       </c>
       <c r="G49">
         <v>224.6</v>
@@ -5311,45 +5311,45 @@
         <v>227</v>
       </c>
       <c r="M49">
-        <v>450.0130808</v>
+        <v>539.6952672000001</v>
       </c>
       <c r="N49">
-        <v>-223.0130808</v>
+        <v>-312.6952672000001</v>
       </c>
       <c r="O49">
-        <v>-55.61946235152001</v>
+        <v>-77.98619963968002</v>
       </c>
       <c r="P49">
-        <v>-167.39361844848</v>
+        <v>-234.7090675603201</v>
       </c>
       <c r="Q49">
-        <v>-166.69361844848</v>
+        <v>-234.0090675603201</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08436434640881277</v>
+        <v>0.08547261478533121</v>
       </c>
       <c r="T49">
-        <v>0.890631556785514</v>
+        <v>0.9162266694071871</v>
       </c>
       <c r="U49">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1258047874949683</v>
+        <v>0.1048995672941858</v>
       </c>
       <c r="W49">
-        <v>0.1755383986710103</v>
+        <v>0.211064682032031</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.5044297814553661</v>
+        <v>0.4206077277232791</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1457568070637471</v>
+        <v>0.1476568070637471</v>
       </c>
       <c r="C50">
-        <v>-592.2254461224488</v>
+        <v>-663.0813716512173</v>
       </c>
       <c r="D50">
-        <v>1471.958553877551</v>
+        <v>1448.785628348783</v>
       </c>
       <c r="E50">
-        <v>1175.884</v>
+        <v>1223.567</v>
       </c>
       <c r="F50">
-        <v>2288.784</v>
+        <v>2336.467</v>
       </c>
       <c r="G50">
         <v>224.6</v>
@@ -5393,37 +5393,37 @@
         <v>227</v>
       </c>
       <c r="M50">
-        <v>539.6952672000001</v>
+        <v>550.9389186000001</v>
       </c>
       <c r="N50">
-        <v>-312.6952672000001</v>
+        <v>-323.9389186000001</v>
       </c>
       <c r="O50">
-        <v>-77.98619963968002</v>
+        <v>-80.79036629884003</v>
       </c>
       <c r="P50">
-        <v>-234.7090675603201</v>
+        <v>-243.1485523011601</v>
       </c>
       <c r="Q50">
-        <v>-234.0090675603201</v>
+        <v>-242.4485523011601</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08547261478533121</v>
+        <v>0.08625050919288671</v>
       </c>
       <c r="T50">
-        <v>0.9162266694071871</v>
+        <v>0.9341918982190927</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1048995672941858</v>
+        <v>0.1027587597983861</v>
       </c>
       <c r="W50">
-        <v>0.211064682032031</v>
+        <v>0.2115694844395406</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4206077277232791</v>
+        <v>0.412023896545253</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1476568070637471</v>
+        <v>0.1495568070637471</v>
       </c>
       <c r="C51">
-        <v>-663.0813716512173</v>
+        <v>-733.2189864695786</v>
       </c>
       <c r="D51">
-        <v>1448.785628348783</v>
+        <v>1426.331013530422</v>
       </c>
       <c r="E51">
-        <v>1223.567</v>
+        <v>1271.25</v>
       </c>
       <c r="F51">
-        <v>2336.467</v>
+        <v>2384.15</v>
       </c>
       <c r="G51">
         <v>224.6</v>
@@ -5475,37 +5475,37 @@
         <v>227</v>
       </c>
       <c r="M51">
-        <v>550.9389186000001</v>
+        <v>562.1825700000001</v>
       </c>
       <c r="N51">
-        <v>-323.9389186000001</v>
+        <v>-335.1825700000001</v>
       </c>
       <c r="O51">
-        <v>-80.79036629884003</v>
+        <v>-83.59453295800002</v>
       </c>
       <c r="P51">
-        <v>-243.1485523011601</v>
+        <v>-251.5880370420001</v>
       </c>
       <c r="Q51">
-        <v>-242.4485523011601</v>
+        <v>-250.8880370420001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08625050919288671</v>
+        <v>0.08705951937674446</v>
       </c>
       <c r="T51">
-        <v>0.9341918982190927</v>
+        <v>0.9528757361834747</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1027587597983861</v>
+        <v>0.1007035846024184</v>
       </c>
       <c r="W51">
-        <v>0.2115694844395406</v>
+        <v>0.2120540947507498</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.412023896545253</v>
+        <v>0.403783418614348</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1495568070637471</v>
+        <v>0.1514568070637471</v>
       </c>
       <c r="C52">
-        <v>-733.2189864695786</v>
+        <v>-802.6711799517809</v>
       </c>
       <c r="D52">
-        <v>1426.331013530422</v>
+        <v>1404.561820048219</v>
       </c>
       <c r="E52">
-        <v>1271.25</v>
+        <v>1318.933</v>
       </c>
       <c r="F52">
-        <v>2384.15</v>
+        <v>2431.833</v>
       </c>
       <c r="G52">
         <v>224.6</v>
@@ -5557,37 +5557,37 @@
         <v>227</v>
       </c>
       <c r="M52">
-        <v>562.1825700000001</v>
+        <v>573.4262214</v>
       </c>
       <c r="N52">
-        <v>-335.1825700000001</v>
+        <v>-346.4262214</v>
       </c>
       <c r="O52">
-        <v>-83.59453295800002</v>
+        <v>-86.39869961716001</v>
       </c>
       <c r="P52">
-        <v>-251.5880370420001</v>
+        <v>-260.02752178284</v>
       </c>
       <c r="Q52">
-        <v>-250.8880370420001</v>
+        <v>-259.3275217828401</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08705951937674446</v>
+        <v>0.08790155038443312</v>
       </c>
       <c r="T52">
-        <v>0.9528757361834747</v>
+        <v>0.9723221797790557</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1007035846024184</v>
+        <v>0.09872900451217489</v>
       </c>
       <c r="W52">
-        <v>0.2120540947507498</v>
+        <v>0.2125197007360292</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.403783418614348</v>
+        <v>0.3958660966807334</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1514568070637471</v>
+        <v>0.1533568070637471</v>
       </c>
       <c r="C53">
-        <v>-802.6711799517809</v>
+        <v>-871.4688637770264</v>
       </c>
       <c r="D53">
-        <v>1404.561820048219</v>
+        <v>1383.447136222974</v>
       </c>
       <c r="E53">
-        <v>1318.933</v>
+        <v>1366.616</v>
       </c>
       <c r="F53">
-        <v>2431.833</v>
+        <v>2479.516</v>
       </c>
       <c r="G53">
         <v>224.6</v>
@@ -5639,37 +5639,37 @@
         <v>227</v>
       </c>
       <c r="M53">
-        <v>573.4262214</v>
+        <v>584.6698728</v>
       </c>
       <c r="N53">
-        <v>-346.4262214</v>
+        <v>-357.6698728</v>
       </c>
       <c r="O53">
-        <v>-86.39869961716001</v>
+        <v>-89.20286627632001</v>
       </c>
       <c r="P53">
-        <v>-260.02752178284</v>
+        <v>-268.46700652368</v>
       </c>
       <c r="Q53">
-        <v>-259.3275217828401</v>
+        <v>-267.76700652368</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08790155038443312</v>
+        <v>0.08877866601744214</v>
       </c>
       <c r="T53">
-        <v>0.9723221797790557</v>
+        <v>0.992578891857786</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.09872900451217489</v>
+        <v>0.09683036981001769</v>
       </c>
       <c r="W53">
-        <v>0.2125197007360292</v>
+        <v>0.2129673987987978</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3958660966807334</v>
+        <v>0.3882532871291807</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1533568070637471</v>
+        <v>0.1552568070637471</v>
       </c>
       <c r="C54">
-        <v>-871.4688637770264</v>
+        <v>-939.6411183806661</v>
       </c>
       <c r="D54">
-        <v>1383.447136222974</v>
+        <v>1362.957881619334</v>
       </c>
       <c r="E54">
-        <v>1366.616</v>
+        <v>1414.299</v>
       </c>
       <c r="F54">
-        <v>2479.516</v>
+        <v>2527.199</v>
       </c>
       <c r="G54">
         <v>224.6</v>
@@ -5721,37 +5721,37 @@
         <v>227</v>
       </c>
       <c r="M54">
-        <v>584.6698728</v>
+        <v>595.9135242000001</v>
       </c>
       <c r="N54">
-        <v>-357.6698728</v>
+        <v>-368.9135242000001</v>
       </c>
       <c r="O54">
-        <v>-89.20286627632001</v>
+        <v>-92.00703293548003</v>
       </c>
       <c r="P54">
-        <v>-268.46700652368</v>
+        <v>-276.9064912645201</v>
       </c>
       <c r="Q54">
-        <v>-267.76700652368</v>
+        <v>-276.2064912645201</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08877866601744214</v>
+        <v>0.08969310571994092</v>
       </c>
       <c r="T54">
-        <v>0.992578891857786</v>
+        <v>1.013697591684548</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.09683036981001769</v>
+        <v>0.0950033817003947</v>
       </c>
       <c r="W54">
-        <v>0.2129673987987978</v>
+        <v>0.2133982025950469</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3882532871291807</v>
+        <v>0.3809277534097623</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1552568070637471</v>
+        <v>0.1571568070637471</v>
       </c>
       <c r="C55">
-        <v>-939.6411183806661</v>
+        <v>-1007.215326581412</v>
       </c>
       <c r="D55">
-        <v>1362.957881619334</v>
+        <v>1343.066673418589</v>
       </c>
       <c r="E55">
-        <v>1414.299</v>
+        <v>1461.982</v>
       </c>
       <c r="F55">
-        <v>2527.199</v>
+        <v>2574.882</v>
       </c>
       <c r="G55">
         <v>224.6</v>
@@ -5803,37 +5803,37 @@
         <v>227</v>
       </c>
       <c r="M55">
-        <v>595.9135242000001</v>
+        <v>607.1571756000001</v>
       </c>
       <c r="N55">
-        <v>-368.9135242000001</v>
+        <v>-380.1571756000001</v>
       </c>
       <c r="O55">
-        <v>-92.00703293548003</v>
+        <v>-94.81119959464002</v>
       </c>
       <c r="P55">
-        <v>-276.9064912645201</v>
+        <v>-285.3459760053601</v>
       </c>
       <c r="Q55">
-        <v>-276.2064912645201</v>
+        <v>-284.6459760053601</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08969310571994092</v>
+        <v>0.09064730367037441</v>
       </c>
       <c r="T55">
-        <v>1.013697591684548</v>
+        <v>1.035734495851603</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0950033817003947</v>
+        <v>0.09324405981705405</v>
       </c>
       <c r="W55">
-        <v>0.2133982025950469</v>
+        <v>0.2138130506951386</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3809277534097623</v>
+        <v>0.3738735357540259</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1571568070637471</v>
+        <v>0.1590568070637471</v>
       </c>
       <c r="C56">
-        <v>-1007.215326581412</v>
+        <v>-1074.217295675811</v>
       </c>
       <c r="D56">
-        <v>1343.066673418589</v>
+        <v>1323.747704324189</v>
       </c>
       <c r="E56">
-        <v>1461.982</v>
+        <v>1509.665</v>
       </c>
       <c r="F56">
-        <v>2574.882</v>
+        <v>2622.565000000001</v>
       </c>
       <c r="G56">
         <v>224.6</v>
@@ -5885,37 +5885,37 @@
         <v>227</v>
       </c>
       <c r="M56">
-        <v>607.1571756000001</v>
+        <v>618.4008270000002</v>
       </c>
       <c r="N56">
-        <v>-380.1571756000001</v>
+        <v>-391.4008270000002</v>
       </c>
       <c r="O56">
-        <v>-94.81119959464002</v>
+        <v>-97.61536625380005</v>
       </c>
       <c r="P56">
-        <v>-285.3459760053601</v>
+        <v>-293.7854607462001</v>
       </c>
       <c r="Q56">
-        <v>-284.6459760053601</v>
+        <v>-293.0854607462001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09064730367037441</v>
+        <v>0.09164391041860495</v>
       </c>
       <c r="T56">
-        <v>1.035734495851603</v>
+        <v>1.058750817981639</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.09324405981705405</v>
+        <v>0.09154871327492579</v>
       </c>
       <c r="W56">
-        <v>0.2138130506951386</v>
+        <v>0.2142128134097725</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3738735357540259</v>
+        <v>0.3670758351039526</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1590568070637471</v>
+        <v>0.1609568070637471</v>
       </c>
       <c r="C57">
-        <v>-1074.217295675811</v>
+        <v>-1140.671369144737</v>
       </c>
       <c r="D57">
-        <v>1323.747704324189</v>
+        <v>1304.976630855264</v>
       </c>
       <c r="E57">
-        <v>1509.665</v>
+        <v>1557.348</v>
       </c>
       <c r="F57">
-        <v>2622.565000000001</v>
+        <v>2670.248000000001</v>
       </c>
       <c r="G57">
         <v>224.6</v>
@@ -5967,37 +5967,37 @@
         <v>227</v>
       </c>
       <c r="M57">
-        <v>618.4008270000002</v>
+        <v>629.6444784000001</v>
       </c>
       <c r="N57">
-        <v>-391.4008270000002</v>
+        <v>-402.6444784000001</v>
       </c>
       <c r="O57">
-        <v>-97.61536625380005</v>
+        <v>-100.41953291296</v>
       </c>
       <c r="P57">
-        <v>-293.7854607462001</v>
+        <v>-302.2249454870401</v>
       </c>
       <c r="Q57">
-        <v>-293.0854607462001</v>
+        <v>-301.5249454870401</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09164391041860495</v>
+        <v>0.09268581747357324</v>
       </c>
       <c r="T57">
-        <v>1.058750817981639</v>
+        <v>1.08281333657213</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.09154871327492579</v>
+        <v>0.08991391482358783</v>
       </c>
       <c r="W57">
-        <v>0.2142128134097725</v>
+        <v>0.214598298884598</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3670758351039526</v>
+        <v>0.3605209094770964</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1609568070637471</v>
+        <v>0.1628568070637471</v>
       </c>
       <c r="C58">
-        <v>-1140.671369144737</v>
+        <v>-1206.600528988611</v>
       </c>
       <c r="D58">
-        <v>1304.976630855264</v>
+        <v>1286.73047101139</v>
       </c>
       <c r="E58">
-        <v>1557.348</v>
+        <v>1605.031</v>
       </c>
       <c r="F58">
-        <v>2670.248000000001</v>
+        <v>2717.931</v>
       </c>
       <c r="G58">
         <v>224.6</v>
@@ -6049,37 +6049,37 @@
         <v>227</v>
       </c>
       <c r="M58">
-        <v>629.6444784000001</v>
+        <v>640.8881298000001</v>
       </c>
       <c r="N58">
-        <v>-402.6444784000001</v>
+        <v>-413.8881298000001</v>
       </c>
       <c r="O58">
-        <v>-100.41953291296</v>
+        <v>-103.22369957212</v>
       </c>
       <c r="P58">
-        <v>-302.2249454870401</v>
+        <v>-310.6644302278801</v>
       </c>
       <c r="Q58">
-        <v>-301.5249454870401</v>
+        <v>-309.9644302278801</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09268581747357324</v>
+        <v>0.09377618532179588</v>
       </c>
       <c r="T58">
-        <v>1.08281333657213</v>
+        <v>1.107995042073808</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.08991391482358783</v>
+        <v>0.08833647772141963</v>
       </c>
       <c r="W58">
-        <v>0.214598298884598</v>
+        <v>0.2149702585532893</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3605209094770964</v>
+        <v>0.3541959812406561</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1628568070637471</v>
+        <v>0.1647568070637471</v>
       </c>
       <c r="C59">
-        <v>-1206.600528988611</v>
+        <v>-1272.026489595911</v>
       </c>
       <c r="D59">
-        <v>1286.73047101139</v>
+        <v>1268.98751040409</v>
       </c>
       <c r="E59">
-        <v>1605.031</v>
+        <v>1652.714</v>
       </c>
       <c r="F59">
-        <v>2717.931</v>
+        <v>2765.614</v>
       </c>
       <c r="G59">
         <v>224.6</v>
@@ -6131,37 +6131,37 @@
         <v>227</v>
       </c>
       <c r="M59">
-        <v>640.8881298000001</v>
+        <v>652.1317812000001</v>
       </c>
       <c r="N59">
-        <v>-413.8881298000001</v>
+        <v>-425.1317812000001</v>
       </c>
       <c r="O59">
-        <v>-103.22369957212</v>
+        <v>-106.02786623128</v>
       </c>
       <c r="P59">
-        <v>-310.6644302278801</v>
+        <v>-319.1039149687201</v>
       </c>
       <c r="Q59">
-        <v>-309.9644302278801</v>
+        <v>-318.4039149687201</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09377618532179588</v>
+        <v>0.09491847544850529</v>
       </c>
       <c r="T59">
-        <v>1.107995042073808</v>
+        <v>1.134375876408898</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08833647772141963</v>
+        <v>0.08681343500208481</v>
       </c>
       <c r="W59">
-        <v>0.2149702585532893</v>
+        <v>0.2153293920265084</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3541959812406561</v>
+        <v>0.3480891539778862</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1647568070637471</v>
+        <v>0.1666568070637471</v>
       </c>
       <c r="C60">
-        <v>-1272.02648959591</v>
+        <v>-1336.969783951094</v>
       </c>
       <c r="D60">
-        <v>1268.98751040409</v>
+        <v>1251.727216048906</v>
       </c>
       <c r="E60">
-        <v>1652.714</v>
+        <v>1700.397</v>
       </c>
       <c r="F60">
-        <v>2765.614</v>
+        <v>2813.297</v>
       </c>
       <c r="G60">
         <v>224.6</v>
@@ -6213,37 +6213,37 @@
         <v>227</v>
       </c>
       <c r="M60">
-        <v>652.1317812</v>
+        <v>663.3754326000001</v>
       </c>
       <c r="N60">
-        <v>-425.1317812</v>
+        <v>-436.3754326000001</v>
       </c>
       <c r="O60">
-        <v>-106.02786623128</v>
+        <v>-108.83203289044</v>
       </c>
       <c r="P60">
-        <v>-319.10391496872</v>
+        <v>-327.54339970956</v>
       </c>
       <c r="Q60">
-        <v>-318.40391496872</v>
+        <v>-326.8433997095601</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09491847544850529</v>
+        <v>0.09611648704481029</v>
       </c>
       <c r="T60">
-        <v>1.134375876408898</v>
+        <v>1.162043580711554</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08681343500208483</v>
+        <v>0.08534202084950711</v>
       </c>
       <c r="W60">
-        <v>0.2153293920265084</v>
+        <v>0.2156763514836862</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3480891539778862</v>
+        <v>0.3421893378087695</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1666568070637471</v>
+        <v>0.1685568070637471</v>
       </c>
       <c r="C61">
-        <v>-1336.969783951094</v>
+        <v>-1401.449842901522</v>
       </c>
       <c r="D61">
-        <v>1251.727216048906</v>
+        <v>1234.930157098479</v>
       </c>
       <c r="E61">
-        <v>1700.397</v>
+        <v>1748.08</v>
       </c>
       <c r="F61">
-        <v>2813.297</v>
+        <v>2860.98</v>
       </c>
       <c r="G61">
         <v>224.6</v>
@@ -6295,37 +6295,37 @@
         <v>227</v>
       </c>
       <c r="M61">
-        <v>663.3754326000001</v>
+        <v>674.619084</v>
       </c>
       <c r="N61">
-        <v>-436.3754326000001</v>
+        <v>-447.619084</v>
       </c>
       <c r="O61">
-        <v>-108.83203289044</v>
+        <v>-111.6361995496</v>
       </c>
       <c r="P61">
-        <v>-327.54339970956</v>
+        <v>-335.9828844504</v>
       </c>
       <c r="Q61">
-        <v>-326.8433997095601</v>
+        <v>-335.2828844504</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09611648704481029</v>
+        <v>0.09737439922093057</v>
       </c>
       <c r="T61">
-        <v>1.162043580711554</v>
+        <v>1.191094670229343</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08534202084950711</v>
+        <v>0.08391965383534866</v>
       </c>
       <c r="W61">
-        <v>0.2156763514836862</v>
+        <v>0.2160117456256248</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3421893378087695</v>
+        <v>0.3364861821786234</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1685568070637471</v>
+        <v>0.1704568070637471</v>
       </c>
       <c r="C62">
-        <v>-1401.449842901522</v>
+        <v>-1465.485068126738</v>
       </c>
       <c r="D62">
-        <v>1234.930157098479</v>
+        <v>1218.577931873262</v>
       </c>
       <c r="E62">
-        <v>1748.08</v>
+        <v>1795.763</v>
       </c>
       <c r="F62">
-        <v>2860.98</v>
+        <v>2908.663</v>
       </c>
       <c r="G62">
         <v>224.6</v>
@@ -6377,37 +6377,37 @@
         <v>227</v>
       </c>
       <c r="M62">
-        <v>674.619084</v>
+        <v>685.8627354</v>
       </c>
       <c r="N62">
-        <v>-447.619084</v>
+        <v>-458.8627354</v>
       </c>
       <c r="O62">
-        <v>-111.6361995496</v>
+        <v>-114.44036620876</v>
       </c>
       <c r="P62">
-        <v>-335.9828844504</v>
+        <v>-344.42236919124</v>
       </c>
       <c r="Q62">
-        <v>-335.2828844504</v>
+        <v>-343.72236919124</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09737439922093057</v>
+        <v>0.09869681971377495</v>
       </c>
       <c r="T62">
-        <v>1.191094670229343</v>
+        <v>1.221635559209583</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08391965383534866</v>
+        <v>0.08254392180526098</v>
       </c>
       <c r="W62">
-        <v>0.2160117456256248</v>
+        <v>0.2163361432383195</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3364861821786234</v>
+        <v>0.3309700152576623</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1704568070637471</v>
+        <v>0.1723568070637471</v>
       </c>
       <c r="C63">
-        <v>-1465.485068126738</v>
+        <v>-1529.092899386222</v>
       </c>
       <c r="D63">
-        <v>1218.577931873262</v>
+        <v>1202.653100613778</v>
       </c>
       <c r="E63">
-        <v>1795.763</v>
+        <v>1843.446</v>
       </c>
       <c r="F63">
-        <v>2908.663</v>
+        <v>2956.346</v>
       </c>
       <c r="G63">
         <v>224.6</v>
@@ -6459,37 +6459,37 @@
         <v>227</v>
       </c>
       <c r="M63">
-        <v>685.8627354</v>
+        <v>697.1063868</v>
       </c>
       <c r="N63">
-        <v>-458.8627354</v>
+        <v>-470.1063868</v>
       </c>
       <c r="O63">
-        <v>-114.44036620876</v>
+        <v>-117.24453286792</v>
       </c>
       <c r="P63">
-        <v>-344.42236919124</v>
+        <v>-352.86185393208</v>
       </c>
       <c r="Q63">
-        <v>-343.72236919124</v>
+        <v>-352.16185393208</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09869681971377495</v>
+        <v>0.1000888412851901</v>
       </c>
       <c r="T63">
-        <v>1.221635559209583</v>
+        <v>1.253783863399309</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08254392180526098</v>
+        <v>0.08121256822775677</v>
       </c>
       <c r="W63">
-        <v>0.2163361432383195</v>
+        <v>0.216650076411895</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3309700152576623</v>
+        <v>0.3256317892051194</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1723568070637471</v>
+        <v>0.1742568070637471</v>
       </c>
       <c r="C64">
-        <v>-1529.092899386222</v>
+        <v>-1592.289876562238</v>
       </c>
       <c r="D64">
-        <v>1202.653100613778</v>
+        <v>1187.139123437762</v>
       </c>
       <c r="E64">
-        <v>1843.446</v>
+        <v>1891.129</v>
       </c>
       <c r="F64">
-        <v>2956.346</v>
+        <v>3004.029</v>
       </c>
       <c r="G64">
         <v>224.6</v>
@@ -6541,37 +6541,37 @@
         <v>227</v>
       </c>
       <c r="M64">
-        <v>697.1063868</v>
+        <v>708.3500382</v>
       </c>
       <c r="N64">
-        <v>-470.1063868</v>
+        <v>-481.3500382</v>
       </c>
       <c r="O64">
-        <v>-117.24453286792</v>
+        <v>-120.04869952708</v>
       </c>
       <c r="P64">
-        <v>-352.86185393208</v>
+        <v>-361.30133867292</v>
       </c>
       <c r="Q64">
-        <v>-352.16185393208</v>
+        <v>-360.60133867292</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1000888412851901</v>
+        <v>0.1015561072658709</v>
       </c>
       <c r="T64">
-        <v>1.253783863399309</v>
+        <v>1.287669913761452</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08121256822775677</v>
+        <v>0.0799234798431892</v>
       </c>
       <c r="W64">
-        <v>0.216650076411895</v>
+        <v>0.216954043452976</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3256317892051194</v>
+        <v>0.320463030646308</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1742568070637471</v>
+        <v>0.1761568070637471</v>
       </c>
       <c r="C65">
-        <v>-1592.289876562238</v>
+        <v>-1655.091696961805</v>
       </c>
       <c r="D65">
-        <v>1187.139123437762</v>
+        <v>1172.020303038195</v>
       </c>
       <c r="E65">
-        <v>1891.129</v>
+        <v>1938.812</v>
       </c>
       <c r="F65">
-        <v>3004.029</v>
+        <v>3051.712</v>
       </c>
       <c r="G65">
         <v>224.6</v>
@@ -6623,37 +6623,37 @@
         <v>227</v>
       </c>
       <c r="M65">
-        <v>708.3500382</v>
+        <v>719.5936896000001</v>
       </c>
       <c r="N65">
-        <v>-481.3500382</v>
+        <v>-492.5936896000001</v>
       </c>
       <c r="O65">
-        <v>-120.04869952708</v>
+        <v>-122.85286618624</v>
       </c>
       <c r="P65">
-        <v>-361.30133867292</v>
+        <v>-369.74082341376</v>
       </c>
       <c r="Q65">
-        <v>-360.60133867292</v>
+        <v>-369.0408234137601</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1015561072658709</v>
+        <v>0.1031048880232562</v>
       </c>
       <c r="T65">
-        <v>1.287669913761452</v>
+        <v>1.323438522477048</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0799234798431892</v>
+        <v>0.07867467547063937</v>
       </c>
       <c r="W65">
-        <v>0.216954043452976</v>
+        <v>0.2172485115240232</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.320463030646308</v>
+        <v>0.3154557957924593</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1761568070637471</v>
+        <v>0.1780568070637471</v>
       </c>
       <c r="C66">
-        <v>-1655.091696961805</v>
+        <v>-1717.513268295111</v>
       </c>
       <c r="D66">
-        <v>1172.020303038195</v>
+        <v>1157.281731704889</v>
       </c>
       <c r="E66">
-        <v>1938.812</v>
+        <v>1986.495</v>
       </c>
       <c r="F66">
-        <v>3051.712</v>
+        <v>3099.395</v>
       </c>
       <c r="G66">
         <v>224.6</v>
@@ -6705,37 +6705,37 @@
         <v>227</v>
       </c>
       <c r="M66">
-        <v>719.5936896000001</v>
+        <v>730.8373410000002</v>
       </c>
       <c r="N66">
-        <v>-492.5936896000001</v>
+        <v>-503.8373410000002</v>
       </c>
       <c r="O66">
-        <v>-122.85286618624</v>
+        <v>-125.6570328454</v>
       </c>
       <c r="P66">
-        <v>-369.74082341376</v>
+        <v>-378.1803081546001</v>
       </c>
       <c r="Q66">
-        <v>-369.0408234137601</v>
+        <v>-377.4803081546001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1031048880232562</v>
+        <v>0.1047421705382064</v>
       </c>
       <c r="T66">
-        <v>1.323438522477048</v>
+        <v>1.361251051690678</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07867467547063937</v>
+        <v>0.07746429584801413</v>
       </c>
       <c r="W66">
-        <v>0.2172485115240232</v>
+        <v>0.2175339190390383</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3154557957924593</v>
+        <v>0.3106026297033445</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1780568070637471</v>
+        <v>0.1799568070637471</v>
       </c>
       <c r="C67">
-        <v>-1717.513268295111</v>
+        <v>-1779.568757706237</v>
       </c>
       <c r="D67">
-        <v>1157.281731704889</v>
+        <v>1142.909242293763</v>
       </c>
       <c r="E67">
-        <v>1986.495</v>
+        <v>2034.178</v>
       </c>
       <c r="F67">
-        <v>3099.395</v>
+        <v>3147.078</v>
       </c>
       <c r="G67">
         <v>224.6</v>
@@ -6787,37 +6787,37 @@
         <v>227</v>
       </c>
       <c r="M67">
-        <v>730.8373410000002</v>
+        <v>742.0809924000001</v>
       </c>
       <c r="N67">
-        <v>-503.8373410000002</v>
+        <v>-515.0809924000001</v>
       </c>
       <c r="O67">
-        <v>-125.6570328454</v>
+        <v>-128.46119950456</v>
       </c>
       <c r="P67">
-        <v>-378.1803081546001</v>
+        <v>-386.6197928954401</v>
       </c>
       <c r="Q67">
-        <v>-377.4803081546001</v>
+        <v>-385.9197928954401</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1047421705382064</v>
+        <v>0.1064757637893301</v>
       </c>
       <c r="T67">
-        <v>1.361251051690678</v>
+        <v>1.401287847328639</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07746429584801413</v>
+        <v>0.0762905943957715</v>
       </c>
       <c r="W67">
-        <v>0.2175339190390383</v>
+        <v>0.2178106778414771</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3106026297033445</v>
+        <v>0.3058965292532939</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1799568070637471</v>
+        <v>0.1818568070637471</v>
       </c>
       <c r="C68">
-        <v>-1779.568757706237</v>
+        <v>-1841.27163719517</v>
       </c>
       <c r="D68">
-        <v>1142.909242293763</v>
+        <v>1128.889362804831</v>
       </c>
       <c r="E68">
-        <v>2034.178</v>
+        <v>2081.861</v>
       </c>
       <c r="F68">
-        <v>3147.078</v>
+        <v>3194.761</v>
       </c>
       <c r="G68">
         <v>224.6</v>
@@ -6869,37 +6869,37 @@
         <v>227</v>
       </c>
       <c r="M68">
-        <v>742.0809924000001</v>
+        <v>753.3246438000001</v>
       </c>
       <c r="N68">
-        <v>-515.0809924000001</v>
+        <v>-526.3246438000001</v>
       </c>
       <c r="O68">
-        <v>-128.46119950456</v>
+        <v>-131.26536616372</v>
       </c>
       <c r="P68">
-        <v>-386.6197928954401</v>
+        <v>-395.0592776362801</v>
       </c>
       <c r="Q68">
-        <v>-385.9197928954401</v>
+        <v>-394.3592776362801</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1064757637893301</v>
+        <v>0.1083144232980977</v>
       </c>
       <c r="T68">
-        <v>1.401287847328639</v>
+        <v>1.443751115429507</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0762905943957715</v>
+        <v>0.07515192880777491</v>
       </c>
       <c r="W68">
-        <v>0.2178106778414771</v>
+        <v>0.2180791751871267</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3058965292532939</v>
+        <v>0.3013309094136924</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1818568070637471</v>
+        <v>0.1837568070637471</v>
       </c>
       <c r="C69">
-        <v>-1841.27163719517</v>
+        <v>-1902.634725737218</v>
       </c>
       <c r="D69">
-        <v>1128.889362804831</v>
+        <v>1115.209274262783</v>
       </c>
       <c r="E69">
-        <v>2081.861</v>
+        <v>2129.544</v>
       </c>
       <c r="F69">
-        <v>3194.761</v>
+        <v>3242.444</v>
       </c>
       <c r="G69">
         <v>224.6</v>
@@ -6951,37 +6951,37 @@
         <v>227</v>
       </c>
       <c r="M69">
-        <v>753.3246438000001</v>
+        <v>764.5682952000001</v>
       </c>
       <c r="N69">
-        <v>-526.3246438000001</v>
+        <v>-537.5682952000001</v>
       </c>
       <c r="O69">
-        <v>-131.26536616372</v>
+        <v>-134.06953282288</v>
       </c>
       <c r="P69">
-        <v>-395.0592776362801</v>
+        <v>-403.49876237712</v>
       </c>
       <c r="Q69">
-        <v>-394.3592776362801</v>
+        <v>-402.7987623771201</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1083144232980977</v>
+        <v>0.1102679990261632</v>
       </c>
       <c r="T69">
-        <v>1.443751115429507</v>
+        <v>1.488868337786679</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07515192880777491</v>
+        <v>0.07404675338413116</v>
       </c>
       <c r="W69">
-        <v>0.2180791751871267</v>
+        <v>0.2183397755520219</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3013309094136924</v>
+        <v>0.29689957251055</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1837568070637471</v>
+        <v>0.1856568070637471</v>
       </c>
       <c r="C70">
-        <v>-1902.634725737218</v>
+        <v>-1963.670228376636</v>
       </c>
       <c r="D70">
-        <v>1115.209274262783</v>
+        <v>1101.856771623364</v>
       </c>
       <c r="E70">
-        <v>2129.544</v>
+        <v>2177.227</v>
       </c>
       <c r="F70">
-        <v>3242.444</v>
+        <v>3290.127</v>
       </c>
       <c r="G70">
         <v>224.6</v>
@@ -7033,37 +7033,37 @@
         <v>227</v>
       </c>
       <c r="M70">
-        <v>764.5682952000001</v>
+        <v>775.8119466000002</v>
       </c>
       <c r="N70">
-        <v>-537.5682952000001</v>
+        <v>-548.8119466000002</v>
       </c>
       <c r="O70">
-        <v>-134.06953282288</v>
+        <v>-136.8736994820401</v>
       </c>
       <c r="P70">
-        <v>-403.49876237712</v>
+        <v>-411.9382471179601</v>
       </c>
       <c r="Q70">
-        <v>-402.7987623771201</v>
+        <v>-411.2382471179602</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1102679990261632</v>
+        <v>0.1123476118979749</v>
       </c>
       <c r="T70">
-        <v>1.488868337786679</v>
+        <v>1.536896348683024</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07404675338413116</v>
+        <v>0.07297361203073796</v>
       </c>
       <c r="W70">
-        <v>0.2183397755520219</v>
+        <v>0.218592822283152</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.29689957251055</v>
+        <v>0.2925966801553246</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1856568070637471</v>
+        <v>0.1875568070637471</v>
       </c>
       <c r="C71">
-        <v>-1963.670228376636</v>
+        <v>-2024.389772545044</v>
       </c>
       <c r="D71">
-        <v>1101.856771623364</v>
+        <v>1088.820227454957</v>
       </c>
       <c r="E71">
-        <v>2177.227</v>
+        <v>2224.91</v>
       </c>
       <c r="F71">
-        <v>3290.127</v>
+        <v>3337.81</v>
       </c>
       <c r="G71">
         <v>224.6</v>
@@ -7115,37 +7115,37 @@
         <v>227</v>
       </c>
       <c r="M71">
-        <v>775.8119466000002</v>
+        <v>787.0555980000001</v>
       </c>
       <c r="N71">
-        <v>-548.8119466000002</v>
+        <v>-560.0555980000001</v>
       </c>
       <c r="O71">
-        <v>-136.8736994820401</v>
+        <v>-139.6778661412</v>
       </c>
       <c r="P71">
-        <v>-411.9382471179601</v>
+        <v>-420.3777318588001</v>
       </c>
       <c r="Q71">
-        <v>-411.2382471179602</v>
+        <v>-419.6777318588001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1123476118979749</v>
+        <v>0.1145658656279074</v>
       </c>
       <c r="T71">
-        <v>1.536896348683024</v>
+        <v>1.588126226972458</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07297361203073796</v>
+        <v>0.07193113185887026</v>
       </c>
       <c r="W71">
-        <v>0.218592822283152</v>
+        <v>0.2188386391076784</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2925966801553246</v>
+        <v>0.2884167275816771</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1875568070637471</v>
+        <v>0.1894568070637471</v>
       </c>
       <c r="C72">
-        <v>-2024.389772545044</v>
+        <v>-2084.804441831797</v>
       </c>
       <c r="D72">
-        <v>1088.820227454957</v>
+        <v>1076.088558168204</v>
       </c>
       <c r="E72">
-        <v>2224.91</v>
+        <v>2272.593</v>
       </c>
       <c r="F72">
-        <v>3337.81</v>
+        <v>3385.493</v>
       </c>
       <c r="G72">
         <v>224.6</v>
@@ -7197,37 +7197,37 @@
         <v>227</v>
       </c>
       <c r="M72">
-        <v>787.0555980000001</v>
+        <v>798.2992494000001</v>
       </c>
       <c r="N72">
-        <v>-560.0555980000001</v>
+        <v>-571.2992494000001</v>
       </c>
       <c r="O72">
-        <v>-139.6778661412</v>
+        <v>-142.48203280036</v>
       </c>
       <c r="P72">
-        <v>-420.3777318588001</v>
+        <v>-428.8172165996401</v>
       </c>
       <c r="Q72">
-        <v>-419.6777318588001</v>
+        <v>-428.1172165996401</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1145658656279074</v>
+        <v>0.1169371023736974</v>
       </c>
       <c r="T72">
-        <v>1.588126226972458</v>
+        <v>1.642889200316336</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07193113185887026</v>
+        <v>0.07091801732564675</v>
       </c>
       <c r="W72">
-        <v>0.2188386391076784</v>
+        <v>0.2190775315146125</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2884167275816771</v>
+        <v>0.2843545201509493</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1894568070637471</v>
+        <v>0.1913568070637471</v>
       </c>
       <c r="C73">
-        <v>-2084.804441831796</v>
+        <v>-2144.924807412465</v>
       </c>
       <c r="D73">
-        <v>1076.088558168204</v>
+        <v>1063.651192587535</v>
       </c>
       <c r="E73">
-        <v>2272.593</v>
+        <v>2320.276</v>
       </c>
       <c r="F73">
-        <v>3385.493</v>
+        <v>3433.176</v>
       </c>
       <c r="G73">
         <v>224.6</v>
@@ -7279,37 +7279,37 @@
         <v>227</v>
       </c>
       <c r="M73">
-        <v>798.2992494</v>
+        <v>809.5429008</v>
       </c>
       <c r="N73">
-        <v>-571.2992494</v>
+        <v>-582.5429008</v>
       </c>
       <c r="O73">
-        <v>-142.48203280036</v>
+        <v>-145.28619945952</v>
       </c>
       <c r="P73">
-        <v>-428.81721659964</v>
+        <v>-437.25670134048</v>
       </c>
       <c r="Q73">
-        <v>-428.11721659964</v>
+        <v>-436.55670134048</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1169371023736973</v>
+        <v>0.119477713172758</v>
       </c>
       <c r="T73">
-        <v>1.642889200316335</v>
+        <v>1.701563814613347</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07091801732564676</v>
+        <v>0.06993304486279055</v>
       </c>
       <c r="W73">
-        <v>0.2190775315146125</v>
+        <v>0.219309788021354</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2843545201509493</v>
+        <v>0.2804051518155195</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1913568070637471</v>
+        <v>0.1932568070637471</v>
       </c>
       <c r="C74">
-        <v>-2144.924807412465</v>
+        <v>-2204.760957322726</v>
       </c>
       <c r="D74">
-        <v>1063.651192587535</v>
+        <v>1051.498042677274</v>
       </c>
       <c r="E74">
-        <v>2320.276</v>
+        <v>2367.959</v>
       </c>
       <c r="F74">
-        <v>3433.176</v>
+        <v>3480.859</v>
       </c>
       <c r="G74">
         <v>224.6</v>
@@ -7361,37 +7361,37 @@
         <v>227</v>
       </c>
       <c r="M74">
-        <v>809.5429008</v>
+        <v>820.7865522</v>
       </c>
       <c r="N74">
-        <v>-582.5429008</v>
+        <v>-593.7865522</v>
       </c>
       <c r="O74">
-        <v>-145.28619945952</v>
+        <v>-148.09036611868</v>
       </c>
       <c r="P74">
-        <v>-437.25670134048</v>
+        <v>-445.69618608132</v>
       </c>
       <c r="Q74">
-        <v>-436.55670134048</v>
+        <v>-444.99618608132</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.119477713172758</v>
+        <v>0.1222065173643416</v>
       </c>
       <c r="T74">
-        <v>1.701563814613347</v>
+        <v>1.764584696636064</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06993304486279055</v>
+        <v>0.06897505794686191</v>
       </c>
       <c r="W74">
-        <v>0.219309788021354</v>
+        <v>0.21953568133613</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2804051518155195</v>
+        <v>0.2765639853522932</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1932568070637471</v>
+        <v>0.1951568070637471</v>
       </c>
       <c r="C75">
-        <v>-2204.760957322726</v>
+        <v>-2264.322523748042</v>
       </c>
       <c r="D75">
-        <v>1051.498042677274</v>
+        <v>1039.619476251958</v>
       </c>
       <c r="E75">
-        <v>2367.959</v>
+        <v>2415.642</v>
       </c>
       <c r="F75">
-        <v>3480.859</v>
+        <v>3528.542</v>
       </c>
       <c r="G75">
         <v>224.6</v>
@@ -7443,37 +7443,37 @@
         <v>227</v>
       </c>
       <c r="M75">
-        <v>820.7865522</v>
+        <v>832.0302036</v>
       </c>
       <c r="N75">
-        <v>-593.7865522</v>
+        <v>-605.0302036</v>
       </c>
       <c r="O75">
-        <v>-148.09036611868</v>
+        <v>-150.89453277784</v>
       </c>
       <c r="P75">
-        <v>-445.69618608132</v>
+        <v>-454.13567082216</v>
       </c>
       <c r="Q75">
-        <v>-444.99618608132</v>
+        <v>-453.43567082216</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1222065173643416</v>
+        <v>0.1251452295706624</v>
       </c>
       <c r="T75">
-        <v>1.764584696636064</v>
+        <v>1.832453338814374</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06897505794686191</v>
+        <v>0.06804296256920161</v>
       </c>
       <c r="W75">
-        <v>0.21953568133613</v>
+        <v>0.2197554694261823</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2765639853522932</v>
+        <v>0.2728266341988838</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1951568070637471</v>
+        <v>0.1970568070637471</v>
       </c>
       <c r="C76">
-        <v>-2264.322523748042</v>
+        <v>-2323.618708484289</v>
       </c>
       <c r="D76">
-        <v>1039.619476251958</v>
+        <v>1028.006291515712</v>
       </c>
       <c r="E76">
-        <v>2415.642</v>
+        <v>2463.325</v>
       </c>
       <c r="F76">
-        <v>3528.542</v>
+        <v>3576.225</v>
       </c>
       <c r="G76">
         <v>224.6</v>
@@ -7525,37 +7525,37 @@
         <v>227</v>
       </c>
       <c r="M76">
-        <v>832.0302036</v>
+        <v>843.2738550000001</v>
       </c>
       <c r="N76">
-        <v>-605.0302036</v>
+        <v>-616.2738550000001</v>
       </c>
       <c r="O76">
-        <v>-150.89453277784</v>
+        <v>-153.698699437</v>
       </c>
       <c r="P76">
-        <v>-454.13567082216</v>
+        <v>-462.5751555630001</v>
       </c>
       <c r="Q76">
-        <v>-453.43567082216</v>
+        <v>-461.8751555630001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1251452295706624</v>
+        <v>0.1283190387534889</v>
       </c>
       <c r="T76">
-        <v>1.832453338814374</v>
+        <v>1.905751472366949</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06804296256920161</v>
+        <v>0.06713572306827892</v>
       </c>
       <c r="W76">
-        <v>0.2197554694261823</v>
+        <v>0.2199693965004998</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2728266341988838</v>
+        <v>0.2691889457428986</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1970568070637471</v>
+        <v>0.1989568070637471</v>
       </c>
       <c r="C77">
-        <v>-2323.618708484289</v>
+        <v>-2382.658306710768</v>
       </c>
       <c r="D77">
-        <v>1028.006291515712</v>
+        <v>1016.649693289233</v>
       </c>
       <c r="E77">
-        <v>2463.325</v>
+        <v>2511.008</v>
       </c>
       <c r="F77">
-        <v>3576.225</v>
+        <v>3623.908</v>
       </c>
       <c r="G77">
         <v>224.6</v>
@@ -7607,37 +7607,37 @@
         <v>227</v>
       </c>
       <c r="M77">
-        <v>843.2738550000001</v>
+        <v>854.5175064000001</v>
       </c>
       <c r="N77">
-        <v>-616.2738550000001</v>
+        <v>-627.5175064000001</v>
       </c>
       <c r="O77">
-        <v>-153.698699437</v>
+        <v>-156.50286609616</v>
       </c>
       <c r="P77">
-        <v>-462.5751555630001</v>
+        <v>-471.0146403038401</v>
       </c>
       <c r="Q77">
-        <v>-461.8751555630001</v>
+        <v>-470.3146403038401</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1283190387534889</v>
+        <v>0.1317573320348843</v>
       </c>
       <c r="T77">
-        <v>1.905751472366949</v>
+        <v>1.985157783715572</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06713572306827892</v>
+        <v>0.06625235829106473</v>
       </c>
       <c r="W77">
-        <v>0.2199693965004998</v>
+        <v>0.2201776939149669</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2691889457428986</v>
+        <v>0.2656469859304921</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1989568070637471</v>
+        <v>0.2008568070637471</v>
       </c>
       <c r="C78">
-        <v>-2382.658306710768</v>
+        <v>-2441.449729204688</v>
       </c>
       <c r="D78">
-        <v>1016.649693289233</v>
+        <v>1005.541270795312</v>
       </c>
       <c r="E78">
-        <v>2511.008</v>
+        <v>2558.691</v>
       </c>
       <c r="F78">
-        <v>3623.908</v>
+        <v>3671.591</v>
       </c>
       <c r="G78">
         <v>224.6</v>
@@ -7689,37 +7689,37 @@
         <v>227</v>
       </c>
       <c r="M78">
-        <v>854.5175064000001</v>
+        <v>865.7611578000001</v>
       </c>
       <c r="N78">
-        <v>-627.5175064000001</v>
+        <v>-638.7611578000001</v>
       </c>
       <c r="O78">
-        <v>-156.50286609616</v>
+        <v>-159.30703275532</v>
       </c>
       <c r="P78">
-        <v>-471.0146403038401</v>
+        <v>-479.45412504468</v>
       </c>
       <c r="Q78">
-        <v>-470.3146403038401</v>
+        <v>-478.7541250446801</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1317573320348843</v>
+        <v>0.1354946073407488</v>
       </c>
       <c r="T78">
-        <v>1.985157783715572</v>
+        <v>2.071468991703206</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06625235829106473</v>
+        <v>0.06539193805351842</v>
       </c>
       <c r="W78">
-        <v>0.2201776939149669</v>
+        <v>0.2203805810069804</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2656469859304921</v>
+        <v>0.2621970250742519</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2008568070637471</v>
+        <v>0.2027568070637471</v>
       </c>
       <c r="C79">
-        <v>-2441.449729204688</v>
+        <v>-2500.001023115027</v>
       </c>
       <c r="D79">
-        <v>1005.541270795312</v>
+        <v>994.6729768849729</v>
       </c>
       <c r="E79">
-        <v>2558.691</v>
+        <v>2606.374</v>
       </c>
       <c r="F79">
-        <v>3671.591</v>
+        <v>3719.274</v>
       </c>
       <c r="G79">
         <v>224.6</v>
@@ -7771,37 +7771,37 @@
         <v>227</v>
       </c>
       <c r="M79">
-        <v>865.7611578000001</v>
+        <v>877.0048092000001</v>
       </c>
       <c r="N79">
-        <v>-638.7611578000001</v>
+        <v>-650.0048092000001</v>
       </c>
       <c r="O79">
-        <v>-159.30703275532</v>
+        <v>-162.11119941448</v>
       </c>
       <c r="P79">
-        <v>-479.45412504468</v>
+        <v>-487.8936097855201</v>
       </c>
       <c r="Q79">
-        <v>-478.7541250446801</v>
+        <v>-487.1936097855201</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1354946073407488</v>
+        <v>0.1395716349471465</v>
       </c>
       <c r="T79">
-        <v>2.071468991703206</v>
+        <v>2.16562667314426</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06539193805351842</v>
+        <v>0.06455357987334512</v>
       </c>
       <c r="W79">
-        <v>0.2203805810069804</v>
+        <v>0.2205782658658652</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2621970250742519</v>
+        <v>0.2588355247527871</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2027568070637471</v>
+        <v>0.2046568070637471</v>
       </c>
       <c r="C80">
-        <v>-2500.001023115027</v>
+        <v>-2558.319891403604</v>
       </c>
       <c r="D80">
-        <v>994.6729768849729</v>
+        <v>984.0371085963966</v>
       </c>
       <c r="E80">
-        <v>2606.374</v>
+        <v>2654.057</v>
       </c>
       <c r="F80">
-        <v>3719.274</v>
+        <v>3766.957</v>
       </c>
       <c r="G80">
         <v>224.6</v>
@@ -7853,37 +7853,37 @@
         <v>227</v>
       </c>
       <c r="M80">
-        <v>877.0048092000001</v>
+        <v>888.2484606000002</v>
       </c>
       <c r="N80">
-        <v>-650.0048092000001</v>
+        <v>-661.2484606000002</v>
       </c>
       <c r="O80">
-        <v>-162.11119941448</v>
+        <v>-164.9153660736401</v>
       </c>
       <c r="P80">
-        <v>-487.8936097855201</v>
+        <v>-496.3330945263601</v>
       </c>
       <c r="Q80">
-        <v>-487.1936097855201</v>
+        <v>-495.6330945263601</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1395716349471465</v>
+        <v>0.1440369508970106</v>
       </c>
       <c r="T80">
-        <v>2.16562667314426</v>
+        <v>2.268751752817797</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06455357987334512</v>
+        <v>0.06373644595089771</v>
       </c>
       <c r="W80">
-        <v>0.2205782658658652</v>
+        <v>0.2207709460447783</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2588355247527871</v>
+        <v>0.2555591257052835</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2046568070637471</v>
+        <v>0.2065568070637471</v>
       </c>
       <c r="C81">
-        <v>-2558.319891403604</v>
+        <v>-2616.413711052063</v>
       </c>
       <c r="D81">
-        <v>984.0371085963966</v>
+        <v>973.6262889479375</v>
       </c>
       <c r="E81">
-        <v>2654.057</v>
+        <v>2701.74</v>
       </c>
       <c r="F81">
-        <v>3766.957</v>
+        <v>3814.64</v>
       </c>
       <c r="G81">
         <v>224.6</v>
@@ -7935,37 +7935,37 @@
         <v>227</v>
       </c>
       <c r="M81">
-        <v>888.2484606000002</v>
+        <v>899.4921120000001</v>
       </c>
       <c r="N81">
-        <v>-661.2484606000002</v>
+        <v>-672.4921120000001</v>
       </c>
       <c r="O81">
-        <v>-164.9153660736401</v>
+        <v>-167.7195327328</v>
       </c>
       <c r="P81">
-        <v>-496.3330945263601</v>
+        <v>-504.7725792672001</v>
       </c>
       <c r="Q81">
-        <v>-495.6330945263601</v>
+        <v>-504.0725792672001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1440369508970106</v>
+        <v>0.1489487984418612</v>
       </c>
       <c r="T81">
-        <v>2.268751752817797</v>
+        <v>2.382189340458687</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06373644595089771</v>
+        <v>0.06293974037651148</v>
       </c>
       <c r="W81">
-        <v>0.2207709460447783</v>
+        <v>0.2209588092192186</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2555591257052835</v>
+        <v>0.2523646366339675</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2065568070637471</v>
+        <v>0.2084568070637471</v>
       </c>
       <c r="C82">
-        <v>-2616.413711052063</v>
+        <v>-2674.289550125221</v>
       </c>
       <c r="D82">
-        <v>973.6262889479375</v>
+        <v>963.4334498747789</v>
       </c>
       <c r="E82">
-        <v>2701.74</v>
+        <v>2749.423</v>
       </c>
       <c r="F82">
-        <v>3814.64</v>
+        <v>3862.323</v>
       </c>
       <c r="G82">
         <v>224.6</v>
@@ -8017,37 +8017,37 @@
         <v>227</v>
       </c>
       <c r="M82">
-        <v>899.4921120000001</v>
+        <v>910.7357634000001</v>
       </c>
       <c r="N82">
-        <v>-672.4921120000001</v>
+        <v>-683.7357634000001</v>
       </c>
       <c r="O82">
-        <v>-167.7195327328</v>
+        <v>-170.52369939196</v>
       </c>
       <c r="P82">
-        <v>-504.7725792672001</v>
+        <v>-513.2120640080401</v>
       </c>
       <c r="Q82">
-        <v>-504.0725792672001</v>
+        <v>-512.5120640080402</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1489487984418612</v>
+        <v>0.1543776825703802</v>
       </c>
       <c r="T82">
-        <v>2.382189340458687</v>
+        <v>2.507567726798618</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06293974037651148</v>
+        <v>0.06216270654470271</v>
       </c>
       <c r="W82">
-        <v>0.2209588092192186</v>
+        <v>0.2211420337967591</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2523646366339675</v>
+        <v>0.2492490238360172</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2084568070637471</v>
+        <v>0.2103568070637471</v>
       </c>
       <c r="C83">
-        <v>-2674.289550125221</v>
+        <v>-2731.954183773699</v>
       </c>
       <c r="D83">
-        <v>963.4334498747789</v>
+        <v>953.4518162263013</v>
       </c>
       <c r="E83">
-        <v>2749.423</v>
+        <v>2797.106</v>
       </c>
       <c r="F83">
-        <v>3862.323</v>
+        <v>3910.006</v>
       </c>
       <c r="G83">
         <v>224.6</v>
@@ -8099,37 +8099,37 @@
         <v>227</v>
       </c>
       <c r="M83">
-        <v>910.7357634000001</v>
+        <v>921.9794148000001</v>
       </c>
       <c r="N83">
-        <v>-683.7357634000001</v>
+        <v>-694.9794148000001</v>
       </c>
       <c r="O83">
-        <v>-170.52369939196</v>
+        <v>-173.32786605112</v>
       </c>
       <c r="P83">
-        <v>-513.2120640080401</v>
+        <v>-521.65154874888</v>
       </c>
       <c r="Q83">
-        <v>-512.5120640080402</v>
+        <v>-520.95154874888</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1543776825703802</v>
+        <v>0.1604097760465124</v>
       </c>
       <c r="T83">
-        <v>2.507567726798618</v>
+        <v>2.646877044954097</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06216270654470271</v>
+        <v>0.06140462475757219</v>
       </c>
       <c r="W83">
-        <v>0.2211420337967591</v>
+        <v>0.2213207894821645</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2492490238360172</v>
+        <v>0.2462094015941146</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2103568070637471</v>
+        <v>0.2122568070637471</v>
       </c>
       <c r="C84">
-        <v>-2731.954183773699</v>
+        <v>-2789.414109251985</v>
       </c>
       <c r="D84">
-        <v>953.4518162263013</v>
+        <v>943.6748907480149</v>
       </c>
       <c r="E84">
-        <v>2797.106</v>
+        <v>2844.789</v>
       </c>
       <c r="F84">
-        <v>3910.006</v>
+        <v>3957.689</v>
       </c>
       <c r="G84">
         <v>224.6</v>
@@ -8181,37 +8181,37 @@
         <v>227</v>
       </c>
       <c r="M84">
-        <v>921.9794148000001</v>
+        <v>933.2230662000001</v>
       </c>
       <c r="N84">
-        <v>-694.9794148000001</v>
+        <v>-706.2230662000001</v>
       </c>
       <c r="O84">
-        <v>-173.32786605112</v>
+        <v>-176.13203271028</v>
       </c>
       <c r="P84">
-        <v>-521.65154874888</v>
+        <v>-530.0910334897201</v>
       </c>
       <c r="Q84">
-        <v>-520.95154874888</v>
+        <v>-529.39103348972</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1604097760465124</v>
+        <v>0.1671515275786602</v>
       </c>
       <c r="T84">
-        <v>2.646877044954097</v>
+        <v>2.802575694657279</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06140462475757219</v>
+        <v>0.06066481000145686</v>
       </c>
       <c r="W84">
-        <v>0.2213207894821645</v>
+        <v>0.2214952378016565</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2462094015941146</v>
+        <v>0.2432430232616554</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2122568070637471</v>
+        <v>0.2141568070637471</v>
       </c>
       <c r="C85">
-        <v>-2789.414109251985</v>
+        <v>-2846.675560021889</v>
       </c>
       <c r="D85">
-        <v>943.6748907480149</v>
+        <v>934.0964399781117</v>
       </c>
       <c r="E85">
-        <v>2844.789</v>
+        <v>2892.472000000001</v>
       </c>
       <c r="F85">
-        <v>3957.689</v>
+        <v>4005.372000000001</v>
       </c>
       <c r="G85">
         <v>224.6</v>
@@ -8263,37 +8263,37 @@
         <v>227</v>
       </c>
       <c r="M85">
-        <v>933.2230662000001</v>
+        <v>944.4667176000003</v>
       </c>
       <c r="N85">
-        <v>-706.2230662000001</v>
+        <v>-717.4667176000003</v>
       </c>
       <c r="O85">
-        <v>-176.13203271028</v>
+        <v>-178.9361993694401</v>
       </c>
       <c r="P85">
-        <v>-530.0910334897201</v>
+        <v>-538.5305182305602</v>
       </c>
       <c r="Q85">
-        <v>-529.39103348972</v>
+        <v>-537.8305182305603</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1671515275786602</v>
+        <v>0.1747359980523265</v>
       </c>
       <c r="T85">
-        <v>2.802575694657279</v>
+        <v>2.97773667557336</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06066481000145686</v>
+        <v>0.05994260988239188</v>
       </c>
       <c r="W85">
-        <v>0.2214952378016565</v>
+        <v>0.221665532589732</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2432430232616554</v>
+        <v>0.2403472729847309</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2141568070637471</v>
+        <v>0.2160568070637471</v>
       </c>
       <c r="C86">
-        <v>-2846.675560021888</v>
+        <v>-2903.744519005704</v>
       </c>
       <c r="D86">
-        <v>934.0964399781117</v>
+        <v>924.7104809942959</v>
       </c>
       <c r="E86">
-        <v>2892.472</v>
+        <v>2940.155</v>
       </c>
       <c r="F86">
-        <v>4005.372</v>
+        <v>4053.055</v>
       </c>
       <c r="G86">
         <v>224.6</v>
@@ -8345,37 +8345,37 @@
         <v>227</v>
       </c>
       <c r="M86">
-        <v>944.4667176</v>
+        <v>955.710369</v>
       </c>
       <c r="N86">
-        <v>-717.4667176</v>
+        <v>-728.710369</v>
       </c>
       <c r="O86">
-        <v>-178.93619936944</v>
+        <v>-181.7403660286</v>
       </c>
       <c r="P86">
-        <v>-538.53051823056</v>
+        <v>-546.9700029713999</v>
       </c>
       <c r="Q86">
-        <v>-537.8305182305601</v>
+        <v>-546.2700029713999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1747359980523264</v>
+        <v>0.1833317312558148</v>
       </c>
       <c r="T86">
-        <v>2.977736675573357</v>
+        <v>3.176252453944915</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0599426098823919</v>
+        <v>0.05923740270730494</v>
       </c>
       <c r="W86">
-        <v>0.221665532589732</v>
+        <v>0.2218318204416175</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2403472729847309</v>
+        <v>0.23751965800844</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2160568070637471</v>
+        <v>0.2179568070637471</v>
       </c>
       <c r="C87">
-        <v>-2903.744519005704</v>
+        <v>-2960.62673104831</v>
       </c>
       <c r="D87">
-        <v>924.7104809942959</v>
+        <v>915.5112689516907</v>
       </c>
       <c r="E87">
-        <v>2940.155</v>
+        <v>2987.838</v>
       </c>
       <c r="F87">
-        <v>4053.055</v>
+        <v>4100.738</v>
       </c>
       <c r="G87">
         <v>224.6</v>
@@ -8427,37 +8427,37 @@
         <v>227</v>
       </c>
       <c r="M87">
-        <v>955.710369</v>
+        <v>966.9540204000001</v>
       </c>
       <c r="N87">
-        <v>-728.710369</v>
+        <v>-739.9540204000001</v>
       </c>
       <c r="O87">
-        <v>-181.7403660286</v>
+        <v>-184.54453268776</v>
       </c>
       <c r="P87">
-        <v>-546.9700029713999</v>
+        <v>-555.4094877122401</v>
       </c>
       <c r="Q87">
-        <v>-546.2700029713999</v>
+        <v>-554.7094877122402</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1833317312558148</v>
+        <v>0.1931554263455159</v>
       </c>
       <c r="T87">
-        <v>3.176252453944915</v>
+        <v>3.403127629226694</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05923740270730494</v>
+        <v>0.05854859569908046</v>
       </c>
       <c r="W87">
-        <v>0.2218318204416175</v>
+        <v>0.2219942411341568</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.23751965800844</v>
+        <v>0.2347578015199697</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2179568070637471</v>
+        <v>0.2198568070637471</v>
       </c>
       <c r="C88">
-        <v>-2960.62673104831</v>
+        <v>-3017.327714642735</v>
       </c>
       <c r="D88">
-        <v>915.5112689516907</v>
+        <v>906.4932853572654</v>
       </c>
       <c r="E88">
-        <v>2987.838</v>
+        <v>3035.521</v>
       </c>
       <c r="F88">
-        <v>4100.738</v>
+        <v>4148.421</v>
       </c>
       <c r="G88">
         <v>224.6</v>
@@ -8509,37 +8509,37 @@
         <v>227</v>
       </c>
       <c r="M88">
-        <v>966.9540204000001</v>
+        <v>978.1976718000001</v>
       </c>
       <c r="N88">
-        <v>-739.9540204000001</v>
+        <v>-751.1976718000001</v>
       </c>
       <c r="O88">
-        <v>-184.54453268776</v>
+        <v>-187.34869934692</v>
       </c>
       <c r="P88">
-        <v>-555.4094877122401</v>
+        <v>-563.84897245308</v>
       </c>
       <c r="Q88">
-        <v>-554.7094877122402</v>
+        <v>-563.14897245308</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1931554263455159</v>
+        <v>0.2044904591413248</v>
       </c>
       <c r="T88">
-        <v>3.403127629226694</v>
+        <v>3.664906677628748</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05854859569908046</v>
+        <v>0.05787562333472322</v>
       </c>
       <c r="W88">
-        <v>0.2219942411341568</v>
+        <v>0.2221529280176723</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2347578015199697</v>
+        <v>0.2320594359852575</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2198568070637471</v>
+        <v>0.2217568070637471</v>
       </c>
       <c r="C89">
-        <v>-3017.327714642735</v>
+        <v>-3073.852772969494</v>
       </c>
       <c r="D89">
-        <v>906.4932853572654</v>
+        <v>897.6512270305059</v>
       </c>
       <c r="E89">
-        <v>3035.521</v>
+        <v>3083.204</v>
       </c>
       <c r="F89">
-        <v>4148.421</v>
+        <v>4196.104</v>
       </c>
       <c r="G89">
         <v>224.6</v>
@@ -8591,37 +8591,37 @@
         <v>227</v>
       </c>
       <c r="M89">
-        <v>978.1976718000001</v>
+        <v>989.4413232000001</v>
       </c>
       <c r="N89">
-        <v>-751.1976718000001</v>
+        <v>-762.4413232000001</v>
       </c>
       <c r="O89">
-        <v>-187.34869934692</v>
+        <v>-190.15286600608</v>
       </c>
       <c r="P89">
-        <v>-563.84897245308</v>
+        <v>-572.2884571939201</v>
       </c>
       <c r="Q89">
-        <v>-563.14897245308</v>
+        <v>-571.58845719392</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2044904591413248</v>
+        <v>0.2177146640697686</v>
       </c>
       <c r="T89">
-        <v>3.664906677628748</v>
+        <v>3.970315567431145</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05787562333472322</v>
+        <v>0.05721794579682863</v>
       </c>
       <c r="W89">
-        <v>0.2221529280176723</v>
+        <v>0.2223080083811078</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2320594359852575</v>
+        <v>0.2294223969399705</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2217568070637471</v>
+        <v>0.2236568070637471</v>
       </c>
       <c r="C90">
-        <v>-3073.852772969494</v>
+        <v>-3130.207004296088</v>
       </c>
       <c r="D90">
-        <v>897.6512270305059</v>
+        <v>888.9799957039123</v>
       </c>
       <c r="E90">
-        <v>3083.204</v>
+        <v>3130.887</v>
       </c>
       <c r="F90">
-        <v>4196.104</v>
+        <v>4243.787</v>
       </c>
       <c r="G90">
         <v>224.6</v>
@@ -8673,37 +8673,37 @@
         <v>227</v>
       </c>
       <c r="M90">
-        <v>989.4413232000001</v>
+        <v>1000.6849746</v>
       </c>
       <c r="N90">
-        <v>-762.4413232000001</v>
+        <v>-773.6849746000001</v>
       </c>
       <c r="O90">
-        <v>-190.15286600608</v>
+        <v>-192.95703266524</v>
       </c>
       <c r="P90">
-        <v>-572.2884571939201</v>
+        <v>-580.7279419347601</v>
       </c>
       <c r="Q90">
-        <v>-571.58845719392</v>
+        <v>-580.0279419347601</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2177146640697686</v>
+        <v>0.233343269894293</v>
       </c>
       <c r="T90">
-        <v>3.970315567431145</v>
+        <v>4.331253346288521</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05721794579682863</v>
+        <v>0.05657504752944852</v>
       </c>
       <c r="W90">
-        <v>0.2223080083811078</v>
+        <v>0.2224596037925561</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2294223969399705</v>
+        <v>0.2268446171990719</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2236568070637471</v>
+        <v>0.2255568070637471</v>
       </c>
       <c r="C91">
-        <v>-3130.207004296088</v>
+        <v>-3186.395311779515</v>
       </c>
       <c r="D91">
-        <v>888.9799957039123</v>
+        <v>880.4746882204854</v>
       </c>
       <c r="E91">
-        <v>3130.887</v>
+        <v>3178.57</v>
       </c>
       <c r="F91">
-        <v>4243.787</v>
+        <v>4291.47</v>
       </c>
       <c r="G91">
         <v>224.6</v>
@@ -8755,37 +8755,37 @@
         <v>227</v>
       </c>
       <c r="M91">
-        <v>1000.6849746</v>
+        <v>1011.928626</v>
       </c>
       <c r="N91">
-        <v>-773.6849746000001</v>
+        <v>-784.9286260000001</v>
       </c>
       <c r="O91">
-        <v>-192.95703266524</v>
+        <v>-195.7611993244</v>
       </c>
       <c r="P91">
-        <v>-580.7279419347601</v>
+        <v>-589.1674266756002</v>
       </c>
       <c r="Q91">
-        <v>-580.0279419347601</v>
+        <v>-588.4674266756001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.233343269894293</v>
+        <v>0.2520975968837223</v>
       </c>
       <c r="T91">
-        <v>4.331253346288521</v>
+        <v>4.764378680917374</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05657504752944852</v>
+        <v>0.05594643589023244</v>
       </c>
       <c r="W91">
-        <v>0.2224596037925561</v>
+        <v>0.2226078304170832</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2268446171990719</v>
+        <v>0.2243241214524155</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2255568070637471</v>
+        <v>0.2274568070637471</v>
       </c>
       <c r="C92">
-        <v>-3186.395311779515</v>
+        <v>-3242.422412711413</v>
       </c>
       <c r="D92">
-        <v>880.4746882204854</v>
+        <v>872.1305872885875</v>
       </c>
       <c r="E92">
-        <v>3178.57</v>
+        <v>3226.253</v>
       </c>
       <c r="F92">
-        <v>4291.47</v>
+        <v>4339.153</v>
       </c>
       <c r="G92">
         <v>224.6</v>
@@ -8837,37 +8837,37 @@
         <v>227</v>
       </c>
       <c r="M92">
-        <v>1011.928626</v>
+        <v>1023.1722774</v>
       </c>
       <c r="N92">
-        <v>-784.9286260000001</v>
+        <v>-796.1722774000001</v>
       </c>
       <c r="O92">
-        <v>-195.7611993244</v>
+        <v>-198.56536598356</v>
       </c>
       <c r="P92">
-        <v>-589.1674266756002</v>
+        <v>-597.6069114164401</v>
       </c>
       <c r="Q92">
-        <v>-588.4674266756001</v>
+        <v>-596.9069114164402</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2520975968837223</v>
+        <v>0.2750195520930248</v>
       </c>
       <c r="T92">
-        <v>4.764378680917374</v>
+        <v>5.293754089908194</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05594643589023244</v>
+        <v>0.05533163989143867</v>
       </c>
       <c r="W92">
-        <v>0.2226078304170832</v>
+        <v>0.2227527993135988</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2243241214524155</v>
+        <v>0.2218590212166747</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2274568070637471</v>
+        <v>0.2293568070637471</v>
       </c>
       <c r="C93">
-        <v>-3242.422412711413</v>
+        <v>-3298.292847242438</v>
       </c>
       <c r="D93">
-        <v>872.1305872885875</v>
+        <v>863.9431527575617</v>
       </c>
       <c r="E93">
-        <v>3226.253</v>
+        <v>3273.936</v>
       </c>
       <c r="F93">
-        <v>4339.153</v>
+        <v>4386.836</v>
       </c>
       <c r="G93">
         <v>224.6</v>
@@ -8919,37 +8919,37 @@
         <v>227</v>
       </c>
       <c r="M93">
-        <v>1023.1722774</v>
+        <v>1034.4159288</v>
       </c>
       <c r="N93">
-        <v>-796.1722774000001</v>
+        <v>-807.4159288000001</v>
       </c>
       <c r="O93">
-        <v>-198.56536598356</v>
+        <v>-201.36953264272</v>
       </c>
       <c r="P93">
-        <v>-597.6069114164401</v>
+        <v>-606.04639615728</v>
       </c>
       <c r="Q93">
-        <v>-596.9069114164402</v>
+        <v>-605.34639615728</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2750195520930248</v>
+        <v>0.303671996104653</v>
       </c>
       <c r="T93">
-        <v>5.293754089908194</v>
+        <v>5.955473351146719</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05533163989143867</v>
+        <v>0.05473020902305347</v>
       </c>
       <c r="W93">
-        <v>0.2227527993135988</v>
+        <v>0.222894616712364</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2218590212166747</v>
+        <v>0.2194475101164934</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2293568070637471</v>
+        <v>0.2312568070637471</v>
       </c>
       <c r="C94">
-        <v>-3298.292847242438</v>
+        <v>-3354.010986619808</v>
       </c>
       <c r="D94">
-        <v>863.9431527575617</v>
+        <v>855.9080133801921</v>
       </c>
       <c r="E94">
-        <v>3273.936</v>
+        <v>3321.619</v>
       </c>
       <c r="F94">
-        <v>4386.836</v>
+        <v>4434.519</v>
       </c>
       <c r="G94">
         <v>224.6</v>
@@ -9001,37 +9001,37 @@
         <v>227</v>
       </c>
       <c r="M94">
-        <v>1034.4159288</v>
+        <v>1045.6595802</v>
       </c>
       <c r="N94">
-        <v>-807.4159288000001</v>
+        <v>-818.6595802000002</v>
       </c>
       <c r="O94">
-        <v>-201.36953264272</v>
+        <v>-204.17369930188</v>
       </c>
       <c r="P94">
-        <v>-606.04639615728</v>
+        <v>-614.4858808981201</v>
       </c>
       <c r="Q94">
-        <v>-605.34639615728</v>
+        <v>-613.78588089812</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.303671996104653</v>
+        <v>0.340510852691032</v>
       </c>
       <c r="T94">
-        <v>5.955473351146719</v>
+        <v>6.806255258453394</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05473020902305347</v>
+        <v>0.05414171215183784</v>
       </c>
       <c r="W94">
-        <v>0.222894616712364</v>
+        <v>0.2230333842745967</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2194475101164934</v>
+        <v>0.2170878594700796</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2312568070637471</v>
+        <v>0.2331568070637471</v>
       </c>
       <c r="C95">
-        <v>-3354.010986619808</v>
+        <v>-3409.581040969383</v>
       </c>
       <c r="D95">
-        <v>855.9080133801921</v>
+        <v>848.0209590306174</v>
       </c>
       <c r="E95">
-        <v>3321.619</v>
+        <v>3369.302</v>
       </c>
       <c r="F95">
-        <v>4434.519</v>
+        <v>4482.202</v>
       </c>
       <c r="G95">
         <v>224.6</v>
@@ -9083,37 +9083,37 @@
         <v>227</v>
       </c>
       <c r="M95">
-        <v>1045.6595802</v>
+        <v>1056.9032316</v>
       </c>
       <c r="N95">
-        <v>-818.6595802000002</v>
+        <v>-829.9032316</v>
       </c>
       <c r="O95">
-        <v>-204.17369930188</v>
+        <v>-206.97786596104</v>
       </c>
       <c r="P95">
-        <v>-614.4858808981201</v>
+        <v>-622.92536563896</v>
       </c>
       <c r="Q95">
-        <v>-613.78588089812</v>
+        <v>-622.2253656389601</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.340510852691032</v>
+        <v>0.3896293281395374</v>
       </c>
       <c r="T95">
-        <v>6.806255258453394</v>
+        <v>7.940631134862295</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05414171215183784</v>
+        <v>0.05356573649064809</v>
       </c>
       <c r="W95">
-        <v>0.2230333842745967</v>
+        <v>0.2231691993355052</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2170878594700796</v>
+        <v>0.2147784141565681</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2331568070637471</v>
+        <v>0.2350568070637472</v>
       </c>
       <c r="C96">
-        <v>-3409.581040969383</v>
+        <v>-3465.007066651425</v>
       </c>
       <c r="D96">
-        <v>848.0209590306174</v>
+        <v>840.2779333485752</v>
       </c>
       <c r="E96">
-        <v>3369.302</v>
+        <v>3416.985</v>
       </c>
       <c r="F96">
-        <v>4482.202</v>
+        <v>4529.885</v>
       </c>
       <c r="G96">
         <v>224.6</v>
@@ -9165,37 +9165,37 @@
         <v>227</v>
       </c>
       <c r="M96">
-        <v>1056.9032316</v>
+        <v>1068.146883</v>
       </c>
       <c r="N96">
-        <v>-829.9032316</v>
+        <v>-841.1468830000001</v>
       </c>
       <c r="O96">
-        <v>-206.97786596104</v>
+        <v>-209.7820326202</v>
       </c>
       <c r="P96">
-        <v>-622.92536563896</v>
+        <v>-631.3648503798001</v>
       </c>
       <c r="Q96">
-        <v>-622.2253656389601</v>
+        <v>-630.6648503798001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3896293281395374</v>
+        <v>0.4583951937674451</v>
       </c>
       <c r="T96">
-        <v>7.940631134862295</v>
+        <v>9.52875736183476</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05356573649064809</v>
+        <v>0.05300188663285178</v>
       </c>
       <c r="W96">
-        <v>0.2231691993355052</v>
+        <v>0.2233021551319736</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2147784141565681</v>
+        <v>0.2125175887443936</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2350568070637472</v>
+        <v>0.2369568070637471</v>
       </c>
       <c r="C97">
-        <v>-3465.007066651425</v>
+        <v>-3520.29297321702</v>
       </c>
       <c r="D97">
-        <v>840.2779333485752</v>
+        <v>832.6750267829807</v>
       </c>
       <c r="E97">
-        <v>3416.985</v>
+        <v>3464.668</v>
       </c>
       <c r="F97">
-        <v>4529.885</v>
+        <v>4577.568</v>
       </c>
       <c r="G97">
         <v>224.6</v>
@@ -9247,37 +9247,37 @@
         <v>227</v>
       </c>
       <c r="M97">
-        <v>1068.146883</v>
+        <v>1079.3905344</v>
       </c>
       <c r="N97">
-        <v>-841.1468830000001</v>
+        <v>-852.3905344000002</v>
       </c>
       <c r="O97">
-        <v>-209.7820326202</v>
+        <v>-212.5861992793601</v>
       </c>
       <c r="P97">
-        <v>-631.3648503798001</v>
+        <v>-639.8043351206402</v>
       </c>
       <c r="Q97">
-        <v>-630.6648503798001</v>
+        <v>-639.1043351206401</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4583951937674451</v>
+        <v>0.5615439922093065</v>
       </c>
       <c r="T97">
-        <v>9.52875736183476</v>
+        <v>11.91094670229345</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05300188663285178</v>
+        <v>0.05244978364709291</v>
       </c>
       <c r="W97">
-        <v>0.2233021551319736</v>
+        <v>0.2234323410160155</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2125175887443936</v>
+        <v>0.2103038638616396</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2369568070637471</v>
+        <v>0.2388568070637471</v>
       </c>
       <c r="C98">
-        <v>-3520.292973217019</v>
+        <v>-3575.442529990228</v>
       </c>
       <c r="D98">
-        <v>832.6750267829811</v>
+        <v>825.2084700097723</v>
       </c>
       <c r="E98">
-        <v>3464.668</v>
+        <v>3512.351</v>
       </c>
       <c r="F98">
-        <v>4577.568</v>
+        <v>4625.251</v>
       </c>
       <c r="G98">
         <v>224.6</v>
@@ -9329,37 +9329,37 @@
         <v>227</v>
       </c>
       <c r="M98">
-        <v>1079.3905344</v>
+        <v>1090.6341858</v>
       </c>
       <c r="N98">
-        <v>-852.3905344000002</v>
+        <v>-863.6341858000001</v>
       </c>
       <c r="O98">
-        <v>-212.5861992793601</v>
+        <v>-215.39036593852</v>
       </c>
       <c r="P98">
-        <v>-639.8043351206402</v>
+        <v>-648.24381986148</v>
       </c>
       <c r="Q98">
-        <v>-639.1043351206401</v>
+        <v>-647.54381986148</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5615439922093052</v>
+        <v>0.7334586562790737</v>
       </c>
       <c r="T98">
-        <v>11.91094670229342</v>
+        <v>15.88126226972456</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05244978364709291</v>
+        <v>0.05190906422805072</v>
       </c>
       <c r="W98">
-        <v>0.2234323410160155</v>
+        <v>0.2235598426550257</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2103038638616396</v>
+        <v>0.2081357827909011</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2388568070637471</v>
+        <v>0.2407568070637471</v>
       </c>
       <c r="C99">
-        <v>-3575.442529990228</v>
+        <v>-3630.459372299259</v>
       </c>
       <c r="D99">
-        <v>825.2084700097723</v>
+        <v>817.8746277007414</v>
       </c>
       <c r="E99">
-        <v>3512.351</v>
+        <v>3560.034</v>
       </c>
       <c r="F99">
-        <v>4625.251</v>
+        <v>4672.934</v>
       </c>
       <c r="G99">
         <v>224.6</v>
@@ -9411,37 +9411,37 @@
         <v>227</v>
       </c>
       <c r="M99">
-        <v>1090.6341858</v>
+        <v>1101.8778372</v>
       </c>
       <c r="N99">
-        <v>-863.6341858000001</v>
+        <v>-874.8778372000002</v>
       </c>
       <c r="O99">
-        <v>-215.39036593852</v>
+        <v>-218.1945325976801</v>
       </c>
       <c r="P99">
-        <v>-648.24381986148</v>
+        <v>-656.68330460232</v>
       </c>
       <c r="Q99">
-        <v>-647.54381986148</v>
+        <v>-655.98330460232</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7334586562790737</v>
+        <v>1.077287984418611</v>
       </c>
       <c r="T99">
-        <v>15.88126226972456</v>
+        <v>23.82189340458684</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05190906422805072</v>
+        <v>0.05137937989919305</v>
       </c>
       <c r="W99">
-        <v>0.2235598426550257</v>
+        <v>0.2236847422197703</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2081357827909011</v>
+        <v>0.2060119482726265</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2407568070637471</v>
+        <v>0.2426568070637471</v>
       </c>
       <c r="C100">
-        <v>-3630.459372299259</v>
+        <v>-3685.347007378296</v>
       </c>
       <c r="D100">
-        <v>817.8746277007414</v>
+        <v>810.6699926217045</v>
       </c>
       <c r="E100">
-        <v>3560.034</v>
+        <v>3607.717</v>
       </c>
       <c r="F100">
-        <v>4672.934</v>
+        <v>4720.617</v>
       </c>
       <c r="G100">
         <v>224.6</v>
@@ -9493,37 +9493,37 @@
         <v>227</v>
       </c>
       <c r="M100">
-        <v>1101.8778372</v>
+        <v>1113.1214886</v>
       </c>
       <c r="N100">
-        <v>-874.8778372000002</v>
+        <v>-886.1214886</v>
       </c>
       <c r="O100">
-        <v>-218.1945325976801</v>
+        <v>-220.99869925684</v>
       </c>
       <c r="P100">
-        <v>-656.68330460232</v>
+        <v>-665.12278934316</v>
       </c>
       <c r="Q100">
-        <v>-655.98330460232</v>
+        <v>-664.42278934316</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.077287984418611</v>
+        <v>2.108775968837221</v>
       </c>
       <c r="T100">
-        <v>23.82189340458684</v>
+        <v>47.64378680917368</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05137937989919305</v>
+        <v>0.05086039626384768</v>
       </c>
       <c r="W100">
-        <v>0.2236847422197703</v>
+        <v>0.2238071185609847</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2060119482726265</v>
+        <v>0.2039310195021959</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2426568070637471</v>
-      </c>
-      <c r="C101">
-        <v>-3685.347007378296</v>
-      </c>
-      <c r="D101">
-        <v>810.6699926217045</v>
-      </c>
-      <c r="E101">
-        <v>3607.717</v>
-      </c>
-      <c r="F101">
-        <v>4720.617</v>
-      </c>
-      <c r="G101">
-        <v>224.6</v>
-      </c>
-      <c r="H101">
-        <v>3655.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>227.7</v>
-      </c>
-      <c r="K101">
-        <v>0.6999999999999886</v>
-      </c>
-      <c r="L101">
-        <v>227</v>
-      </c>
-      <c r="M101">
-        <v>1113.1214886</v>
-      </c>
-      <c r="N101">
-        <v>-886.1214886</v>
-      </c>
-      <c r="O101">
-        <v>-220.99869925684</v>
-      </c>
-      <c r="P101">
-        <v>-665.12278934316</v>
-      </c>
-      <c r="Q101">
-        <v>-664.42278934316</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.108775968837221</v>
-      </c>
-      <c r="T101">
-        <v>47.64378680917368</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05086039626384768</v>
-      </c>
-      <c r="W101">
-        <v>0.2238071185609847</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2039310195021959</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
